--- a/DataAnalyst.xlsx
+++ b/DataAnalyst.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malik\OneDrive\Documents\Data\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905D8985-61CD-4899-A562-ED3E8E77DD00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA12FAED-D298-487E-BF6A-1C04E77CB6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-9015" windowWidth="21840" windowHeight="13740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-9015" windowWidth="21840" windowHeight="13740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="creatingtable" sheetId="2" r:id="rId2"/>
-    <sheet name="pivottable" sheetId="3" r:id="rId3"/>
+    <sheet name="InventorySys" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/DataAnalyst.xlsx
+++ b/DataAnalyst.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malik\OneDrive\Documents\Data\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA12FAED-D298-487E-BF6A-1C04E77CB6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68258BC7-63FF-4AB6-925A-834993375F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21720" yWindow="-9015" windowWidth="21840" windowHeight="13740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,9 @@
     <sheet name="creatingtable" sheetId="2" r:id="rId2"/>
     <sheet name="InventorySys" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="ProductList">Products[ProductID]</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="229">
   <si>
     <t>ELECTRONICS COMPANIES REPORT Q1 2023</t>
   </si>
@@ -215,17 +218,526 @@
   </si>
   <si>
     <t>Reacher Gr</t>
+  </si>
+  <si>
+    <t>ProductID</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>P001</t>
+  </si>
+  <si>
+    <t>P002</t>
+  </si>
+  <si>
+    <t>P003</t>
+  </si>
+  <si>
+    <t>P004</t>
+  </si>
+  <si>
+    <t>P005</t>
+  </si>
+  <si>
+    <t>P006</t>
+  </si>
+  <si>
+    <t>P007</t>
+  </si>
+  <si>
+    <t>P008</t>
+  </si>
+  <si>
+    <t>P009</t>
+  </si>
+  <si>
+    <t>P010</t>
+  </si>
+  <si>
+    <t>P011</t>
+  </si>
+  <si>
+    <t>P012</t>
+  </si>
+  <si>
+    <t>P013</t>
+  </si>
+  <si>
+    <t>P014</t>
+  </si>
+  <si>
+    <t>P015</t>
+  </si>
+  <si>
+    <t>P016</t>
+  </si>
+  <si>
+    <t>P017</t>
+  </si>
+  <si>
+    <t>P018</t>
+  </si>
+  <si>
+    <t>P019</t>
+  </si>
+  <si>
+    <t>P020</t>
+  </si>
+  <si>
+    <t>Cost/Unit</t>
+  </si>
+  <si>
+    <t>Reorder Level</t>
+  </si>
+  <si>
+    <t>Supplier</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Industrial Safety Gloves</t>
+  </si>
+  <si>
+    <t>PPE</t>
+  </si>
+  <si>
+    <t>NorthStar Industrial Supply</t>
+  </si>
+  <si>
+    <t>Steel-Toe Work Boots</t>
+  </si>
+  <si>
+    <t>ProSafe Equipment</t>
+  </si>
+  <si>
+    <t>Safety Glasses</t>
+  </si>
+  <si>
+    <t>Guardian Safety Products</t>
+  </si>
+  <si>
+    <t>High-Visibility Safety Vest</t>
+  </si>
+  <si>
+    <t>WorkShield Canada</t>
+  </si>
+  <si>
+    <t>Hard Hat - Yellow</t>
+  </si>
+  <si>
+    <t>Ear Protection Earmuffs</t>
+  </si>
+  <si>
+    <t>Disposable Dust Mask</t>
+  </si>
+  <si>
+    <t>Cut-Resistant Gloves</t>
+  </si>
+  <si>
+    <t>Aluminum Step Ladder</t>
+  </si>
+  <si>
+    <t>Warehouse Equipment</t>
+  </si>
+  <si>
+    <t>Maple Industrial Supply</t>
+  </si>
+  <si>
+    <t>Platform Hand Truck</t>
+  </si>
+  <si>
+    <t>Material Handling</t>
+  </si>
+  <si>
+    <t>Northern Material Handling</t>
+  </si>
+  <si>
+    <t>Heavy-Duty Pallet Jack</t>
+  </si>
+  <si>
+    <t>Warehouse Solutions Inc.</t>
+  </si>
+  <si>
+    <t>Steel Storage Bin</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Plastic Parts Bin</t>
+  </si>
+  <si>
+    <t>StoragePro Canada</t>
+  </si>
+  <si>
+    <t>Wire Shelving Unit</t>
+  </si>
+  <si>
+    <t>Mobile Storage Cart</t>
+  </si>
+  <si>
+    <t>Plastic Tote - 27 Gallon</t>
+  </si>
+  <si>
+    <t>Corrugated Shipping Box - Small</t>
+  </si>
+  <si>
+    <t>Packaging</t>
+  </si>
+  <si>
+    <t>PackRight Solutions</t>
+  </si>
+  <si>
+    <t>Corrugated Shipping Box - Medium</t>
+  </si>
+  <si>
+    <t>Corrugated Shipping Box - Large</t>
+  </si>
+  <si>
+    <t>BoxWorks Canada</t>
+  </si>
+  <si>
+    <t>Stretch Wrap Roll</t>
+  </si>
+  <si>
+    <t>Bubble Wrap Roll</t>
+  </si>
+  <si>
+    <t>Packaging Plus</t>
+  </si>
+  <si>
+    <t>Packing Tape - Clear</t>
+  </si>
+  <si>
+    <t>Heavy-Duty Strapping</t>
+  </si>
+  <si>
+    <t>Shipping Labels - 4x6</t>
+  </si>
+  <si>
+    <t>LabelPro Canada</t>
+  </si>
+  <si>
+    <t>Barcode Label Roll</t>
+  </si>
+  <si>
+    <t>Inventory Supplies</t>
+  </si>
+  <si>
+    <t>Thermal Printer Labels</t>
+  </si>
+  <si>
+    <t>PrintSupply Solutions</t>
+  </si>
+  <si>
+    <t>Permanent Marker - Black</t>
+  </si>
+  <si>
+    <t>Office Supplies</t>
+  </si>
+  <si>
+    <t>Grand Office Supply</t>
+  </si>
+  <si>
+    <t>Clipboard - Plastic</t>
+  </si>
+  <si>
+    <t>Warehouse Clipboard</t>
+  </si>
+  <si>
+    <t>OfficeSource Canada</t>
+  </si>
+  <si>
+    <t>Inventory Count Sheets</t>
+  </si>
+  <si>
+    <t>RF Barcode Scanner</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>ScanTech Solutions</t>
+  </si>
+  <si>
+    <t>USB Barcode Scanner</t>
+  </si>
+  <si>
+    <t>Wireless Keyboard</t>
+  </si>
+  <si>
+    <t>TechSource Canada</t>
+  </si>
+  <si>
+    <t>Wireless Mouse</t>
+  </si>
+  <si>
+    <t>Industrial Tablet</t>
+  </si>
+  <si>
+    <t>WarehouseTech Inc.</t>
+  </si>
+  <si>
+    <t>Ethernet Cable - 10ft</t>
+  </si>
+  <si>
+    <t>Network Supply Co.</t>
+  </si>
+  <si>
+    <t>Label Printer</t>
+  </si>
+  <si>
+    <t>Portable Work Light</t>
+  </si>
+  <si>
+    <t>Tools &amp; Equipment</t>
+  </si>
+  <si>
+    <t>ToolPro Canada</t>
+  </si>
+  <si>
+    <t>Cordless Drill</t>
+  </si>
+  <si>
+    <t>Adjustable Wrench</t>
+  </si>
+  <si>
+    <t>Canadian Tool Supply</t>
+  </si>
+  <si>
+    <t>Socket Set - 40 Piece</t>
+  </si>
+  <si>
+    <t>Screwdriver Set</t>
+  </si>
+  <si>
+    <t>Utility Knife</t>
+  </si>
+  <si>
+    <t>Industrial Tool Depot</t>
+  </si>
+  <si>
+    <t>Replacement Utility Blades</t>
+  </si>
+  <si>
+    <t>Measuring Tape - 25ft</t>
+  </si>
+  <si>
+    <t>Machine Lubricant</t>
+  </si>
+  <si>
+    <t>Maintenance Supplies</t>
+  </si>
+  <si>
+    <t>Industrial Maintenance Co.</t>
+  </si>
+  <si>
+    <t>Multi-Purpose Grease</t>
+  </si>
+  <si>
+    <t>Hydraulic Oil - 5L</t>
+  </si>
+  <si>
+    <t>FluidTech Canada</t>
+  </si>
+  <si>
+    <t>Industrial Cleaner</t>
+  </si>
+  <si>
+    <t>CleanTech Supply</t>
+  </si>
+  <si>
+    <t>Degreaser - 4L</t>
+  </si>
+  <si>
+    <t>Absorbent Spill Pads</t>
+  </si>
+  <si>
+    <t>SafetyFirst Canada</t>
+  </si>
+  <si>
+    <t>Oil Absorbent Granules</t>
+  </si>
+  <si>
+    <t>Replacement Air Filter</t>
+  </si>
+  <si>
+    <t>Maintenance Parts</t>
+  </si>
+  <si>
+    <t>FilterSource Canada</t>
+  </si>
+  <si>
+    <t>Hydraulic Filter</t>
+  </si>
+  <si>
+    <t>Conveyor Belt - 10ft</t>
+  </si>
+  <si>
+    <t>Conveyor Solutions Inc.</t>
+  </si>
+  <si>
+    <t>Roller Bearing - 6205</t>
+  </si>
+  <si>
+    <t>Bearing Supply Canada</t>
+  </si>
+  <si>
+    <t>Steel Fasteners - M8</t>
+  </si>
+  <si>
+    <t>Hardware</t>
+  </si>
+  <si>
+    <t>FastenRight Canada</t>
+  </si>
+  <si>
+    <t>Hex Bolts - M10</t>
+  </si>
+  <si>
+    <t>Stainless Steel Nuts</t>
+  </si>
+  <si>
+    <t>HardwareSource Inc.</t>
+  </si>
+  <si>
+    <t>Flat Washers - M10</t>
+  </si>
+  <si>
+    <t>P021</t>
+  </si>
+  <si>
+    <t>P022</t>
+  </si>
+  <si>
+    <t>P023</t>
+  </si>
+  <si>
+    <t>P024</t>
+  </si>
+  <si>
+    <t>P025</t>
+  </si>
+  <si>
+    <t>P026</t>
+  </si>
+  <si>
+    <t>P027</t>
+  </si>
+  <si>
+    <t>P028</t>
+  </si>
+  <si>
+    <t>P029</t>
+  </si>
+  <si>
+    <t>P030</t>
+  </si>
+  <si>
+    <t>P031</t>
+  </si>
+  <si>
+    <t>P032</t>
+  </si>
+  <si>
+    <t>P033</t>
+  </si>
+  <si>
+    <t>P034</t>
+  </si>
+  <si>
+    <t>P035</t>
+  </si>
+  <si>
+    <t>P036</t>
+  </si>
+  <si>
+    <t>P037</t>
+  </si>
+  <si>
+    <t>P038</t>
+  </si>
+  <si>
+    <t>P039</t>
+  </si>
+  <si>
+    <t>P040</t>
+  </si>
+  <si>
+    <t>P041</t>
+  </si>
+  <si>
+    <t>P042</t>
+  </si>
+  <si>
+    <t>P043</t>
+  </si>
+  <si>
+    <t>P044</t>
+  </si>
+  <si>
+    <t>P045</t>
+  </si>
+  <si>
+    <t>P046</t>
+  </si>
+  <si>
+    <t>P047</t>
+  </si>
+  <si>
+    <t>P048</t>
+  </si>
+  <si>
+    <t>P049</t>
+  </si>
+  <si>
+    <t>P050</t>
+  </si>
+  <si>
+    <t>P051</t>
+  </si>
+  <si>
+    <t>P052</t>
+  </si>
+  <si>
+    <t>P053</t>
+  </si>
+  <si>
+    <t>P054</t>
+  </si>
+  <si>
+    <t>P055</t>
+  </si>
+  <si>
+    <t>P056</t>
+  </si>
+  <si>
+    <t>P057</t>
+  </si>
+  <si>
+    <t>P058</t>
+  </si>
+  <si>
+    <t>P059</t>
+  </si>
+  <si>
+    <t>P060</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00;\-&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="164" formatCode="mmm/dd"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,6 +795,27 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -475,10 +1008,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -668,11 +1207,83 @@
     <xf numFmtId="7" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="4"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="4" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="3" xfId="4" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="7">
+    <cellStyle name="Comma 2" xfId="2" xr:uid="{72D35A1C-E0E1-4D48-ACA5-2713C7D76C54}"/>
+    <cellStyle name="Currency 2" xfId="3" xr:uid="{5FCDA341-36C1-44C8-A84F-DD4220D7588E}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{4F19D639-9EDA-4ED7-894B-95E892051C00}"/>
+    <cellStyle name="Normal 3" xfId="4" xr:uid="{EB00786D-1BFA-4FE2-9C94-0F83B3ABD247}"/>
+    <cellStyle name="Normal 4" xfId="5" xr:uid="{EE3DB81E-1F5E-40AE-96F3-E9492D96486F}"/>
+    <cellStyle name="Normal 5" xfId="6" xr:uid="{B7B71ECD-932F-4B2C-AEDB-A565C2663224}"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1198,23 +1809,38 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="C4:Q31" totalsRowCount="1">
   <autoFilter ref="C4:Q30" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" totalsRowLabel="Total" totalsRowDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMPANIES" totalsRowDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NUMBER OF EMPLOYEES" totalsRowDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COLOR" totalsRowDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LAUNCH DATE" totalsRowDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="QUANTITY" totalsRowFunction="sum" totalsRowDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PRICE" totalsRowFunction="sum" totalsRowDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AMOUNT" totalsRowFunction="sum" totalsRowDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="QUANTITY " totalsRowDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRICE " totalsRowDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="AMOUNT " totalsRowFunction="sum" totalsRowDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QUANTITY  " totalsRowDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="PRICE  " totalsRowDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="AMOUNT  " totalsRowFunction="sum" totalsRowDxfId="1"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="TOTAL" totalsRowFunction="sum" totalsRowDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" totalsRowLabel="Total" totalsRowDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMPANIES" totalsRowDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NUMBER OF EMPLOYEES" totalsRowDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COLOR" totalsRowDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LAUNCH DATE" totalsRowDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="QUANTITY" totalsRowFunction="sum" totalsRowDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PRICE" totalsRowFunction="sum" totalsRowDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AMOUNT" totalsRowFunction="sum" totalsRowDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="QUANTITY " totalsRowDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRICE " totalsRowDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="AMOUNT " totalsRowFunction="sum" totalsRowDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QUANTITY  " totalsRowDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="PRICE  " totalsRowDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="AMOUNT  " totalsRowFunction="sum" totalsRowDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="TOTAL" totalsRowFunction="sum" totalsRowDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}" name="Products" displayName="Products" ref="A1:F61" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:F61" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{E8F4DFB0-EC56-4CBF-9F8C-23EDCA50F713}" name="ProductID" dataCellStyle="Normal 3"/>
+    <tableColumn id="2" xr3:uid="{01A2DB73-B8C2-4A45-A7CC-94CB4A4A2FEF}" name="Product Name" dataDxfId="4" dataCellStyle="Comma 2"/>
+    <tableColumn id="3" xr3:uid="{D7712E33-EC2C-4BBC-9183-D4083230AE51}" name="Category" dataCellStyle="Normal 3"/>
+    <tableColumn id="4" xr3:uid="{10280736-93EE-4A73-97B0-1F59FABAB46F}" name="Cost/Unit" dataDxfId="3" dataCellStyle="Comma 2"/>
+    <tableColumn id="5" xr3:uid="{AC22B57B-F391-4278-9CEA-6381C3C7599A}" name="Reorder Level" dataDxfId="2" dataCellStyle="Normal 3"/>
+    <tableColumn id="6" xr3:uid="{ECE3A126-A7F6-4E8A-B4CA-AC1B78868DAB}" name="Supplier" dataDxfId="1" dataCellStyle="Normal 3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -3463,9 +4089,1303 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.06640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="15.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="65" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A1" s="65" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="65" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="65" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="65" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="65" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="65" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="66" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="68">
+        <v>12.5</v>
+      </c>
+      <c r="E2" s="68" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="66" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="68"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="66" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="70" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="68">
+        <v>85</v>
+      </c>
+      <c r="E3" s="69">
+        <v>50</v>
+      </c>
+      <c r="F3" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="68"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="66" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="70" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="68">
+        <v>4.25</v>
+      </c>
+      <c r="E4" s="69">
+        <v>15</v>
+      </c>
+      <c r="F4" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="68"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="68">
+        <v>9.75</v>
+      </c>
+      <c r="E5" s="69">
+        <v>25</v>
+      </c>
+      <c r="F5" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="G5" s="68"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="66" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="70" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="68">
+        <v>14.5</v>
+      </c>
+      <c r="E6" s="69">
+        <v>30</v>
+      </c>
+      <c r="F6" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="68"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="70" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="68">
+        <v>18</v>
+      </c>
+      <c r="E7" s="69">
+        <v>20</v>
+      </c>
+      <c r="F7" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="68"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="70" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="68">
+        <v>6.25</v>
+      </c>
+      <c r="E8" s="69">
+        <v>15</v>
+      </c>
+      <c r="F8" s="66" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="68"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="66" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="70" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="68">
+        <v>11.5</v>
+      </c>
+      <c r="E9" s="69">
+        <v>40</v>
+      </c>
+      <c r="F9" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="G9" s="68"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="70" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="66" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="68">
+        <v>89</v>
+      </c>
+      <c r="E10" s="69">
+        <v>25</v>
+      </c>
+      <c r="F10" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="68"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="70" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="66" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="68">
+        <v>125</v>
+      </c>
+      <c r="E11" s="69">
+        <v>5</v>
+      </c>
+      <c r="F11" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="G11" s="68"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="70" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="66" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="68">
+        <v>475</v>
+      </c>
+      <c r="E12" s="69">
+        <v>8</v>
+      </c>
+      <c r="F12" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="G12" s="68"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="70" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="66" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="68">
+        <v>18.75</v>
+      </c>
+      <c r="E13" s="69">
+        <v>3</v>
+      </c>
+      <c r="F13" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="68"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A14" s="66" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="70" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="66" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="68">
+        <v>6.5</v>
+      </c>
+      <c r="E14" s="69">
+        <v>20</v>
+      </c>
+      <c r="F14" s="66" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="68"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A15" s="66" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="70" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="66" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="68">
+        <v>145</v>
+      </c>
+      <c r="E15" s="69">
+        <v>30</v>
+      </c>
+      <c r="F15" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" s="68"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A16" s="66" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="66" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="68">
+        <v>95</v>
+      </c>
+      <c r="E16" s="69">
+        <v>5</v>
+      </c>
+      <c r="F16" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" s="68"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="66" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="68">
+        <v>22.5</v>
+      </c>
+      <c r="E17" s="69">
+        <v>8</v>
+      </c>
+      <c r="F17" s="66" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="68"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" s="66" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="70" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="68">
+        <v>1.25</v>
+      </c>
+      <c r="E18" s="69">
+        <v>15</v>
+      </c>
+      <c r="F18" s="66" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" s="68"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="68">
+        <v>2.1</v>
+      </c>
+      <c r="E19" s="69">
+        <v>100</v>
+      </c>
+      <c r="F19" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="G19" s="68"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20" s="66" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="70" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" s="68">
+        <v>3.75</v>
+      </c>
+      <c r="E20" s="69">
+        <v>100</v>
+      </c>
+      <c r="F20" s="66" t="s">
+        <v>119</v>
+      </c>
+      <c r="G20" s="68"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" s="66" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="70" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="68">
+        <v>18.5</v>
+      </c>
+      <c r="E21" s="69">
+        <v>75</v>
+      </c>
+      <c r="F21" s="66" t="s">
+        <v>116</v>
+      </c>
+      <c r="G21" s="68"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="B22" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" s="68">
+        <v>24</v>
+      </c>
+      <c r="E22" s="69">
+        <v>25</v>
+      </c>
+      <c r="F22" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="G22" s="68"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A23" s="66" t="s">
+        <v>190</v>
+      </c>
+      <c r="B23" s="70" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" s="68">
+        <v>4.75</v>
+      </c>
+      <c r="E23" s="69">
+        <v>30</v>
+      </c>
+      <c r="F23" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="G23" s="68"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" s="66" t="s">
+        <v>191</v>
+      </c>
+      <c r="B24" s="70" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" s="68">
+        <v>32</v>
+      </c>
+      <c r="E24" s="69">
+        <v>50</v>
+      </c>
+      <c r="F24" s="67" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="68"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A25" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="B25" s="70" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="68">
+        <v>15.5</v>
+      </c>
+      <c r="E25" s="69">
+        <v>20</v>
+      </c>
+      <c r="F25" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" s="68"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" s="66" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="D26" s="68">
+        <v>12.75</v>
+      </c>
+      <c r="E26" s="69">
+        <v>40</v>
+      </c>
+      <c r="F26" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="G26" s="68"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A27" s="66" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" s="70" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="68">
+        <v>28</v>
+      </c>
+      <c r="E27" s="69">
+        <v>25</v>
+      </c>
+      <c r="F27" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" s="68"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" s="66" t="s">
+        <v>195</v>
+      </c>
+      <c r="B28" s="70" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="66" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="68">
+        <v>1.5</v>
+      </c>
+      <c r="E28" s="69">
+        <v>20</v>
+      </c>
+      <c r="F28" s="67" t="s">
+        <v>133</v>
+      </c>
+      <c r="G28" s="68"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" s="66" t="s">
+        <v>196</v>
+      </c>
+      <c r="B29" s="70" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" s="66" t="s">
+        <v>132</v>
+      </c>
+      <c r="D29" s="68">
+        <v>8.25</v>
+      </c>
+      <c r="E29" s="69">
+        <v>50</v>
+      </c>
+      <c r="F29" s="67" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" s="68"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30" s="66" t="s">
+        <v>197</v>
+      </c>
+      <c r="B30" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" s="66" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" s="68">
+        <v>6.75</v>
+      </c>
+      <c r="E30" s="69">
+        <v>15</v>
+      </c>
+      <c r="F30" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="G30" s="68"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31" s="66" t="s">
+        <v>198</v>
+      </c>
+      <c r="B31" s="70" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" s="68">
+        <v>9.5</v>
+      </c>
+      <c r="E31" s="69">
+        <v>20</v>
+      </c>
+      <c r="F31" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="G31" s="68"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="B32" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="C32" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" s="68">
+        <v>325</v>
+      </c>
+      <c r="E32" s="69">
+        <v>30</v>
+      </c>
+      <c r="F32" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32" s="68"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A33" s="66" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" s="70" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="D33" s="68">
+        <v>85</v>
+      </c>
+      <c r="E33" s="69">
+        <v>5</v>
+      </c>
+      <c r="F33" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="G33" s="68"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A34" s="66" t="s">
+        <v>201</v>
+      </c>
+      <c r="B34" s="70" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="D34" s="68">
+        <v>42</v>
+      </c>
+      <c r="E34" s="69">
+        <v>10</v>
+      </c>
+      <c r="F34" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="G34" s="68"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A35" s="66" t="s">
+        <v>202</v>
+      </c>
+      <c r="B35" s="70" t="s">
+        <v>144</v>
+      </c>
+      <c r="C35" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="D35" s="68">
+        <v>28.5</v>
+      </c>
+      <c r="E35" s="69">
+        <v>10</v>
+      </c>
+      <c r="F35" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="G35" s="68"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A36" s="66" t="s">
+        <v>203</v>
+      </c>
+      <c r="B36" s="70" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="D36" s="68">
+        <v>675</v>
+      </c>
+      <c r="E36" s="69">
+        <v>10</v>
+      </c>
+      <c r="F36" s="67" t="s">
+        <v>146</v>
+      </c>
+      <c r="G36" s="68"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A37" s="66" t="s">
+        <v>204</v>
+      </c>
+      <c r="B37" s="70" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="D37" s="68">
+        <v>12.5</v>
+      </c>
+      <c r="E37" s="69">
+        <v>3</v>
+      </c>
+      <c r="F37" s="67" t="s">
+        <v>148</v>
+      </c>
+      <c r="G37" s="68"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A38" s="66" t="s">
+        <v>205</v>
+      </c>
+      <c r="B38" s="70" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="D38" s="68">
+        <v>285</v>
+      </c>
+      <c r="E38" s="69">
+        <v>25</v>
+      </c>
+      <c r="F38" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="G38" s="68"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A39" s="66" t="s">
+        <v>206</v>
+      </c>
+      <c r="B39" s="70" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="D39" s="68">
+        <v>45</v>
+      </c>
+      <c r="E39" s="69">
+        <v>5</v>
+      </c>
+      <c r="F39" s="67" t="s">
+        <v>152</v>
+      </c>
+      <c r="G39" s="68"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A40" s="66" t="s">
+        <v>207</v>
+      </c>
+      <c r="B40" s="70" t="s">
+        <v>153</v>
+      </c>
+      <c r="C40" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="D40" s="68">
+        <v>165</v>
+      </c>
+      <c r="E40" s="69">
+        <v>10</v>
+      </c>
+      <c r="F40" s="67" t="s">
+        <v>152</v>
+      </c>
+      <c r="G40" s="68"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A41" s="66" t="s">
+        <v>208</v>
+      </c>
+      <c r="B41" s="70" t="s">
+        <v>154</v>
+      </c>
+      <c r="C41" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="D41" s="68">
+        <v>24.5</v>
+      </c>
+      <c r="E41" s="69">
+        <v>5</v>
+      </c>
+      <c r="F41" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="G41" s="68"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A42" s="66" t="s">
+        <v>209</v>
+      </c>
+      <c r="B42" s="70" t="s">
+        <v>156</v>
+      </c>
+      <c r="C42" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="D42" s="68">
+        <v>78</v>
+      </c>
+      <c r="E42" s="69">
+        <v>15</v>
+      </c>
+      <c r="F42" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="G42" s="68"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A43" s="66" t="s">
+        <v>210</v>
+      </c>
+      <c r="B43" s="70" t="s">
+        <v>157</v>
+      </c>
+      <c r="C43" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="D43" s="68">
+        <v>32</v>
+      </c>
+      <c r="E43" s="69">
+        <v>8</v>
+      </c>
+      <c r="F43" s="67" t="s">
+        <v>152</v>
+      </c>
+      <c r="G43" s="68"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A44" s="66" t="s">
+        <v>211</v>
+      </c>
+      <c r="B44" s="70" t="s">
+        <v>158</v>
+      </c>
+      <c r="C44" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="D44" s="68">
+        <v>12.75</v>
+      </c>
+      <c r="E44" s="69">
+        <v>10</v>
+      </c>
+      <c r="F44" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="G44" s="68"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A45" s="66" t="s">
+        <v>212</v>
+      </c>
+      <c r="B45" s="70" t="s">
+        <v>160</v>
+      </c>
+      <c r="C45" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="D45" s="68">
+        <v>18.5</v>
+      </c>
+      <c r="E45" s="69">
+        <v>25</v>
+      </c>
+      <c r="F45" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="G45" s="68"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A46" s="66" t="s">
+        <v>213</v>
+      </c>
+      <c r="B46" s="70" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="D46" s="68">
+        <v>22</v>
+      </c>
+      <c r="E46" s="69">
+        <v>30</v>
+      </c>
+      <c r="F46" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="G46" s="68"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A47" s="66" t="s">
+        <v>214</v>
+      </c>
+      <c r="B47" s="70" t="s">
+        <v>162</v>
+      </c>
+      <c r="C47" s="66" t="s">
+        <v>163</v>
+      </c>
+      <c r="D47" s="68">
+        <v>18.75</v>
+      </c>
+      <c r="E47" s="69">
+        <v>10</v>
+      </c>
+      <c r="F47" s="67" t="s">
+        <v>164</v>
+      </c>
+      <c r="G47" s="68"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A48" s="66" t="s">
+        <v>215</v>
+      </c>
+      <c r="B48" s="70" t="s">
+        <v>165</v>
+      </c>
+      <c r="C48" s="66" t="s">
+        <v>163</v>
+      </c>
+      <c r="D48" s="68">
+        <v>24.5</v>
+      </c>
+      <c r="E48" s="69">
+        <v>15</v>
+      </c>
+      <c r="F48" s="67" t="s">
+        <v>164</v>
+      </c>
+      <c r="G48" s="68"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A49" s="66" t="s">
+        <v>216</v>
+      </c>
+      <c r="B49" s="70" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" s="66" t="s">
+        <v>163</v>
+      </c>
+      <c r="D49" s="68">
+        <v>42</v>
+      </c>
+      <c r="E49" s="69">
+        <v>20</v>
+      </c>
+      <c r="F49" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="G49" s="68"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" s="66" t="s">
+        <v>217</v>
+      </c>
+      <c r="B50" s="70" t="s">
+        <v>168</v>
+      </c>
+      <c r="C50" s="66" t="s">
+        <v>163</v>
+      </c>
+      <c r="D50" s="68">
+        <v>35</v>
+      </c>
+      <c r="E50" s="69">
+        <v>10</v>
+      </c>
+      <c r="F50" s="67" t="s">
+        <v>169</v>
+      </c>
+      <c r="G50" s="68"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A51" s="66" t="s">
+        <v>218</v>
+      </c>
+      <c r="B51" s="70" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51" s="66" t="s">
+        <v>163</v>
+      </c>
+      <c r="D51" s="68">
+        <v>28.5</v>
+      </c>
+      <c r="E51" s="69">
+        <v>15</v>
+      </c>
+      <c r="F51" s="67" t="s">
+        <v>169</v>
+      </c>
+      <c r="G51" s="68"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A52" s="66" t="s">
+        <v>219</v>
+      </c>
+      <c r="B52" s="70" t="s">
+        <v>171</v>
+      </c>
+      <c r="C52" s="66" t="s">
+        <v>163</v>
+      </c>
+      <c r="D52" s="68">
+        <v>19.75</v>
+      </c>
+      <c r="E52" s="69">
+        <v>10</v>
+      </c>
+      <c r="F52" s="67" t="s">
+        <v>172</v>
+      </c>
+      <c r="G52" s="68"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A53" s="66" t="s">
+        <v>220</v>
+      </c>
+      <c r="B53" s="70" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" s="66" t="s">
+        <v>163</v>
+      </c>
+      <c r="D53" s="68">
+        <v>16.5</v>
+      </c>
+      <c r="E53" s="69">
+        <v>25</v>
+      </c>
+      <c r="F53" s="67" t="s">
+        <v>172</v>
+      </c>
+      <c r="G53" s="68"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A54" s="66" t="s">
+        <v>221</v>
+      </c>
+      <c r="B54" s="70" t="s">
+        <v>174</v>
+      </c>
+      <c r="C54" s="66" t="s">
+        <v>175</v>
+      </c>
+      <c r="D54" s="68">
+        <v>45</v>
+      </c>
+      <c r="E54" s="69">
+        <v>20</v>
+      </c>
+      <c r="F54" s="67" t="s">
+        <v>176</v>
+      </c>
+      <c r="G54" s="68"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A55" s="66" t="s">
+        <v>222</v>
+      </c>
+      <c r="B55" s="70" t="s">
+        <v>177</v>
+      </c>
+      <c r="C55" s="66" t="s">
+        <v>175</v>
+      </c>
+      <c r="D55" s="68">
+        <v>185</v>
+      </c>
+      <c r="E55" s="69">
+        <v>10</v>
+      </c>
+      <c r="F55" s="67" t="s">
+        <v>176</v>
+      </c>
+      <c r="G55" s="68"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A56" s="66" t="s">
+        <v>223</v>
+      </c>
+      <c r="B56" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="C56" s="66" t="s">
+        <v>175</v>
+      </c>
+      <c r="D56" s="68">
+        <v>38.5</v>
+      </c>
+      <c r="E56" s="69">
+        <v>5</v>
+      </c>
+      <c r="F56" s="67" t="s">
+        <v>179</v>
+      </c>
+      <c r="G56" s="68"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A57" s="66" t="s">
+        <v>224</v>
+      </c>
+      <c r="B57" s="70" t="s">
+        <v>180</v>
+      </c>
+      <c r="C57" s="66" t="s">
+        <v>175</v>
+      </c>
+      <c r="D57" s="68">
+        <v>0.18</v>
+      </c>
+      <c r="E57" s="69">
+        <v>15</v>
+      </c>
+      <c r="F57" s="67" t="s">
+        <v>181</v>
+      </c>
+      <c r="G57" s="68"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A58" s="66" t="s">
+        <v>225</v>
+      </c>
+      <c r="B58" s="70" t="s">
+        <v>182</v>
+      </c>
+      <c r="C58" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="D58" s="68">
+        <v>0.25</v>
+      </c>
+      <c r="E58" s="69">
+        <v>100</v>
+      </c>
+      <c r="F58" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="G58" s="68"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A59" s="66" t="s">
+        <v>226</v>
+      </c>
+      <c r="B59" s="70" t="s">
+        <v>185</v>
+      </c>
+      <c r="C59" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="D59" s="68">
+        <v>0.15</v>
+      </c>
+      <c r="E59" s="69">
+        <v>100</v>
+      </c>
+      <c r="F59" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="G59" s="68"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A60" s="66" t="s">
+        <v>227</v>
+      </c>
+      <c r="B60" s="70" t="s">
+        <v>186</v>
+      </c>
+      <c r="C60" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="D60" s="68">
+        <v>0.12</v>
+      </c>
+      <c r="E60" s="69">
+        <v>100</v>
+      </c>
+      <c r="F60" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="G60" s="68"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A61" s="66" t="s">
+        <v>228</v>
+      </c>
+      <c r="B61" s="70" t="s">
+        <v>188</v>
+      </c>
+      <c r="C61" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="D61">
+        <v>8.5</v>
+      </c>
+      <c r="E61" s="69">
+        <v>100</v>
+      </c>
+      <c r="F61" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="G61" s="68"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/DataAnalyst.xlsx
+++ b/DataAnalyst.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malik\OneDrive\Documents\Data\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68258BC7-63FF-4AB6-925A-834993375F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2A9D38-99A3-4E6A-A65B-CA57F4A6A1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21720" yWindow="-9015" windowWidth="21840" windowHeight="13740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="creatingtable" sheetId="2" r:id="rId2"/>
-    <sheet name="InventorySys" sheetId="3" r:id="rId3"/>
+    <sheet name="Products" sheetId="3" r:id="rId3"/>
+    <sheet name="Transactions" sheetId="4" r:id="rId4"/>
+    <sheet name="Inventory Sheet" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="ProductList">Products[ProductID]</definedName>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="304">
   <si>
     <t>ELECTRONICS COMPANIES REPORT Q1 2023</t>
   </si>
@@ -226,9 +228,18 @@
     <t>Product Name</t>
   </si>
   <si>
+    <t>Store A</t>
+  </si>
+  <si>
     <t>P001</t>
   </si>
   <si>
+    <t>Store B</t>
+  </si>
+  <si>
+    <t>Store C</t>
+  </si>
+  <si>
     <t>P002</t>
   </si>
   <si>
@@ -286,12 +297,30 @@
     <t>P020</t>
   </si>
   <si>
+    <t>Site</t>
+  </si>
+  <si>
     <t>Cost/Unit</t>
   </si>
   <si>
     <t>Reorder Level</t>
   </si>
   <si>
+    <t>QuantityOnHand</t>
+  </si>
+  <si>
+    <t>Stock Value</t>
+  </si>
+  <si>
+    <t>Reorder</t>
+  </si>
+  <si>
+    <t>Order Date</t>
+  </si>
+  <si>
+    <t>Product Description</t>
+  </si>
+  <si>
     <t>Supplier</t>
   </si>
   <si>
@@ -725,6 +754,204 @@
   </si>
   <si>
     <t>P060</t>
+  </si>
+  <si>
+    <t>TransID</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>T001</t>
+  </si>
+  <si>
+    <t>T002</t>
+  </si>
+  <si>
+    <t>T003</t>
+  </si>
+  <si>
+    <t>T004</t>
+  </si>
+  <si>
+    <t>T005</t>
+  </si>
+  <si>
+    <t>T006</t>
+  </si>
+  <si>
+    <t>T007</t>
+  </si>
+  <si>
+    <t>T008</t>
+  </si>
+  <si>
+    <t>T009</t>
+  </si>
+  <si>
+    <t>T010</t>
+  </si>
+  <si>
+    <t>T011</t>
+  </si>
+  <si>
+    <t>T012</t>
+  </si>
+  <si>
+    <t>T013</t>
+  </si>
+  <si>
+    <t>T014</t>
+  </si>
+  <si>
+    <t>T015</t>
+  </si>
+  <si>
+    <t>T016</t>
+  </si>
+  <si>
+    <t>T017</t>
+  </si>
+  <si>
+    <t>T018</t>
+  </si>
+  <si>
+    <t>T019</t>
+  </si>
+  <si>
+    <t>T020</t>
+  </si>
+  <si>
+    <t>T021</t>
+  </si>
+  <si>
+    <t>T022</t>
+  </si>
+  <si>
+    <t>T023</t>
+  </si>
+  <si>
+    <t>T024</t>
+  </si>
+  <si>
+    <t>T025</t>
+  </si>
+  <si>
+    <t>T026</t>
+  </si>
+  <si>
+    <t>T027</t>
+  </si>
+  <si>
+    <t>T028</t>
+  </si>
+  <si>
+    <t>T029</t>
+  </si>
+  <si>
+    <t>T030</t>
+  </si>
+  <si>
+    <t>T031</t>
+  </si>
+  <si>
+    <t>T032</t>
+  </si>
+  <si>
+    <t>T033</t>
+  </si>
+  <si>
+    <t>T034</t>
+  </si>
+  <si>
+    <t>T035</t>
+  </si>
+  <si>
+    <t>T036</t>
+  </si>
+  <si>
+    <t>T037</t>
+  </si>
+  <si>
+    <t>T038</t>
+  </si>
+  <si>
+    <t>T039</t>
+  </si>
+  <si>
+    <t>T040</t>
+  </si>
+  <si>
+    <t>T041</t>
+  </si>
+  <si>
+    <t>T042</t>
+  </si>
+  <si>
+    <t>T043</t>
+  </si>
+  <si>
+    <t>T044</t>
+  </si>
+  <si>
+    <t>T045</t>
+  </si>
+  <si>
+    <t>T046</t>
+  </si>
+  <si>
+    <t>T047</t>
+  </si>
+  <si>
+    <t>T048</t>
+  </si>
+  <si>
+    <t>T049</t>
+  </si>
+  <si>
+    <t>T050</t>
+  </si>
+  <si>
+    <t>T051</t>
+  </si>
+  <si>
+    <t>T052</t>
+  </si>
+  <si>
+    <t>T053</t>
+  </si>
+  <si>
+    <t>T054</t>
+  </si>
+  <si>
+    <t>T055</t>
+  </si>
+  <si>
+    <t>T056</t>
+  </si>
+  <si>
+    <t>T057</t>
+  </si>
+  <si>
+    <t>T058</t>
+  </si>
+  <si>
+    <t>T059</t>
+  </si>
+  <si>
+    <t>T060</t>
+  </si>
+  <si>
+    <t>Opening Stock</t>
+  </si>
+  <si>
+    <t>Sale</t>
+  </si>
+  <si>
+    <t>Receipt</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1235,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1016,8 +1243,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1213,8 +1444,23 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1"/>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="3" xfId="4" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="7" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="9"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="9" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="8" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="10"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="11">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{72D35A1C-E0E1-4D48-ACA5-2713C7D76C54}"/>
     <cellStyle name="Currency 2" xfId="3" xr:uid="{5FCDA341-36C1-44C8-A84F-DD4220D7588E}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1222,8 +1468,21 @@
     <cellStyle name="Normal 3" xfId="4" xr:uid="{EB00786D-1BFA-4FE2-9C94-0F83B3ABD247}"/>
     <cellStyle name="Normal 4" xfId="5" xr:uid="{EE3DB81E-1F5E-40AE-96F3-E9492D96486F}"/>
     <cellStyle name="Normal 5" xfId="6" xr:uid="{B7B71ECD-932F-4B2C-AEDB-A565C2663224}"/>
+    <cellStyle name="Normal 6" xfId="7" xr:uid="{EE61153F-2D20-41FC-881C-0DE085562B8B}"/>
+    <cellStyle name="Normal 7" xfId="8" xr:uid="{7515CE29-CEE9-4E05-A649-1306565DAB80}"/>
+    <cellStyle name="Normal 8" xfId="9" xr:uid="{0EFC0AAE-EB0E-4FA2-885A-2DA2EB3F3608}"/>
+    <cellStyle name="Normal 9" xfId="10" xr:uid="{DFABB175-7506-410D-8AC4-26F83CE150B7}"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="23">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1809,36 +2068,51 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="C4:Q31" totalsRowCount="1">
   <autoFilter ref="C4:Q30" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" totalsRowLabel="Total" totalsRowDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMPANIES" totalsRowDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NUMBER OF EMPLOYEES" totalsRowDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COLOR" totalsRowDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LAUNCH DATE" totalsRowDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="QUANTITY" totalsRowFunction="sum" totalsRowDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PRICE" totalsRowFunction="sum" totalsRowDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AMOUNT" totalsRowFunction="sum" totalsRowDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="QUANTITY " totalsRowDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRICE " totalsRowDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="AMOUNT " totalsRowFunction="sum" totalsRowDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QUANTITY  " totalsRowDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="PRICE  " totalsRowDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="AMOUNT  " totalsRowFunction="sum" totalsRowDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="TOTAL" totalsRowFunction="sum" totalsRowDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" totalsRowLabel="Total" totalsRowDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMPANIES" totalsRowDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NUMBER OF EMPLOYEES" totalsRowDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COLOR" totalsRowDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LAUNCH DATE" totalsRowDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="QUANTITY" totalsRowFunction="sum" totalsRowDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PRICE" totalsRowFunction="sum" totalsRowDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AMOUNT" totalsRowFunction="sum" totalsRowDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="QUANTITY " totalsRowDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRICE " totalsRowDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="AMOUNT " totalsRowFunction="sum" totalsRowDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QUANTITY  " totalsRowDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="PRICE  " totalsRowDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="AMOUNT  " totalsRowFunction="sum" totalsRowDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="TOTAL" totalsRowFunction="sum" totalsRowDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}" name="Products" displayName="Products" ref="A1:F61" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}" name="Products" displayName="Products" ref="A1:F61" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="A1:F61" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{E8F4DFB0-EC56-4CBF-9F8C-23EDCA50F713}" name="ProductID" dataCellStyle="Normal 3"/>
-    <tableColumn id="2" xr3:uid="{01A2DB73-B8C2-4A45-A7CC-94CB4A4A2FEF}" name="Product Name" dataDxfId="4" dataCellStyle="Comma 2"/>
+    <tableColumn id="2" xr3:uid="{01A2DB73-B8C2-4A45-A7CC-94CB4A4A2FEF}" name="Product Name" dataDxfId="7" dataCellStyle="Comma 2"/>
     <tableColumn id="3" xr3:uid="{D7712E33-EC2C-4BBC-9183-D4083230AE51}" name="Category" dataCellStyle="Normal 3"/>
-    <tableColumn id="4" xr3:uid="{10280736-93EE-4A73-97B0-1F59FABAB46F}" name="Cost/Unit" dataDxfId="3" dataCellStyle="Comma 2"/>
-    <tableColumn id="5" xr3:uid="{AC22B57B-F391-4278-9CEA-6381C3C7599A}" name="Reorder Level" dataDxfId="2" dataCellStyle="Normal 3"/>
-    <tableColumn id="6" xr3:uid="{ECE3A126-A7F6-4E8A-B4CA-AC1B78868DAB}" name="Supplier" dataDxfId="1" dataCellStyle="Normal 3"/>
+    <tableColumn id="4" xr3:uid="{10280736-93EE-4A73-97B0-1F59FABAB46F}" name="Cost/Unit" dataDxfId="6" dataCellStyle="Comma 2"/>
+    <tableColumn id="5" xr3:uid="{AC22B57B-F391-4278-9CEA-6381C3C7599A}" name="Reorder Level" dataDxfId="5" dataCellStyle="Normal 3"/>
+    <tableColumn id="6" xr3:uid="{ECE3A126-A7F6-4E8A-B4CA-AC1B78868DAB}" name="Supplier" dataDxfId="4" dataCellStyle="Normal 3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03C4EC66-596A-4191-8AD5-8C56A2B0936F}" name="Transactions" displayName="Transactions" ref="A1:F61" totalsRowShown="0">
+  <autoFilter ref="A1:F61" xr:uid="{03C4EC66-596A-4191-8AD5-8C56A2B0936F}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{CF0FBA31-2E94-4135-8B0A-A8ADD4C1D54E}" name="TransID"/>
+    <tableColumn id="2" xr3:uid="{EB83FE89-2487-49C6-80BE-246C3764EFC8}" name="Date" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{FE85118D-4F73-4CC4-947F-D727DBCF045B}" name="ProductID"/>
+    <tableColumn id="4" xr3:uid="{890FE897-5C0E-4846-94E3-254F9AB59CC8}" name="Site" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{D5DF56AA-CF75-4D46-9133-AE66DE368857}" name="Quantity" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{8D0BBA31-EE38-4A83-9E89-796952F75830}" name="Type"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4109,48 +4383,48 @@
         <v>61</v>
       </c>
       <c r="C1" s="65" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D1" s="65" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E1" s="65" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F1" s="65" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B2" s="70" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C2" s="66" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D2" s="68">
         <v>12.5</v>
       </c>
       <c r="E2" s="68" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G2" s="68"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="66" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B3" s="70" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C3" s="66" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D3" s="68">
         <v>85</v>
@@ -4159,19 +4433,19 @@
         <v>50</v>
       </c>
       <c r="F3" s="66" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="66" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B4" s="70" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C4" s="66" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D4" s="68">
         <v>4.25</v>
@@ -4180,19 +4454,19 @@
         <v>15</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="G4" s="68"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="66" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B5" s="70" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C5" s="66" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D5" s="68">
         <v>9.75</v>
@@ -4201,19 +4475,19 @@
         <v>25</v>
       </c>
       <c r="F5" s="66" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="66" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" s="70" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C6" s="66" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D6" s="68">
         <v>14.5</v>
@@ -4222,19 +4496,19 @@
         <v>30</v>
       </c>
       <c r="F6" s="66" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="66" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B7" s="70" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="66" t="s">
         <v>96</v>
-      </c>
-      <c r="C7" s="66" t="s">
-        <v>87</v>
       </c>
       <c r="D7" s="68">
         <v>18</v>
@@ -4243,19 +4517,19 @@
         <v>20</v>
       </c>
       <c r="F7" s="67" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="G7" s="68"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="66" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B8" s="70" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C8" s="66" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D8" s="68">
         <v>6.25</v>
@@ -4264,19 +4538,19 @@
         <v>15</v>
       </c>
       <c r="F8" s="66" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G8" s="68"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="66" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B9" s="70" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D9" s="68">
         <v>11.5</v>
@@ -4285,19 +4559,19 @@
         <v>40</v>
       </c>
       <c r="F9" s="66" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G9" s="68"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="66" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B10" s="70" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C10" s="66" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D10" s="68">
         <v>89</v>
@@ -4306,19 +4580,19 @@
         <v>25</v>
       </c>
       <c r="F10" s="67" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G10" s="68"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="66" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B11" s="70" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C11" s="66" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D11" s="68">
         <v>125</v>
@@ -4327,19 +4601,19 @@
         <v>5</v>
       </c>
       <c r="F11" s="66" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="G11" s="68"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="66" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B12" s="70" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C12" s="66" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D12" s="68">
         <v>475</v>
@@ -4348,19 +4622,19 @@
         <v>8</v>
       </c>
       <c r="F12" s="67" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="G12" s="68"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="66" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B13" s="70" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C13" s="66" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D13" s="68">
         <v>18.75</v>
@@ -4369,19 +4643,19 @@
         <v>3</v>
       </c>
       <c r="F13" s="67" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G13" s="68"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="66" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C14" s="66" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D14" s="68">
         <v>6.5</v>
@@ -4390,19 +4664,19 @@
         <v>20</v>
       </c>
       <c r="F14" s="66" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G14" s="68"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="66" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B15" s="70" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D15" s="68">
         <v>145</v>
@@ -4411,19 +4685,19 @@
         <v>30</v>
       </c>
       <c r="F15" s="66" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="G15" s="68"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="66" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B16" s="70" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D16" s="68">
         <v>95</v>
@@ -4432,19 +4706,19 @@
         <v>5</v>
       </c>
       <c r="F16" s="66" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="G16" s="68"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="66" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B17" s="70" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C17" s="66" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D17" s="68">
         <v>22.5</v>
@@ -4453,19 +4727,19 @@
         <v>8</v>
       </c>
       <c r="F17" s="66" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G17" s="68"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="66" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B18" s="70" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C18" s="66" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D18" s="68">
         <v>1.25</v>
@@ -4474,19 +4748,19 @@
         <v>15</v>
       </c>
       <c r="F18" s="66" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G18" s="68"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="66" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B19" s="70" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C19" s="66" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D19" s="68">
         <v>2.1</v>
@@ -4495,19 +4769,19 @@
         <v>100</v>
       </c>
       <c r="F19" s="67" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G19" s="68"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="66" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B20" s="70" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C20" s="66" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D20" s="68">
         <v>3.75</v>
@@ -4516,19 +4790,19 @@
         <v>100</v>
       </c>
       <c r="F20" s="66" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="G20" s="68"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="66" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B21" s="70" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C21" s="66" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D21" s="68">
         <v>18.5</v>
@@ -4537,19 +4811,19 @@
         <v>75</v>
       </c>
       <c r="F21" s="66" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G21" s="68"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="66" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B22" s="70" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C22" s="66" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D22" s="68">
         <v>24</v>
@@ -4558,19 +4832,19 @@
         <v>25</v>
       </c>
       <c r="F22" s="67" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G22" s="68"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="66" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B23" s="70" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C23" s="66" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D23" s="68">
         <v>4.75</v>
@@ -4579,19 +4853,19 @@
         <v>30</v>
       </c>
       <c r="F23" s="67" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G23" s="68"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="66" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B24" s="70" t="s">
+        <v>133</v>
+      </c>
+      <c r="C24" s="66" t="s">
         <v>124</v>
-      </c>
-      <c r="C24" s="66" t="s">
-        <v>115</v>
       </c>
       <c r="D24" s="68">
         <v>32</v>
@@ -4600,19 +4874,19 @@
         <v>50</v>
       </c>
       <c r="F24" s="67" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="G24" s="68"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="66" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B25" s="70" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C25" s="66" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D25" s="68">
         <v>15.5</v>
@@ -4621,19 +4895,19 @@
         <v>20</v>
       </c>
       <c r="F25" s="67" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G25" s="68"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="66" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B26" s="70" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C26" s="66" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D26" s="68">
         <v>12.75</v>
@@ -4642,19 +4916,19 @@
         <v>40</v>
       </c>
       <c r="F26" s="67" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G26" s="68"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="66" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B27" s="70" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C27" s="66" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D27" s="68">
         <v>28</v>
@@ -4663,19 +4937,19 @@
         <v>25</v>
       </c>
       <c r="F27" s="67" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G27" s="68"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="66" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B28" s="70" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C28" s="66" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D28" s="68">
         <v>1.5</v>
@@ -4684,19 +4958,19 @@
         <v>20</v>
       </c>
       <c r="F28" s="67" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G28" s="68"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="66" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B29" s="70" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D29" s="68">
         <v>8.25</v>
@@ -4705,19 +4979,19 @@
         <v>50</v>
       </c>
       <c r="F29" s="67" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G29" s="68"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="66" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B30" s="70" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C30" s="66" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D30" s="68">
         <v>6.75</v>
@@ -4726,19 +5000,19 @@
         <v>15</v>
       </c>
       <c r="F30" s="67" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G30" s="68"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="66" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B31" s="70" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" s="66" t="s">
         <v>137</v>
-      </c>
-      <c r="C31" s="66" t="s">
-        <v>128</v>
       </c>
       <c r="D31" s="68">
         <v>9.5</v>
@@ -4747,19 +5021,19 @@
         <v>20</v>
       </c>
       <c r="F31" s="67" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G31" s="68"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="66" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B32" s="70" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C32" s="66" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D32" s="68">
         <v>325</v>
@@ -4768,19 +5042,19 @@
         <v>30</v>
       </c>
       <c r="F32" s="67" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="G32" s="68"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="66" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="B33" s="70" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C33" s="66" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D33" s="68">
         <v>85</v>
@@ -4789,19 +5063,19 @@
         <v>5</v>
       </c>
       <c r="F33" s="67" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="G33" s="68"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="66" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B34" s="70" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C34" s="66" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D34" s="68">
         <v>42</v>
@@ -4810,19 +5084,19 @@
         <v>10</v>
       </c>
       <c r="F34" s="67" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G34" s="68"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="66" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B35" s="70" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C35" s="66" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D35" s="68">
         <v>28.5</v>
@@ -4831,19 +5105,19 @@
         <v>10</v>
       </c>
       <c r="F35" s="67" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G35" s="68"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="66" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B36" s="70" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C36" s="66" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D36" s="68">
         <v>675</v>
@@ -4852,19 +5126,19 @@
         <v>10</v>
       </c>
       <c r="F36" s="67" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="G36" s="68"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="66" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B37" s="70" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C37" s="66" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D37" s="68">
         <v>12.5</v>
@@ -4873,19 +5147,19 @@
         <v>3</v>
       </c>
       <c r="F37" s="67" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="G37" s="68"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="66" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B38" s="70" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C38" s="66" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D38" s="68">
         <v>285</v>
@@ -4894,19 +5168,19 @@
         <v>25</v>
       </c>
       <c r="F38" s="67" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G38" s="68"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="66" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B39" s="70" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C39" s="66" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D39" s="68">
         <v>45</v>
@@ -4915,19 +5189,19 @@
         <v>5</v>
       </c>
       <c r="F39" s="67" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="G39" s="68"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" s="66" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B40" s="70" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="C40" s="66" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D40" s="68">
         <v>165</v>
@@ -4936,19 +5210,19 @@
         <v>10</v>
       </c>
       <c r="F40" s="67" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="G40" s="68"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" s="66" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B41" s="70" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C41" s="66" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D41" s="68">
         <v>24.5</v>
@@ -4957,19 +5231,19 @@
         <v>5</v>
       </c>
       <c r="F41" s="67" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G41" s="68"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" s="66" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B42" s="70" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C42" s="66" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D42" s="68">
         <v>78</v>
@@ -4978,19 +5252,19 @@
         <v>15</v>
       </c>
       <c r="F42" s="67" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G42" s="68"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" s="66" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B43" s="70" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C43" s="66" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D43" s="68">
         <v>32</v>
@@ -4999,19 +5273,19 @@
         <v>8</v>
       </c>
       <c r="F43" s="67" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="G43" s="68"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="66" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B44" s="70" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C44" s="66" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D44" s="68">
         <v>12.75</v>
@@ -5020,19 +5294,19 @@
         <v>10</v>
       </c>
       <c r="F44" s="67" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G44" s="68"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" s="66" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B45" s="70" t="s">
+        <v>169</v>
+      </c>
+      <c r="C45" s="66" t="s">
         <v>160</v>
-      </c>
-      <c r="C45" s="66" t="s">
-        <v>151</v>
       </c>
       <c r="D45" s="68">
         <v>18.5</v>
@@ -5041,19 +5315,19 @@
         <v>25</v>
       </c>
       <c r="F45" s="67" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G45" s="68"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" s="66" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B46" s="70" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C46" s="66" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D46" s="68">
         <v>22</v>
@@ -5062,19 +5336,19 @@
         <v>30</v>
       </c>
       <c r="F46" s="67" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G46" s="68"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" s="66" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B47" s="70" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C47" s="66" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D47" s="68">
         <v>18.75</v>
@@ -5083,19 +5357,19 @@
         <v>10</v>
       </c>
       <c r="F47" s="67" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="G47" s="68"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" s="66" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B48" s="70" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C48" s="66" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D48" s="68">
         <v>24.5</v>
@@ -5104,19 +5378,19 @@
         <v>15</v>
       </c>
       <c r="F48" s="67" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="G48" s="68"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" s="66" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B49" s="70" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="C49" s="66" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D49" s="68">
         <v>42</v>
@@ -5125,19 +5399,19 @@
         <v>20</v>
       </c>
       <c r="F49" s="67" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G49" s="68"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" s="66" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B50" s="70" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C50" s="66" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D50" s="68">
         <v>35</v>
@@ -5146,19 +5420,19 @@
         <v>10</v>
       </c>
       <c r="F50" s="67" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G50" s="68"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" s="66" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B51" s="70" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C51" s="66" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D51" s="68">
         <v>28.5</v>
@@ -5167,19 +5441,19 @@
         <v>15</v>
       </c>
       <c r="F51" s="67" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G51" s="68"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" s="66" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B52" s="70" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C52" s="66" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D52" s="68">
         <v>19.75</v>
@@ -5188,19 +5462,19 @@
         <v>10</v>
       </c>
       <c r="F52" s="67" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="G52" s="68"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" s="66" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B53" s="70" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C53" s="66" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D53" s="68">
         <v>16.5</v>
@@ -5209,19 +5483,19 @@
         <v>25</v>
       </c>
       <c r="F53" s="67" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="G53" s="68"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" s="66" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B54" s="70" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C54" s="66" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D54" s="68">
         <v>45</v>
@@ -5230,19 +5504,19 @@
         <v>20</v>
       </c>
       <c r="F54" s="67" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="G54" s="68"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" s="66" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B55" s="70" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C55" s="66" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D55" s="68">
         <v>185</v>
@@ -5251,19 +5525,19 @@
         <v>10</v>
       </c>
       <c r="F55" s="67" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="G55" s="68"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" s="66" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B56" s="70" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C56" s="66" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D56" s="68">
         <v>38.5</v>
@@ -5272,19 +5546,19 @@
         <v>5</v>
       </c>
       <c r="F56" s="67" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="G56" s="68"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" s="66" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B57" s="70" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C57" s="66" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D57" s="68">
         <v>0.18</v>
@@ -5293,19 +5567,19 @@
         <v>15</v>
       </c>
       <c r="F57" s="67" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="G57" s="68"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" s="66" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B58" s="70" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C58" s="66" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D58" s="68">
         <v>0.25</v>
@@ -5314,19 +5588,19 @@
         <v>100</v>
       </c>
       <c r="F58" s="67" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="G58" s="68"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" s="66" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B59" s="70" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C59" s="66" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D59" s="68">
         <v>0.15</v>
@@ -5335,19 +5609,19 @@
         <v>100</v>
       </c>
       <c r="F59" s="67" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="G59" s="68"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" s="66" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B60" s="70" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C60" s="66" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D60" s="68">
         <v>0.12</v>
@@ -5356,19 +5630,19 @@
         <v>100</v>
       </c>
       <c r="F60" s="67" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="G60" s="68"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" s="66" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B61" s="70" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C61" s="66" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D61">
         <v>8.5</v>
@@ -5377,7 +5651,7 @@
         <v>100</v>
       </c>
       <c r="F61" s="67" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="G61" s="68"/>
     </row>
@@ -5388,4 +5662,1292 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312D5D85-F04D-4F6D-9160-0486A4994C8D}">
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="9.9296875" customWidth="1"/>
+    <col min="3" max="3" width="10.9296875" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="73" customWidth="1"/>
+    <col min="5" max="5" width="12.46484375" style="73" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="73" t="s">
+        <v>240</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="74">
+        <v>50</v>
+      </c>
+      <c r="F2" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B3" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="74">
+        <v>30</v>
+      </c>
+      <c r="F3" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B4" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="74">
+        <v>40</v>
+      </c>
+      <c r="F4" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B5" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="74">
+        <v>12</v>
+      </c>
+      <c r="F5" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>245</v>
+      </c>
+      <c r="B6" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="74">
+        <v>20</v>
+      </c>
+      <c r="F6" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B7" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="74">
+        <v>14</v>
+      </c>
+      <c r="F7" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B8" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="74">
+        <v>25</v>
+      </c>
+      <c r="F8" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>248</v>
+      </c>
+      <c r="B9" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="74">
+        <v>30</v>
+      </c>
+      <c r="F9" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>249</v>
+      </c>
+      <c r="B10" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="74">
+        <v>10</v>
+      </c>
+      <c r="F10" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>250</v>
+      </c>
+      <c r="B11" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="74">
+        <v>35</v>
+      </c>
+      <c r="F11" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="74">
+        <v>25</v>
+      </c>
+      <c r="F12" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>252</v>
+      </c>
+      <c r="B13" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="74">
+        <v>18</v>
+      </c>
+      <c r="F13" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>253</v>
+      </c>
+      <c r="B14" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="74">
+        <v>60</v>
+      </c>
+      <c r="F14" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B15" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="74">
+        <v>50</v>
+      </c>
+      <c r="F15" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>255</v>
+      </c>
+      <c r="B16" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="74">
+        <v>35</v>
+      </c>
+      <c r="F16" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>256</v>
+      </c>
+      <c r="B17" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="74">
+        <v>20</v>
+      </c>
+      <c r="F17" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>257</v>
+      </c>
+      <c r="B18" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="74">
+        <v>15</v>
+      </c>
+      <c r="F18" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>258</v>
+      </c>
+      <c r="B19" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="74">
+        <v>10</v>
+      </c>
+      <c r="F19" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>259</v>
+      </c>
+      <c r="B20" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="74">
+        <v>25</v>
+      </c>
+      <c r="F20" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>260</v>
+      </c>
+      <c r="B21" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="74">
+        <v>25</v>
+      </c>
+      <c r="F21" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>261</v>
+      </c>
+      <c r="B22" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C22" t="s">
+        <v>198</v>
+      </c>
+      <c r="D22" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="74">
+        <v>3</v>
+      </c>
+      <c r="F22" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>262</v>
+      </c>
+      <c r="B23" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C23" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="74">
+        <v>10</v>
+      </c>
+      <c r="F23" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>263</v>
+      </c>
+      <c r="B24" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C24" t="s">
+        <v>200</v>
+      </c>
+      <c r="D24" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="74">
+        <v>1</v>
+      </c>
+      <c r="F24" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>264</v>
+      </c>
+      <c r="B25" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C25" t="s">
+        <v>201</v>
+      </c>
+      <c r="D25" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="74">
+        <v>1</v>
+      </c>
+      <c r="F25" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>265</v>
+      </c>
+      <c r="B26" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C26" t="s">
+        <v>202</v>
+      </c>
+      <c r="D26" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="74">
+        <v>1</v>
+      </c>
+      <c r="F26" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>266</v>
+      </c>
+      <c r="B27" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C27" t="s">
+        <v>203</v>
+      </c>
+      <c r="D27" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="74">
+        <v>1</v>
+      </c>
+      <c r="F27" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>267</v>
+      </c>
+      <c r="B28" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C28" t="s">
+        <v>204</v>
+      </c>
+      <c r="D28" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="74">
+        <v>1</v>
+      </c>
+      <c r="F28" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>268</v>
+      </c>
+      <c r="B29" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C29" t="s">
+        <v>205</v>
+      </c>
+      <c r="D29" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="74">
+        <v>2</v>
+      </c>
+      <c r="F29" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>269</v>
+      </c>
+      <c r="B30" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C30" t="s">
+        <v>206</v>
+      </c>
+      <c r="D30" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" s="74">
+        <v>1</v>
+      </c>
+      <c r="F30" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>270</v>
+      </c>
+      <c r="B31" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C31" t="s">
+        <v>207</v>
+      </c>
+      <c r="D31" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="74">
+        <v>3</v>
+      </c>
+      <c r="F31" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>271</v>
+      </c>
+      <c r="B32" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C32" t="s">
+        <v>208</v>
+      </c>
+      <c r="D32" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="74">
+        <v>1</v>
+      </c>
+      <c r="F32" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>272</v>
+      </c>
+      <c r="B33" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C33" t="s">
+        <v>209</v>
+      </c>
+      <c r="D33" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" s="74">
+        <v>1</v>
+      </c>
+      <c r="F33" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>273</v>
+      </c>
+      <c r="B34" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C34" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" s="74">
+        <v>2</v>
+      </c>
+      <c r="F34" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>274</v>
+      </c>
+      <c r="B35" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C35" t="s">
+        <v>211</v>
+      </c>
+      <c r="D35" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="74">
+        <v>6</v>
+      </c>
+      <c r="F35" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>275</v>
+      </c>
+      <c r="B36" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C36" t="s">
+        <v>212</v>
+      </c>
+      <c r="D36" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" s="74">
+        <v>2</v>
+      </c>
+      <c r="F36" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>276</v>
+      </c>
+      <c r="B37" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C37" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="74">
+        <v>2</v>
+      </c>
+      <c r="F37" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>277</v>
+      </c>
+      <c r="B38" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C38" t="s">
+        <v>214</v>
+      </c>
+      <c r="D38" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="74">
+        <v>2</v>
+      </c>
+      <c r="F38" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>278</v>
+      </c>
+      <c r="B39" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C39" t="s">
+        <v>215</v>
+      </c>
+      <c r="D39" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E39" s="74">
+        <v>5</v>
+      </c>
+      <c r="F39" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>279</v>
+      </c>
+      <c r="B40" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C40" t="s">
+        <v>216</v>
+      </c>
+      <c r="D40" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="74">
+        <v>2</v>
+      </c>
+      <c r="F40" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>280</v>
+      </c>
+      <c r="B41" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C41" t="s">
+        <v>217</v>
+      </c>
+      <c r="D41" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" s="74">
+        <v>3</v>
+      </c>
+      <c r="F41" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>281</v>
+      </c>
+      <c r="B42" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C42" t="s">
+        <v>218</v>
+      </c>
+      <c r="D42" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E42" s="74">
+        <v>2</v>
+      </c>
+      <c r="F42" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>282</v>
+      </c>
+      <c r="B43" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C43" t="s">
+        <v>219</v>
+      </c>
+      <c r="D43" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" s="74">
+        <v>3</v>
+      </c>
+      <c r="F43" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>283</v>
+      </c>
+      <c r="B44" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C44" t="s">
+        <v>220</v>
+      </c>
+      <c r="D44" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="74">
+        <v>3</v>
+      </c>
+      <c r="F44" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>284</v>
+      </c>
+      <c r="B45" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C45" t="s">
+        <v>221</v>
+      </c>
+      <c r="D45" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E45" s="74">
+        <v>4</v>
+      </c>
+      <c r="F45" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>285</v>
+      </c>
+      <c r="B46" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C46" t="s">
+        <v>222</v>
+      </c>
+      <c r="D46" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E46" s="74">
+        <v>4</v>
+      </c>
+      <c r="F46" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>286</v>
+      </c>
+      <c r="B47" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C47" t="s">
+        <v>223</v>
+      </c>
+      <c r="D47" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="74">
+        <v>4</v>
+      </c>
+      <c r="F47" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>287</v>
+      </c>
+      <c r="B48" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C48" t="s">
+        <v>224</v>
+      </c>
+      <c r="D48" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E48" s="74">
+        <v>8</v>
+      </c>
+      <c r="F48" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>288</v>
+      </c>
+      <c r="B49" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C49" t="s">
+        <v>225</v>
+      </c>
+      <c r="D49" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="74">
+        <v>2</v>
+      </c>
+      <c r="F49" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>289</v>
+      </c>
+      <c r="B50" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C50" t="s">
+        <v>226</v>
+      </c>
+      <c r="D50" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="74">
+        <v>2</v>
+      </c>
+      <c r="F50" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>290</v>
+      </c>
+      <c r="B51" s="71">
+        <v>45900</v>
+      </c>
+      <c r="C51" t="s">
+        <v>227</v>
+      </c>
+      <c r="D51" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E51" s="74">
+        <v>3</v>
+      </c>
+      <c r="F51" s="72" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>291</v>
+      </c>
+      <c r="B52" s="71">
+        <v>45901</v>
+      </c>
+      <c r="C52" t="s">
+        <v>228</v>
+      </c>
+      <c r="D52" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" s="74">
+        <v>-2</v>
+      </c>
+      <c r="F52" s="72" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>292</v>
+      </c>
+      <c r="B53" s="71">
+        <v>45901</v>
+      </c>
+      <c r="C53" t="s">
+        <v>229</v>
+      </c>
+      <c r="D53" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E53" s="74">
+        <v>-5</v>
+      </c>
+      <c r="F53" s="72" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>293</v>
+      </c>
+      <c r="B54" s="71">
+        <v>45901</v>
+      </c>
+      <c r="C54" t="s">
+        <v>230</v>
+      </c>
+      <c r="D54" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E54" s="74">
+        <v>20</v>
+      </c>
+      <c r="F54" s="72" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>294</v>
+      </c>
+      <c r="B55" s="71">
+        <v>45902</v>
+      </c>
+      <c r="C55" t="s">
+        <v>231</v>
+      </c>
+      <c r="D55" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55" s="74">
+        <v>15</v>
+      </c>
+      <c r="F55" s="72" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>295</v>
+      </c>
+      <c r="B56" s="71">
+        <v>45902</v>
+      </c>
+      <c r="C56" t="s">
+        <v>232</v>
+      </c>
+      <c r="D56" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E56" s="74">
+        <v>-3</v>
+      </c>
+      <c r="F56" s="72" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>296</v>
+      </c>
+      <c r="B57" s="71">
+        <v>45902</v>
+      </c>
+      <c r="C57" t="s">
+        <v>233</v>
+      </c>
+      <c r="D57" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" s="74">
+        <v>-2</v>
+      </c>
+      <c r="F57" s="72" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>297</v>
+      </c>
+      <c r="B58" s="71">
+        <v>45903</v>
+      </c>
+      <c r="C58" t="s">
+        <v>234</v>
+      </c>
+      <c r="D58" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E58" s="74">
+        <v>-2</v>
+      </c>
+      <c r="F58" s="72" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>298</v>
+      </c>
+      <c r="B59" s="71">
+        <v>45903</v>
+      </c>
+      <c r="C59" t="s">
+        <v>235</v>
+      </c>
+      <c r="D59" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E59" s="74">
+        <v>-1</v>
+      </c>
+      <c r="F59" s="72" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>299</v>
+      </c>
+      <c r="B60" s="71">
+        <v>45903</v>
+      </c>
+      <c r="C60" t="s">
+        <v>236</v>
+      </c>
+      <c r="D60" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E60" s="74">
+        <v>-4</v>
+      </c>
+      <c r="F60" s="72" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>300</v>
+      </c>
+      <c r="B61" s="71">
+        <v>45904</v>
+      </c>
+      <c r="C61" t="s">
+        <v>237</v>
+      </c>
+      <c r="D61" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="74">
+        <v>10</v>
+      </c>
+      <c r="F61" s="72" t="s">
+        <v>303</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C61" xr:uid="{8442A689-EFD5-4F1D-8E71-3A321F89ED08}">
+      <formula1>ProductList</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8064117B-FF42-4F16-ADB2-30D23F9CACA2}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="76" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="76" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="77" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="77" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="76" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="76" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="76" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="76" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="76" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/DataAnalyst.xlsx
+++ b/DataAnalyst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malik\OneDrive\Documents\Data\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2A9D38-99A3-4E6A-A65B-CA57F4A6A1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944A9EAC-22D2-480F-AD77-22186E640129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-9015" windowWidth="21840" windowHeight="13740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-9015" windowWidth="21840" windowHeight="13740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="304">
   <si>
     <t>ELECTRONICS COMPANIES REPORT Q1 2023</t>
   </si>
@@ -1235,7 +1235,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="11">
+  <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1247,8 +1247,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1459,11 +1460,13 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="10"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="11"/>
   </cellXfs>
-  <cellStyles count="11">
+  <cellStyles count="12">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{72D35A1C-E0E1-4D48-ACA5-2713C7D76C54}"/>
     <cellStyle name="Currency 2" xfId="3" xr:uid="{5FCDA341-36C1-44C8-A84F-DD4220D7588E}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 10" xfId="11" xr:uid="{E85ACF5D-AF0D-42E4-9A15-198AAAA0D245}"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{4F19D639-9EDA-4ED7-894B-95E892051C00}"/>
     <cellStyle name="Normal 3" xfId="4" xr:uid="{EB00786D-1BFA-4FE2-9C94-0F83B3ABD247}"/>
     <cellStyle name="Normal 4" xfId="5" xr:uid="{EE3DB81E-1F5E-40AE-96F3-E9492D96486F}"/>
@@ -1473,7 +1476,25 @@
     <cellStyle name="Normal 8" xfId="9" xr:uid="{0EFC0AAE-EB0E-4FA2-885A-2DA2EB3F3608}"/>
     <cellStyle name="Normal 9" xfId="10" xr:uid="{DFABB175-7506-410D-8AC4-26F83CE150B7}"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="29">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2068,36 +2089,36 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="C4:Q31" totalsRowCount="1">
   <autoFilter ref="C4:Q30" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" totalsRowLabel="Total" totalsRowDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMPANIES" totalsRowDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NUMBER OF EMPLOYEES" totalsRowDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COLOR" totalsRowDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LAUNCH DATE" totalsRowDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="QUANTITY" totalsRowFunction="sum" totalsRowDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PRICE" totalsRowFunction="sum" totalsRowDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AMOUNT" totalsRowFunction="sum" totalsRowDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="QUANTITY " totalsRowDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRICE " totalsRowDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="AMOUNT " totalsRowFunction="sum" totalsRowDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QUANTITY  " totalsRowDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="PRICE  " totalsRowDxfId="10"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="AMOUNT  " totalsRowFunction="sum" totalsRowDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="TOTAL" totalsRowFunction="sum" totalsRowDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" totalsRowLabel="Total" totalsRowDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMPANIES" totalsRowDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NUMBER OF EMPLOYEES" totalsRowDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COLOR" totalsRowDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LAUNCH DATE" totalsRowDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="QUANTITY" totalsRowFunction="sum" totalsRowDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PRICE" totalsRowFunction="sum" totalsRowDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AMOUNT" totalsRowFunction="sum" totalsRowDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="QUANTITY " totalsRowDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRICE " totalsRowDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="AMOUNT " totalsRowFunction="sum" totalsRowDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QUANTITY  " totalsRowDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="PRICE  " totalsRowDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="AMOUNT  " totalsRowFunction="sum" totalsRowDxfId="15"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="TOTAL" totalsRowFunction="sum" totalsRowDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}" name="Products" displayName="Products" ref="A1:F61" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}" name="Products" displayName="Products" ref="A1:F61" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="A1:F61" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{E8F4DFB0-EC56-4CBF-9F8C-23EDCA50F713}" name="ProductID" dataCellStyle="Normal 3"/>
-    <tableColumn id="2" xr3:uid="{01A2DB73-B8C2-4A45-A7CC-94CB4A4A2FEF}" name="Product Name" dataDxfId="7" dataCellStyle="Comma 2"/>
+    <tableColumn id="2" xr3:uid="{01A2DB73-B8C2-4A45-A7CC-94CB4A4A2FEF}" name="Product Name" dataDxfId="13" dataCellStyle="Comma 2"/>
     <tableColumn id="3" xr3:uid="{D7712E33-EC2C-4BBC-9183-D4083230AE51}" name="Category" dataCellStyle="Normal 3"/>
-    <tableColumn id="4" xr3:uid="{10280736-93EE-4A73-97B0-1F59FABAB46F}" name="Cost/Unit" dataDxfId="6" dataCellStyle="Comma 2"/>
-    <tableColumn id="5" xr3:uid="{AC22B57B-F391-4278-9CEA-6381C3C7599A}" name="Reorder Level" dataDxfId="5" dataCellStyle="Normal 3"/>
-    <tableColumn id="6" xr3:uid="{ECE3A126-A7F6-4E8A-B4CA-AC1B78868DAB}" name="Supplier" dataDxfId="4" dataCellStyle="Normal 3"/>
+    <tableColumn id="4" xr3:uid="{10280736-93EE-4A73-97B0-1F59FABAB46F}" name="Cost/Unit" dataDxfId="12" dataCellStyle="Comma 2"/>
+    <tableColumn id="5" xr3:uid="{AC22B57B-F391-4278-9CEA-6381C3C7599A}" name="Reorder Level" dataDxfId="11" dataCellStyle="Normal 3"/>
+    <tableColumn id="6" xr3:uid="{ECE3A126-A7F6-4E8A-B4CA-AC1B78868DAB}" name="Supplier" dataDxfId="10" dataCellStyle="Normal 3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2108,11 +2129,44 @@
   <autoFilter ref="A1:F61" xr:uid="{03C4EC66-596A-4191-8AD5-8C56A2B0936F}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{CF0FBA31-2E94-4135-8B0A-A8ADD4C1D54E}" name="TransID"/>
-    <tableColumn id="2" xr3:uid="{EB83FE89-2487-49C6-80BE-246C3764EFC8}" name="Date" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{EB83FE89-2487-49C6-80BE-246C3764EFC8}" name="Date" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{FE85118D-4F73-4CC4-947F-D727DBCF045B}" name="ProductID"/>
-    <tableColumn id="4" xr3:uid="{890FE897-5C0E-4846-94E3-254F9AB59CC8}" name="Site" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{D5DF56AA-CF75-4D46-9133-AE66DE368857}" name="Quantity" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{890FE897-5C0E-4846-94E3-254F9AB59CC8}" name="Site" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{D5DF56AA-CF75-4D46-9133-AE66DE368857}" name="Quantity" dataDxfId="8"/>
     <tableColumn id="6" xr3:uid="{8D0BBA31-EE38-4A83-9E89-796952F75830}" name="Type"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A5DC87FD-A8D1-440B-BAC9-DE34E48E5936}" name="Inventory" displayName="Inventory" ref="A1:J61" totalsRowShown="0" headerRowCellStyle="Normal 9">
+  <autoFilter ref="A1:J61" xr:uid="{A5DC87FD-A8D1-440B-BAC9-DE34E48E5936}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{E8701318-3AEB-41C8-947D-8F382111F831}" name="Site" dataCellStyle="Normal 10"/>
+    <tableColumn id="2" xr3:uid="{A8F9A49C-2A9D-43FA-9513-36E70E2B2700}" name="ProductID" dataCellStyle="Normal 10"/>
+    <tableColumn id="3" xr3:uid="{DD7691E1-3B82-419A-A596-FD7160832936}" name="Product Description" dataDxfId="5">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{3B6081B7-6D7B-40BA-B050-3F97A1DD80EA}" name="Supplier" dataDxfId="4">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{8BF557DE-8E2B-4AE9-8A66-D281C045EF9F}" name="Cost/Unit" dataDxfId="3">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{82A09554-3010-4D9D-867D-4111E1CD453F}" name="Reorder Level" dataDxfId="2">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{B0173CF8-A36E-441A-B27D-4CB13138DA80}" name="QuantityOnHand">
+      <calculatedColumnFormula>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{F1713281-EF53-48D5-9D64-F33AD9F1106B}" name="Stock Value" dataDxfId="1">
+      <calculatedColumnFormula>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{1AD33891-BE48-4965-8EAA-F8F9DE5AFD47}" name="Reorder" dataDxfId="0">
+      <calculatedColumnFormula>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{02298217-ED20-499A-84FA-6F2061FCCDF1}" name="Order Date"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2424,6 +2478,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
+    <tabColor rgb="FFC00000"/>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E53"/>
@@ -3011,6 +3066,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
+    <tabColor rgb="FFC00000"/>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="C1:Q31"/>
@@ -4361,6 +4417,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
+    <tabColor theme="7" tint="0.39997558519241921"/>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
@@ -5666,6 +5723,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312D5D85-F04D-4F6D-9160-0486A4994C8D}">
+  <sheetPr>
+    <tabColor theme="7" tint="0.39997558519241921"/>
+  </sheetPr>
   <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -6912,8 +6972,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8064117B-FF42-4F16-ADB2-30D23F9CACA2}">
-  <dimension ref="A1:J1"/>
+  <sheetPr>
+    <tabColor theme="7" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="10.59765625" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="3" max="6" width="30.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.3984375" customWidth="1"/>
+    <col min="9" max="9" width="9.46484375" customWidth="1"/>
+    <col min="10" max="10" width="11.86328125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="76" t="s">
@@ -6947,7 +7019,2170 @@
         <v>91</v>
       </c>
     </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="78" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Industrial Safety Gloves</v>
+      </c>
+      <c r="D2" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>NorthStar Industrial Supply</v>
+      </c>
+      <c r="E2">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>12.5</v>
+      </c>
+      <c r="F2" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>Reorder Level</v>
+      </c>
+      <c r="G2">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>50</v>
+      </c>
+      <c r="H2">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>625</v>
+      </c>
+      <c r="I2" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="78" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Industrial Safety Gloves</v>
+      </c>
+      <c r="D3" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>NorthStar Industrial Supply</v>
+      </c>
+      <c r="E3">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>12.5</v>
+      </c>
+      <c r="F3" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>Reorder Level</v>
+      </c>
+      <c r="G3">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I3" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="78" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Industrial Safety Gloves</v>
+      </c>
+      <c r="D4" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>NorthStar Industrial Supply</v>
+      </c>
+      <c r="E4">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>12.5</v>
+      </c>
+      <c r="F4" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>Reorder Level</v>
+      </c>
+      <c r="G4">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I4" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="78" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Steel-Toe Work Boots</v>
+      </c>
+      <c r="D5" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>ProSafe Equipment</v>
+      </c>
+      <c r="E5">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>85</v>
+      </c>
+      <c r="F5">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>50</v>
+      </c>
+      <c r="G5">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I5" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="78" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Steel-Toe Work Boots</v>
+      </c>
+      <c r="D6" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>ProSafe Equipment</v>
+      </c>
+      <c r="E6">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>85</v>
+      </c>
+      <c r="F6">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>50</v>
+      </c>
+      <c r="G6">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>30</v>
+      </c>
+      <c r="H6">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>2550</v>
+      </c>
+      <c r="I6" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="78" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Steel-Toe Work Boots</v>
+      </c>
+      <c r="D7" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>ProSafe Equipment</v>
+      </c>
+      <c r="E7">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>85</v>
+      </c>
+      <c r="F7">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>50</v>
+      </c>
+      <c r="G7">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I7" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="78" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Safety Glasses</v>
+      </c>
+      <c r="D8" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Guardian Safety Products</v>
+      </c>
+      <c r="E8">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>4.25</v>
+      </c>
+      <c r="F8">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I8" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="78" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Safety Glasses</v>
+      </c>
+      <c r="D9" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Guardian Safety Products</v>
+      </c>
+      <c r="E9">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>4.25</v>
+      </c>
+      <c r="F9">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I9" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="78" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Safety Glasses</v>
+      </c>
+      <c r="D10" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Guardian Safety Products</v>
+      </c>
+      <c r="E10">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>4.25</v>
+      </c>
+      <c r="F10">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>15</v>
+      </c>
+      <c r="G10">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>40</v>
+      </c>
+      <c r="H10">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>170</v>
+      </c>
+      <c r="I10" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>High-Visibility Safety Vest</v>
+      </c>
+      <c r="D11" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>WorkShield Canada</v>
+      </c>
+      <c r="E11">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>9.75</v>
+      </c>
+      <c r="F11">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>12</v>
+      </c>
+      <c r="H11">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>117</v>
+      </c>
+      <c r="I11" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>High-Visibility Safety Vest</v>
+      </c>
+      <c r="D12" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>WorkShield Canada</v>
+      </c>
+      <c r="E12">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>9.75</v>
+      </c>
+      <c r="F12">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>25</v>
+      </c>
+      <c r="G12">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I12" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>High-Visibility Safety Vest</v>
+      </c>
+      <c r="D13" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>WorkShield Canada</v>
+      </c>
+      <c r="E13">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>9.75</v>
+      </c>
+      <c r="F13">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>25</v>
+      </c>
+      <c r="G13">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I13" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Hard Hat - Yellow</v>
+      </c>
+      <c r="D14" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>ProSafe Equipment</v>
+      </c>
+      <c r="E14">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>14.5</v>
+      </c>
+      <c r="F14">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>30</v>
+      </c>
+      <c r="G14">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I14" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Hard Hat - Yellow</v>
+      </c>
+      <c r="D15" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>ProSafe Equipment</v>
+      </c>
+      <c r="E15">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>14.5</v>
+      </c>
+      <c r="F15">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>30</v>
+      </c>
+      <c r="G15">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>20</v>
+      </c>
+      <c r="H15">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>290</v>
+      </c>
+      <c r="I15" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Hard Hat - Yellow</v>
+      </c>
+      <c r="D16" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>ProSafe Equipment</v>
+      </c>
+      <c r="E16">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>14.5</v>
+      </c>
+      <c r="F16">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>30</v>
+      </c>
+      <c r="G16">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I16" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A17" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="78" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Ear Protection Earmuffs</v>
+      </c>
+      <c r="D17" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Guardian Safety Products</v>
+      </c>
+      <c r="E17">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>18</v>
+      </c>
+      <c r="F17">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>20</v>
+      </c>
+      <c r="G17">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I17" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A18" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="78" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Ear Protection Earmuffs</v>
+      </c>
+      <c r="D18" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Guardian Safety Products</v>
+      </c>
+      <c r="E18">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>18</v>
+      </c>
+      <c r="F18">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>20</v>
+      </c>
+      <c r="G18">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I18" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A19" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="78" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Ear Protection Earmuffs</v>
+      </c>
+      <c r="D19" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Guardian Safety Products</v>
+      </c>
+      <c r="E19">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>18</v>
+      </c>
+      <c r="F19">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>20</v>
+      </c>
+      <c r="G19">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>14</v>
+      </c>
+      <c r="H19">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>252</v>
+      </c>
+      <c r="I19" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A20" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Disposable Dust Mask</v>
+      </c>
+      <c r="D20" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>NorthStar Industrial Supply</v>
+      </c>
+      <c r="E20">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>6.25</v>
+      </c>
+      <c r="F20">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>15</v>
+      </c>
+      <c r="G20">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>25</v>
+      </c>
+      <c r="H20">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>156.25</v>
+      </c>
+      <c r="I20" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A21" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Disposable Dust Mask</v>
+      </c>
+      <c r="D21" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>NorthStar Industrial Supply</v>
+      </c>
+      <c r="E21">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>6.25</v>
+      </c>
+      <c r="F21">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>15</v>
+      </c>
+      <c r="G21">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I21" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A22" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Disposable Dust Mask</v>
+      </c>
+      <c r="D22" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>NorthStar Industrial Supply</v>
+      </c>
+      <c r="E22">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>6.25</v>
+      </c>
+      <c r="F22">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>15</v>
+      </c>
+      <c r="G22">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I22" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A23" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="78" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Cut-Resistant Gloves</v>
+      </c>
+      <c r="D23" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>WorkShield Canada</v>
+      </c>
+      <c r="E23">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>11.5</v>
+      </c>
+      <c r="F23">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>40</v>
+      </c>
+      <c r="G23">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I23" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A24" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="78" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Cut-Resistant Gloves</v>
+      </c>
+      <c r="D24" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>WorkShield Canada</v>
+      </c>
+      <c r="E24">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>11.5</v>
+      </c>
+      <c r="F24">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>40</v>
+      </c>
+      <c r="G24">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>30</v>
+      </c>
+      <c r="H24">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>345</v>
+      </c>
+      <c r="I24" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A25" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="78" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Cut-Resistant Gloves</v>
+      </c>
+      <c r="D25" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>WorkShield Canada</v>
+      </c>
+      <c r="E25">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>11.5</v>
+      </c>
+      <c r="F25">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>40</v>
+      </c>
+      <c r="G25">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I25" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A26" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="78" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Aluminum Step Ladder</v>
+      </c>
+      <c r="D26" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Maple Industrial Supply</v>
+      </c>
+      <c r="E26">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>89</v>
+      </c>
+      <c r="F26">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>25</v>
+      </c>
+      <c r="G26">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I26" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A27" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="78" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Aluminum Step Ladder</v>
+      </c>
+      <c r="D27" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Maple Industrial Supply</v>
+      </c>
+      <c r="E27">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>89</v>
+      </c>
+      <c r="F27">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>25</v>
+      </c>
+      <c r="G27">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I27" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A28" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="78" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Aluminum Step Ladder</v>
+      </c>
+      <c r="D28" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Maple Industrial Supply</v>
+      </c>
+      <c r="E28">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>89</v>
+      </c>
+      <c r="F28">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>25</v>
+      </c>
+      <c r="G28">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>10</v>
+      </c>
+      <c r="H28">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>890</v>
+      </c>
+      <c r="I28" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A29" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="78" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Platform Hand Truck</v>
+      </c>
+      <c r="D29" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Northern Material Handling</v>
+      </c>
+      <c r="E29">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>125</v>
+      </c>
+      <c r="F29">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>5</v>
+      </c>
+      <c r="G29">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>35</v>
+      </c>
+      <c r="H29">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>4375</v>
+      </c>
+      <c r="I29" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A30" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="78" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Platform Hand Truck</v>
+      </c>
+      <c r="D30" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Northern Material Handling</v>
+      </c>
+      <c r="E30">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>125</v>
+      </c>
+      <c r="F30">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>5</v>
+      </c>
+      <c r="G30">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I30" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A31" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="78" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Platform Hand Truck</v>
+      </c>
+      <c r="D31" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Northern Material Handling</v>
+      </c>
+      <c r="E31">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>125</v>
+      </c>
+      <c r="F31">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I31" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A32" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="78" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Heavy-Duty Pallet Jack</v>
+      </c>
+      <c r="D32" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Warehouse Solutions Inc.</v>
+      </c>
+      <c r="E32">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>475</v>
+      </c>
+      <c r="F32">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>8</v>
+      </c>
+      <c r="G32">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I32" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A33" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="78" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Heavy-Duty Pallet Jack</v>
+      </c>
+      <c r="D33" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Warehouse Solutions Inc.</v>
+      </c>
+      <c r="E33">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>475</v>
+      </c>
+      <c r="F33">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>8</v>
+      </c>
+      <c r="G33">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>25</v>
+      </c>
+      <c r="H33">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>11875</v>
+      </c>
+      <c r="I33" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A34" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="78" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Heavy-Duty Pallet Jack</v>
+      </c>
+      <c r="D34" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Warehouse Solutions Inc.</v>
+      </c>
+      <c r="E34">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>475</v>
+      </c>
+      <c r="F34">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>8</v>
+      </c>
+      <c r="G34">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I34" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A35" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Steel Storage Bin</v>
+      </c>
+      <c r="D35" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Maple Industrial Supply</v>
+      </c>
+      <c r="E35">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>18.75</v>
+      </c>
+      <c r="F35">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>3</v>
+      </c>
+      <c r="G35">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I35" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A36" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Steel Storage Bin</v>
+      </c>
+      <c r="D36" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Maple Industrial Supply</v>
+      </c>
+      <c r="E36">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>18.75</v>
+      </c>
+      <c r="F36">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>3</v>
+      </c>
+      <c r="G36">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I36" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A37" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Steel Storage Bin</v>
+      </c>
+      <c r="D37" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Maple Industrial Supply</v>
+      </c>
+      <c r="E37">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>18.75</v>
+      </c>
+      <c r="F37">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>3</v>
+      </c>
+      <c r="G37">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>18</v>
+      </c>
+      <c r="H37">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>337.5</v>
+      </c>
+      <c r="I37" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A38" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Plastic Parts Bin</v>
+      </c>
+      <c r="D38" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>StoragePro Canada</v>
+      </c>
+      <c r="E38">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>6.5</v>
+      </c>
+      <c r="F38">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>20</v>
+      </c>
+      <c r="G38">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>60</v>
+      </c>
+      <c r="H38">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>390</v>
+      </c>
+      <c r="I38" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A39" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Plastic Parts Bin</v>
+      </c>
+      <c r="D39" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>StoragePro Canada</v>
+      </c>
+      <c r="E39">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>6.5</v>
+      </c>
+      <c r="F39">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>20</v>
+      </c>
+      <c r="G39">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I39" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A40" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Plastic Parts Bin</v>
+      </c>
+      <c r="D40" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>StoragePro Canada</v>
+      </c>
+      <c r="E40">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>6.5</v>
+      </c>
+      <c r="F40">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>20</v>
+      </c>
+      <c r="G40">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I40" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A41" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="78" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Wire Shelving Unit</v>
+      </c>
+      <c r="D41" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Warehouse Solutions Inc.</v>
+      </c>
+      <c r="E41">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>145</v>
+      </c>
+      <c r="F41">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>30</v>
+      </c>
+      <c r="G41">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I41" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A42" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" s="78" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Wire Shelving Unit</v>
+      </c>
+      <c r="D42" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Warehouse Solutions Inc.</v>
+      </c>
+      <c r="E42">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>145</v>
+      </c>
+      <c r="F42">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>30</v>
+      </c>
+      <c r="G42">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>50</v>
+      </c>
+      <c r="H42">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>7250</v>
+      </c>
+      <c r="I42" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A43" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="78" t="s">
+        <v>78</v>
+      </c>
+      <c r="C43" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Wire Shelving Unit</v>
+      </c>
+      <c r="D43" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Warehouse Solutions Inc.</v>
+      </c>
+      <c r="E43">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>145</v>
+      </c>
+      <c r="F43">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>30</v>
+      </c>
+      <c r="G43">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I43" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A44" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="78" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Mobile Storage Cart</v>
+      </c>
+      <c r="D44" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Northern Material Handling</v>
+      </c>
+      <c r="E44">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>95</v>
+      </c>
+      <c r="F44">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>5</v>
+      </c>
+      <c r="G44">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I44" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A45" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" s="78" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Mobile Storage Cart</v>
+      </c>
+      <c r="D45" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Northern Material Handling</v>
+      </c>
+      <c r="E45">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>95</v>
+      </c>
+      <c r="F45">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>5</v>
+      </c>
+      <c r="G45">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I45" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A46" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46" s="78" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Mobile Storage Cart</v>
+      </c>
+      <c r="D46" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>Northern Material Handling</v>
+      </c>
+      <c r="E46">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>95</v>
+      </c>
+      <c r="F46">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>5</v>
+      </c>
+      <c r="G46">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>35</v>
+      </c>
+      <c r="H46">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>3325</v>
+      </c>
+      <c r="I46" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A47" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47" s="78" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Plastic Tote - 27 Gallon</v>
+      </c>
+      <c r="D47" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>StoragePro Canada</v>
+      </c>
+      <c r="E47">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>22.5</v>
+      </c>
+      <c r="F47">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>8</v>
+      </c>
+      <c r="G47">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>20</v>
+      </c>
+      <c r="H47">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>450</v>
+      </c>
+      <c r="I47" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A48" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B48" s="78" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Plastic Tote - 27 Gallon</v>
+      </c>
+      <c r="D48" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>StoragePro Canada</v>
+      </c>
+      <c r="E48">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>22.5</v>
+      </c>
+      <c r="F48">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>8</v>
+      </c>
+      <c r="G48">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I48" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A49" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="78" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Plastic Tote - 27 Gallon</v>
+      </c>
+      <c r="D49" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>StoragePro Canada</v>
+      </c>
+      <c r="E49">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>22.5</v>
+      </c>
+      <c r="F49">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>8</v>
+      </c>
+      <c r="G49">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I49" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A50" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B50" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Corrugated Shipping Box - Small</v>
+      </c>
+      <c r="D50" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>PackRight Solutions</v>
+      </c>
+      <c r="E50">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>1.25</v>
+      </c>
+      <c r="F50">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>15</v>
+      </c>
+      <c r="G50">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I50" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A51" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="C51" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Corrugated Shipping Box - Small</v>
+      </c>
+      <c r="D51" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>PackRight Solutions</v>
+      </c>
+      <c r="E51">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>1.25</v>
+      </c>
+      <c r="F51">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>15</v>
+      </c>
+      <c r="G51">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>15</v>
+      </c>
+      <c r="H51">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>18.75</v>
+      </c>
+      <c r="I51" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A52" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Corrugated Shipping Box - Small</v>
+      </c>
+      <c r="D52" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>PackRight Solutions</v>
+      </c>
+      <c r="E52">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>1.25</v>
+      </c>
+      <c r="F52">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>15</v>
+      </c>
+      <c r="G52">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I52" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A53" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="C53" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Corrugated Shipping Box - Medium</v>
+      </c>
+      <c r="D53" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>PackRight Solutions</v>
+      </c>
+      <c r="E53">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>2.1</v>
+      </c>
+      <c r="F53">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>100</v>
+      </c>
+      <c r="G53">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I53" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A54" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B54" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="C54" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Corrugated Shipping Box - Medium</v>
+      </c>
+      <c r="D54" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>PackRight Solutions</v>
+      </c>
+      <c r="E54">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>2.1</v>
+      </c>
+      <c r="F54">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>100</v>
+      </c>
+      <c r="G54">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I54" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A55" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="C55" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Corrugated Shipping Box - Medium</v>
+      </c>
+      <c r="D55" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>PackRight Solutions</v>
+      </c>
+      <c r="E55">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>2.1</v>
+      </c>
+      <c r="F55">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>100</v>
+      </c>
+      <c r="G55">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>10</v>
+      </c>
+      <c r="H55">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>21</v>
+      </c>
+      <c r="I55" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A56" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="78" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Corrugated Shipping Box - Large</v>
+      </c>
+      <c r="D56" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>BoxWorks Canada</v>
+      </c>
+      <c r="E56">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>3.75</v>
+      </c>
+      <c r="F56">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>100</v>
+      </c>
+      <c r="G56">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>25</v>
+      </c>
+      <c r="H56">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>93.75</v>
+      </c>
+      <c r="I56" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A57" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="78" t="s">
+        <v>83</v>
+      </c>
+      <c r="C57" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Corrugated Shipping Box - Large</v>
+      </c>
+      <c r="D57" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>BoxWorks Canada</v>
+      </c>
+      <c r="E57">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>3.75</v>
+      </c>
+      <c r="F57">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>100</v>
+      </c>
+      <c r="G57">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I57" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A58" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="78" t="s">
+        <v>83</v>
+      </c>
+      <c r="C58" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Corrugated Shipping Box - Large</v>
+      </c>
+      <c r="D58" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>BoxWorks Canada</v>
+      </c>
+      <c r="E58">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>3.75</v>
+      </c>
+      <c r="F58">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>100</v>
+      </c>
+      <c r="G58">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I58" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A59" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59" s="78" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Stretch Wrap Roll</v>
+      </c>
+      <c r="D59" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>PackRight Solutions</v>
+      </c>
+      <c r="E59">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>18.5</v>
+      </c>
+      <c r="F59">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>75</v>
+      </c>
+      <c r="G59">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I59" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A60" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" s="78" t="s">
+        <v>84</v>
+      </c>
+      <c r="C60" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Stretch Wrap Roll</v>
+      </c>
+      <c r="D60" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>PackRight Solutions</v>
+      </c>
+      <c r="E60">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>18.5</v>
+      </c>
+      <c r="F60">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>75</v>
+      </c>
+      <c r="G60">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>25</v>
+      </c>
+      <c r="H60">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>462.5</v>
+      </c>
+      <c r="I60" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A61" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" s="78" t="s">
+        <v>84</v>
+      </c>
+      <c r="C61" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
+        <v>Stretch Wrap Roll</v>
+      </c>
+      <c r="D61" t="str">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
+        <v>PackRight Solutions</v>
+      </c>
+      <c r="E61">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
+        <v>18.5</v>
+      </c>
+      <c r="F61">
+        <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
+        <v>75</v>
+      </c>
+      <c r="G61">
+        <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
+        <v>0</v>
+      </c>
+      <c r="I61" t="str">
+        <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/DataAnalyst.xlsx
+++ b/DataAnalyst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malik\OneDrive\Documents\Data\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944A9EAC-22D2-480F-AD77-22186E640129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A97CD8-BE65-4FCB-8C74-C5148A674D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-9015" windowWidth="21840" windowHeight="13740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <definedName name="ProductList">Products[ProductID]</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="304">
   <si>
     <t>ELECTRONICS COMPANIES REPORT Q1 2023</t>
   </si>
@@ -960,9 +961,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00;\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="mmm/dd"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -1238,8 +1239,8 @@
   <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="3" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
@@ -1249,7 +1250,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1418,6 +1419,26 @@
     <xf numFmtId="7" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="4"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="4" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="3" xfId="4" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="7" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="9"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="9" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="8" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="10"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="11"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1439,28 +1460,6 @@
     <xf numFmtId="7" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="4"/>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="4" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="3" xfId="4" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1"/>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="7" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="9"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="9" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="8" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="10"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="11"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{72D35A1C-E0E1-4D48-ACA5-2713C7D76C54}"/>
@@ -1476,24 +1475,76 @@
     <cellStyle name="Normal 8" xfId="9" xr:uid="{0EFC0AAE-EB0E-4FA2-885A-2DA2EB3F3608}"/>
     <cellStyle name="Normal 9" xfId="10" xr:uid="{DFABB175-7506-410D-8AC4-26F83CE150B7}"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="36">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1505,28 +1556,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="35" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -1558,6 +1591,24 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -2072,6 +2123,24 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2089,28 +2158,28 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="C4:Q31" totalsRowCount="1">
   <autoFilter ref="C4:Q30" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" totalsRowLabel="Total" totalsRowDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMPANIES" totalsRowDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NUMBER OF EMPLOYEES" totalsRowDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COLOR" totalsRowDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LAUNCH DATE" totalsRowDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="QUANTITY" totalsRowFunction="sum" totalsRowDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PRICE" totalsRowFunction="sum" totalsRowDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AMOUNT" totalsRowFunction="sum" totalsRowDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="QUANTITY " totalsRowDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRICE " totalsRowDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="AMOUNT " totalsRowFunction="sum" totalsRowDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QUANTITY  " totalsRowDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="PRICE  " totalsRowDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="AMOUNT  " totalsRowFunction="sum" totalsRowDxfId="15"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="TOTAL" totalsRowFunction="sum" totalsRowDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" totalsRowLabel="Total" totalsRowDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMPANIES" totalsRowDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NUMBER OF EMPLOYEES" totalsRowDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COLOR" totalsRowDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LAUNCH DATE" totalsRowDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="QUANTITY" totalsRowFunction="sum" totalsRowDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PRICE" totalsRowFunction="sum" totalsRowDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AMOUNT" totalsRowFunction="sum" totalsRowDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="QUANTITY " totalsRowDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRICE " totalsRowDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="AMOUNT " totalsRowFunction="sum" totalsRowDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QUANTITY  " totalsRowDxfId="18"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="PRICE  " totalsRowDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="AMOUNT  " totalsRowFunction="sum" totalsRowDxfId="16"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="TOTAL" totalsRowFunction="sum" totalsRowDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}" name="Products" displayName="Products" ref="A1:F61" totalsRowShown="0" headerRowDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}" name="Products" displayName="Products" ref="A1:F61" totalsRowShown="0" headerRowDxfId="14">
   <autoFilter ref="A1:F61" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{E8F4DFB0-EC56-4CBF-9F8C-23EDCA50F713}" name="ProductID" dataCellStyle="Normal 3"/>
@@ -2129,10 +2198,10 @@
   <autoFilter ref="A1:F61" xr:uid="{03C4EC66-596A-4191-8AD5-8C56A2B0936F}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{CF0FBA31-2E94-4135-8B0A-A8ADD4C1D54E}" name="TransID"/>
-    <tableColumn id="2" xr3:uid="{EB83FE89-2487-49C6-80BE-246C3764EFC8}" name="Date" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{EB83FE89-2487-49C6-80BE-246C3764EFC8}" name="Date" dataDxfId="9"/>
     <tableColumn id="3" xr3:uid="{FE85118D-4F73-4CC4-947F-D727DBCF045B}" name="ProductID"/>
-    <tableColumn id="4" xr3:uid="{890FE897-5C0E-4846-94E3-254F9AB59CC8}" name="Site" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{D5DF56AA-CF75-4D46-9133-AE66DE368857}" name="Quantity" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{890FE897-5C0E-4846-94E3-254F9AB59CC8}" name="Site" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{D5DF56AA-CF75-4D46-9133-AE66DE368857}" name="Quantity" dataDxfId="7"/>
     <tableColumn id="6" xr3:uid="{8D0BBA31-EE38-4A83-9E89-796952F75830}" name="Type"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2142,28 +2211,31 @@
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A5DC87FD-A8D1-440B-BAC9-DE34E48E5936}" name="Inventory" displayName="Inventory" ref="A1:J61" totalsRowShown="0" headerRowCellStyle="Normal 9">
   <autoFilter ref="A1:J61" xr:uid="{A5DC87FD-A8D1-440B-BAC9-DE34E48E5936}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J61">
+    <sortCondition ref="I1:I61"/>
+  </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{E8701318-3AEB-41C8-947D-8F382111F831}" name="Site" dataCellStyle="Normal 10"/>
     <tableColumn id="2" xr3:uid="{A8F9A49C-2A9D-43FA-9513-36E70E2B2700}" name="ProductID" dataCellStyle="Normal 10"/>
-    <tableColumn id="3" xr3:uid="{DD7691E1-3B82-419A-A596-FD7160832936}" name="Product Description" dataDxfId="5">
+    <tableColumn id="3" xr3:uid="{DD7691E1-3B82-419A-A596-FD7160832936}" name="Product Description" dataDxfId="35">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3B6081B7-6D7B-40BA-B050-3F97A1DD80EA}" name="Supplier" dataDxfId="4">
+    <tableColumn id="4" xr3:uid="{3B6081B7-6D7B-40BA-B050-3F97A1DD80EA}" name="Supplier" dataDxfId="34">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8BF557DE-8E2B-4AE9-8A66-D281C045EF9F}" name="Cost/Unit" dataDxfId="3">
+    <tableColumn id="5" xr3:uid="{8BF557DE-8E2B-4AE9-8A66-D281C045EF9F}" name="Cost/Unit" dataDxfId="33">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{82A09554-3010-4D9D-867D-4111E1CD453F}" name="Reorder Level" dataDxfId="2">
+    <tableColumn id="6" xr3:uid="{82A09554-3010-4D9D-867D-4111E1CD453F}" name="Reorder Level" dataDxfId="32">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{B0173CF8-A36E-441A-B27D-4CB13138DA80}" name="QuantityOnHand">
       <calculatedColumnFormula>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F1713281-EF53-48D5-9D64-F33AD9F1106B}" name="Stock Value" dataDxfId="1">
+    <tableColumn id="8" xr3:uid="{F1713281-EF53-48D5-9D64-F33AD9F1106B}" name="Stock Value" dataDxfId="31">
       <calculatedColumnFormula>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1AD33891-BE48-4965-8EAA-F8F9DE5AFD47}" name="Reorder" dataDxfId="0">
+    <tableColumn id="9" xr3:uid="{1AD33891-BE48-4965-8EAA-F8F9DE5AFD47}" name="Reorder" dataDxfId="30">
       <calculatedColumnFormula>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{02298217-ED20-499A-84FA-6F2061FCCDF1}" name="Order Date"/>
@@ -3092,23 +3164,23 @@
   <sheetData>
     <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="3:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="C2" s="58" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="59"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
+      <c r="C2" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="71"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="74"/>
+      <c r="Q2" s="74"/>
     </row>
     <row r="3" spans="3:17" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.65">
       <c r="C3" s="8"/>
@@ -3121,16 +3193,16 @@
       </c>
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
-      <c r="K3" s="63" t="s">
+      <c r="K3" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="63" t="s">
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
       <c r="Q3" s="13" t="s">
         <v>4</v>
       </c>
@@ -4432,1285 +4504,1285 @@
     <col min="7" max="9" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="65" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="65" t="s">
+    <row r="1" spans="1:7" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A1" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="58" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="F1" s="65" t="s">
+      <c r="F1" s="58" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="68">
+      <c r="D2" s="61">
         <v>12.5</v>
       </c>
-      <c r="E2" s="68" t="s">
-        <v>87</v>
-      </c>
-      <c r="F2" s="66" t="s">
+      <c r="E2" s="61">
+        <v>9</v>
+      </c>
+      <c r="F2" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="G2" s="68"/>
+      <c r="G2" s="61"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="61" t="s">
         <v>98</v>
       </c>
-      <c r="C3" s="66" t="s">
+      <c r="C3" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="68">
+      <c r="D3" s="61">
         <v>85</v>
       </c>
-      <c r="E3" s="69">
+      <c r="E3" s="62">
         <v>50</v>
       </c>
-      <c r="F3" s="66" t="s">
+      <c r="F3" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="G3" s="68"/>
+      <c r="G3" s="61"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="68">
+      <c r="D4" s="61">
         <v>4.25</v>
       </c>
-      <c r="E4" s="69">
+      <c r="E4" s="62">
         <v>15</v>
       </c>
-      <c r="F4" s="66" t="s">
+      <c r="F4" s="59" t="s">
         <v>101</v>
       </c>
-      <c r="G4" s="68"/>
+      <c r="G4" s="61"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="61" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="66" t="s">
+      <c r="C5" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="68">
+      <c r="D5" s="61">
         <v>9.75</v>
       </c>
-      <c r="E5" s="69">
+      <c r="E5" s="62">
         <v>25</v>
       </c>
-      <c r="F5" s="66" t="s">
+      <c r="F5" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="68"/>
+      <c r="G5" s="61"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="59" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="66" t="s">
+      <c r="C6" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="68">
+      <c r="D6" s="61">
         <v>14.5</v>
       </c>
-      <c r="E6" s="69">
+      <c r="E6" s="62">
         <v>30</v>
       </c>
-      <c r="F6" s="66" t="s">
+      <c r="F6" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="68"/>
+      <c r="G6" s="61"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="70" t="s">
+      <c r="B7" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="68">
+      <c r="D7" s="61">
         <v>18</v>
       </c>
-      <c r="E7" s="69">
+      <c r="E7" s="62">
         <v>20</v>
       </c>
-      <c r="F7" s="67" t="s">
+      <c r="F7" s="60" t="s">
         <v>101</v>
       </c>
-      <c r="G7" s="68"/>
+      <c r="G7" s="61"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="66" t="s">
+      <c r="A8" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="66" t="s">
+      <c r="C8" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="68">
+      <c r="D8" s="61">
         <v>6.25</v>
       </c>
-      <c r="E8" s="69">
+      <c r="E8" s="62">
         <v>15</v>
       </c>
-      <c r="F8" s="66" t="s">
+      <c r="F8" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="G8" s="68"/>
+      <c r="G8" s="61"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="61" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="66" t="s">
+      <c r="C9" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="68">
+      <c r="D9" s="61">
         <v>11.5</v>
       </c>
-      <c r="E9" s="69">
+      <c r="E9" s="62">
         <v>40</v>
       </c>
-      <c r="F9" s="66" t="s">
+      <c r="F9" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="G9" s="68"/>
+      <c r="G9" s="61"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="59" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="61" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="66" t="s">
+      <c r="C10" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="68">
+      <c r="D10" s="61">
         <v>89</v>
       </c>
-      <c r="E10" s="69">
+      <c r="E10" s="62">
         <v>25</v>
       </c>
-      <c r="F10" s="67" t="s">
+      <c r="F10" s="60" t="s">
         <v>110</v>
       </c>
-      <c r="G10" s="68"/>
+      <c r="G10" s="61"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="70" t="s">
+      <c r="B11" s="61" t="s">
         <v>111</v>
       </c>
-      <c r="C11" s="66" t="s">
+      <c r="C11" s="59" t="s">
         <v>112</v>
       </c>
-      <c r="D11" s="68">
+      <c r="D11" s="61">
         <v>125</v>
       </c>
-      <c r="E11" s="69">
+      <c r="E11" s="62">
         <v>5</v>
       </c>
-      <c r="F11" s="66" t="s">
+      <c r="F11" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="G11" s="68"/>
+      <c r="G11" s="61"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="70" t="s">
+      <c r="B12" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="59" t="s">
         <v>112</v>
       </c>
-      <c r="D12" s="68">
+      <c r="D12" s="61">
         <v>475</v>
       </c>
-      <c r="E12" s="69">
+      <c r="E12" s="62">
         <v>8</v>
       </c>
-      <c r="F12" s="67" t="s">
+      <c r="F12" s="60" t="s">
         <v>115</v>
       </c>
-      <c r="G12" s="68"/>
+      <c r="G12" s="61"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="C13" s="66" t="s">
+      <c r="C13" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="68">
+      <c r="D13" s="61">
         <v>18.75</v>
       </c>
-      <c r="E13" s="69">
+      <c r="E13" s="62">
         <v>3</v>
       </c>
-      <c r="F13" s="67" t="s">
+      <c r="F13" s="60" t="s">
         <v>110</v>
       </c>
-      <c r="G13" s="68"/>
+      <c r="G13" s="61"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="59" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="70" t="s">
+      <c r="B14" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="C14" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="D14" s="68">
+      <c r="D14" s="61">
         <v>6.5</v>
       </c>
-      <c r="E14" s="69">
+      <c r="E14" s="62">
         <v>20</v>
       </c>
-      <c r="F14" s="66" t="s">
+      <c r="F14" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="G14" s="68"/>
+      <c r="G14" s="61"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="70" t="s">
+      <c r="B15" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="68">
+      <c r="D15" s="61">
         <v>145</v>
       </c>
-      <c r="E15" s="69">
+      <c r="E15" s="62">
         <v>30</v>
       </c>
-      <c r="F15" s="66" t="s">
+      <c r="F15" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="68"/>
+      <c r="G15" s="61"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A16" s="66" t="s">
+      <c r="A16" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="70" t="s">
+      <c r="B16" s="61" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="66" t="s">
+      <c r="C16" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="D16" s="68">
+      <c r="D16" s="61">
         <v>95</v>
       </c>
-      <c r="E16" s="69">
+      <c r="E16" s="62">
         <v>5</v>
       </c>
-      <c r="F16" s="66" t="s">
+      <c r="F16" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="G16" s="68"/>
+      <c r="G16" s="61"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="B17" s="70" t="s">
+      <c r="B17" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="66" t="s">
+      <c r="C17" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="68">
+      <c r="D17" s="61">
         <v>22.5</v>
       </c>
-      <c r="E17" s="69">
+      <c r="E17" s="62">
         <v>8</v>
       </c>
-      <c r="F17" s="66" t="s">
+      <c r="F17" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="G17" s="68"/>
+      <c r="G17" s="61"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" s="66" t="s">
+      <c r="A18" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="70" t="s">
+      <c r="B18" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="66" t="s">
+      <c r="C18" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="68">
+      <c r="D18" s="61">
         <v>1.25</v>
       </c>
-      <c r="E18" s="69">
+      <c r="E18" s="62">
         <v>15</v>
       </c>
-      <c r="F18" s="66" t="s">
+      <c r="F18" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="G18" s="68"/>
+      <c r="G18" s="61"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" s="66" t="s">
+      <c r="A19" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="70" t="s">
+      <c r="B19" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="66" t="s">
+      <c r="C19" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="D19" s="68">
+      <c r="D19" s="61">
         <v>2.1</v>
       </c>
-      <c r="E19" s="69">
+      <c r="E19" s="62">
         <v>100</v>
       </c>
-      <c r="F19" s="67" t="s">
+      <c r="F19" s="60" t="s">
         <v>125</v>
       </c>
-      <c r="G19" s="68"/>
+      <c r="G19" s="61"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" s="66" t="s">
+      <c r="A20" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="61" t="s">
         <v>127</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="C20" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="68">
+      <c r="D20" s="61">
         <v>3.75</v>
       </c>
-      <c r="E20" s="69">
+      <c r="E20" s="62">
         <v>100</v>
       </c>
-      <c r="F20" s="66" t="s">
+      <c r="F20" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="G20" s="68"/>
+      <c r="G20" s="61"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="66" t="s">
+      <c r="A21" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="70" t="s">
+      <c r="B21" s="61" t="s">
         <v>129</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="C21" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="D21" s="68">
+      <c r="D21" s="61">
         <v>18.5</v>
       </c>
-      <c r="E21" s="69">
+      <c r="E21" s="62">
         <v>75</v>
       </c>
-      <c r="F21" s="66" t="s">
+      <c r="F21" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="G21" s="68"/>
+      <c r="G21" s="61"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" s="66" t="s">
+      <c r="A22" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="61" t="s">
         <v>130</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="68">
+      <c r="D22" s="61">
         <v>24</v>
       </c>
-      <c r="E22" s="69">
+      <c r="E22" s="62">
         <v>25</v>
       </c>
-      <c r="F22" s="67" t="s">
+      <c r="F22" s="60" t="s">
         <v>131</v>
       </c>
-      <c r="G22" s="68"/>
+      <c r="G22" s="61"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="59" t="s">
         <v>199</v>
       </c>
-      <c r="B23" s="70" t="s">
+      <c r="B23" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="C23" s="66" t="s">
+      <c r="C23" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="68">
+      <c r="D23" s="61">
         <v>4.75</v>
       </c>
-      <c r="E23" s="69">
+      <c r="E23" s="62">
         <v>30</v>
       </c>
-      <c r="F23" s="67" t="s">
+      <c r="F23" s="60" t="s">
         <v>131</v>
       </c>
-      <c r="G23" s="68"/>
+      <c r="G23" s="61"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" s="66" t="s">
+      <c r="A24" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="B24" s="70" t="s">
+      <c r="B24" s="61" t="s">
         <v>133</v>
       </c>
-      <c r="C24" s="66" t="s">
+      <c r="C24" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="68">
+      <c r="D24" s="61">
         <v>32</v>
       </c>
-      <c r="E24" s="69">
+      <c r="E24" s="62">
         <v>50</v>
       </c>
-      <c r="F24" s="67" t="s">
+      <c r="F24" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="G24" s="68"/>
+      <c r="G24" s="61"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" s="66" t="s">
+      <c r="A25" s="59" t="s">
         <v>201</v>
       </c>
-      <c r="B25" s="70" t="s">
+      <c r="B25" s="61" t="s">
         <v>134</v>
       </c>
-      <c r="C25" s="66" t="s">
+      <c r="C25" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="D25" s="68">
+      <c r="D25" s="61">
         <v>15.5</v>
       </c>
-      <c r="E25" s="69">
+      <c r="E25" s="62">
         <v>20</v>
       </c>
-      <c r="F25" s="67" t="s">
+      <c r="F25" s="60" t="s">
         <v>135</v>
       </c>
-      <c r="G25" s="68"/>
+      <c r="G25" s="61"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A26" s="66" t="s">
+      <c r="A26" s="59" t="s">
         <v>202</v>
       </c>
-      <c r="B26" s="70" t="s">
+      <c r="B26" s="61" t="s">
         <v>136</v>
       </c>
-      <c r="C26" s="66" t="s">
+      <c r="C26" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="D26" s="68">
+      <c r="D26" s="61">
         <v>12.75</v>
       </c>
-      <c r="E26" s="69">
+      <c r="E26" s="62">
         <v>40</v>
       </c>
-      <c r="F26" s="67" t="s">
+      <c r="F26" s="60" t="s">
         <v>135</v>
       </c>
-      <c r="G26" s="68"/>
+      <c r="G26" s="61"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A27" s="66" t="s">
+      <c r="A27" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="B27" s="70" t="s">
+      <c r="B27" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="C27" s="66" t="s">
+      <c r="C27" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="D27" s="68">
+      <c r="D27" s="61">
         <v>28</v>
       </c>
-      <c r="E27" s="69">
+      <c r="E27" s="62">
         <v>25</v>
       </c>
-      <c r="F27" s="67" t="s">
+      <c r="F27" s="60" t="s">
         <v>139</v>
       </c>
-      <c r="G27" s="68"/>
+      <c r="G27" s="61"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="B28" s="70" t="s">
+      <c r="B28" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="D28" s="68">
+      <c r="D28" s="61">
         <v>1.5</v>
       </c>
-      <c r="E28" s="69">
+      <c r="E28" s="62">
         <v>20</v>
       </c>
-      <c r="F28" s="67" t="s">
+      <c r="F28" s="60" t="s">
         <v>142</v>
       </c>
-      <c r="G28" s="68"/>
+      <c r="G28" s="61"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" s="66" t="s">
+      <c r="A29" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="B29" s="70" t="s">
+      <c r="B29" s="61" t="s">
         <v>143</v>
       </c>
-      <c r="C29" s="66" t="s">
+      <c r="C29" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="68">
+      <c r="D29" s="61">
         <v>8.25</v>
       </c>
-      <c r="E29" s="69">
+      <c r="E29" s="62">
         <v>50</v>
       </c>
-      <c r="F29" s="67" t="s">
+      <c r="F29" s="60" t="s">
         <v>142</v>
       </c>
-      <c r="G29" s="68"/>
+      <c r="G29" s="61"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="66" t="s">
+      <c r="A30" s="59" t="s">
         <v>206</v>
       </c>
-      <c r="B30" s="70" t="s">
+      <c r="B30" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="C30" s="66" t="s">
+      <c r="C30" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="D30" s="68">
+      <c r="D30" s="61">
         <v>6.75</v>
       </c>
-      <c r="E30" s="69">
+      <c r="E30" s="62">
         <v>15</v>
       </c>
-      <c r="F30" s="67" t="s">
+      <c r="F30" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="G30" s="68"/>
+      <c r="G30" s="61"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A31" s="66" t="s">
+      <c r="A31" s="59" t="s">
         <v>207</v>
       </c>
-      <c r="B31" s="70" t="s">
+      <c r="B31" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="C31" s="66" t="s">
+      <c r="C31" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="D31" s="68">
+      <c r="D31" s="61">
         <v>9.5</v>
       </c>
-      <c r="E31" s="69">
+      <c r="E31" s="62">
         <v>20</v>
       </c>
-      <c r="F31" s="67" t="s">
+      <c r="F31" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="G31" s="68"/>
+      <c r="G31" s="61"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A32" s="66" t="s">
+      <c r="A32" s="59" t="s">
         <v>208</v>
       </c>
-      <c r="B32" s="70" t="s">
+      <c r="B32" s="61" t="s">
         <v>147</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="68">
+      <c r="D32" s="61">
         <v>325</v>
       </c>
-      <c r="E32" s="69">
+      <c r="E32" s="62">
         <v>30</v>
       </c>
-      <c r="F32" s="67" t="s">
+      <c r="F32" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="G32" s="68"/>
+      <c r="G32" s="61"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A33" s="66" t="s">
+      <c r="A33" s="59" t="s">
         <v>209</v>
       </c>
-      <c r="B33" s="70" t="s">
+      <c r="B33" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="C33" s="66" t="s">
+      <c r="C33" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="68">
+      <c r="D33" s="61">
         <v>85</v>
       </c>
-      <c r="E33" s="69">
+      <c r="E33" s="62">
         <v>5</v>
       </c>
-      <c r="F33" s="67" t="s">
+      <c r="F33" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="G33" s="68"/>
+      <c r="G33" s="61"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A34" s="66" t="s">
+      <c r="A34" s="59" t="s">
         <v>210</v>
       </c>
-      <c r="B34" s="70" t="s">
+      <c r="B34" s="61" t="s">
         <v>151</v>
       </c>
-      <c r="C34" s="66" t="s">
+      <c r="C34" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="D34" s="68">
+      <c r="D34" s="61">
         <v>42</v>
       </c>
-      <c r="E34" s="69">
+      <c r="E34" s="62">
         <v>10</v>
       </c>
-      <c r="F34" s="67" t="s">
+      <c r="F34" s="60" t="s">
         <v>152</v>
       </c>
-      <c r="G34" s="68"/>
+      <c r="G34" s="61"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A35" s="66" t="s">
+      <c r="A35" s="59" t="s">
         <v>211</v>
       </c>
-      <c r="B35" s="70" t="s">
+      <c r="B35" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="D35" s="68">
+      <c r="D35" s="61">
         <v>28.5</v>
       </c>
-      <c r="E35" s="69">
+      <c r="E35" s="62">
         <v>10</v>
       </c>
-      <c r="F35" s="67" t="s">
+      <c r="F35" s="60" t="s">
         <v>152</v>
       </c>
-      <c r="G35" s="68"/>
+      <c r="G35" s="61"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A36" s="66" t="s">
+      <c r="A36" s="59" t="s">
         <v>212</v>
       </c>
-      <c r="B36" s="70" t="s">
+      <c r="B36" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="C36" s="66" t="s">
+      <c r="C36" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="D36" s="68">
+      <c r="D36" s="61">
         <v>675</v>
       </c>
-      <c r="E36" s="69">
+      <c r="E36" s="62">
         <v>10</v>
       </c>
-      <c r="F36" s="67" t="s">
+      <c r="F36" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="G36" s="68"/>
+      <c r="G36" s="61"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A37" s="66" t="s">
+      <c r="A37" s="59" t="s">
         <v>213</v>
       </c>
-      <c r="B37" s="70" t="s">
+      <c r="B37" s="61" t="s">
         <v>156</v>
       </c>
-      <c r="C37" s="66" t="s">
+      <c r="C37" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="D37" s="68">
+      <c r="D37" s="61">
         <v>12.5</v>
       </c>
-      <c r="E37" s="69">
+      <c r="E37" s="62">
         <v>3</v>
       </c>
-      <c r="F37" s="67" t="s">
+      <c r="F37" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="G37" s="68"/>
+      <c r="G37" s="61"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A38" s="66" t="s">
+      <c r="A38" s="59" t="s">
         <v>214</v>
       </c>
-      <c r="B38" s="70" t="s">
+      <c r="B38" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="C38" s="66" t="s">
+      <c r="C38" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="D38" s="68">
+      <c r="D38" s="61">
         <v>285</v>
       </c>
-      <c r="E38" s="69">
+      <c r="E38" s="62">
         <v>25</v>
       </c>
-      <c r="F38" s="67" t="s">
+      <c r="F38" s="60" t="s">
         <v>139</v>
       </c>
-      <c r="G38" s="68"/>
+      <c r="G38" s="61"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A39" s="66" t="s">
+      <c r="A39" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="B39" s="70" t="s">
+      <c r="B39" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="C39" s="66" t="s">
+      <c r="C39" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="D39" s="68">
+      <c r="D39" s="61">
         <v>45</v>
       </c>
-      <c r="E39" s="69">
+      <c r="E39" s="62">
         <v>5</v>
       </c>
-      <c r="F39" s="67" t="s">
+      <c r="F39" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="G39" s="68"/>
+      <c r="G39" s="61"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="59" t="s">
         <v>216</v>
       </c>
-      <c r="B40" s="70" t="s">
+      <c r="B40" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="C40" s="66" t="s">
+      <c r="C40" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="D40" s="68">
+      <c r="D40" s="61">
         <v>165</v>
       </c>
-      <c r="E40" s="69">
+      <c r="E40" s="62">
         <v>10</v>
       </c>
-      <c r="F40" s="67" t="s">
+      <c r="F40" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="G40" s="68"/>
+      <c r="G40" s="61"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A41" s="66" t="s">
+      <c r="A41" s="59" t="s">
         <v>217</v>
       </c>
-      <c r="B41" s="70" t="s">
+      <c r="B41" s="61" t="s">
         <v>163</v>
       </c>
-      <c r="C41" s="66" t="s">
+      <c r="C41" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="D41" s="68">
+      <c r="D41" s="61">
         <v>24.5</v>
       </c>
-      <c r="E41" s="69">
+      <c r="E41" s="62">
         <v>5</v>
       </c>
-      <c r="F41" s="67" t="s">
+      <c r="F41" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="G41" s="68"/>
+      <c r="G41" s="61"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A42" s="66" t="s">
+      <c r="A42" s="59" t="s">
         <v>218</v>
       </c>
-      <c r="B42" s="70" t="s">
+      <c r="B42" s="61" t="s">
         <v>165</v>
       </c>
-      <c r="C42" s="66" t="s">
+      <c r="C42" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="D42" s="68">
+      <c r="D42" s="61">
         <v>78</v>
       </c>
-      <c r="E42" s="69">
+      <c r="E42" s="62">
         <v>15</v>
       </c>
-      <c r="F42" s="67" t="s">
+      <c r="F42" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="G42" s="68"/>
+      <c r="G42" s="61"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A43" s="66" t="s">
+      <c r="A43" s="59" t="s">
         <v>219</v>
       </c>
-      <c r="B43" s="70" t="s">
+      <c r="B43" s="61" t="s">
         <v>166</v>
       </c>
-      <c r="C43" s="66" t="s">
+      <c r="C43" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="D43" s="68">
+      <c r="D43" s="61">
         <v>32</v>
       </c>
-      <c r="E43" s="69">
+      <c r="E43" s="62">
         <v>8</v>
       </c>
-      <c r="F43" s="67" t="s">
+      <c r="F43" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="G43" s="68"/>
+      <c r="G43" s="61"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A44" s="66" t="s">
+      <c r="A44" s="59" t="s">
         <v>220</v>
       </c>
-      <c r="B44" s="70" t="s">
+      <c r="B44" s="61" t="s">
         <v>167</v>
       </c>
-      <c r="C44" s="66" t="s">
+      <c r="C44" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="D44" s="68">
+      <c r="D44" s="61">
         <v>12.75</v>
       </c>
-      <c r="E44" s="69">
+      <c r="E44" s="62">
         <v>10</v>
       </c>
-      <c r="F44" s="67" t="s">
+      <c r="F44" s="60" t="s">
         <v>168</v>
       </c>
-      <c r="G44" s="68"/>
+      <c r="G44" s="61"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A45" s="66" t="s">
+      <c r="A45" s="59" t="s">
         <v>221</v>
       </c>
-      <c r="B45" s="70" t="s">
+      <c r="B45" s="61" t="s">
         <v>169</v>
       </c>
-      <c r="C45" s="66" t="s">
+      <c r="C45" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="D45" s="68">
+      <c r="D45" s="61">
         <v>18.5</v>
       </c>
-      <c r="E45" s="69">
+      <c r="E45" s="62">
         <v>25</v>
       </c>
-      <c r="F45" s="67" t="s">
+      <c r="F45" s="60" t="s">
         <v>168</v>
       </c>
-      <c r="G45" s="68"/>
+      <c r="G45" s="61"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A46" s="66" t="s">
+      <c r="A46" s="59" t="s">
         <v>222</v>
       </c>
-      <c r="B46" s="70" t="s">
+      <c r="B46" s="61" t="s">
         <v>170</v>
       </c>
-      <c r="C46" s="66" t="s">
+      <c r="C46" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="D46" s="68">
+      <c r="D46" s="61">
         <v>22</v>
       </c>
-      <c r="E46" s="69">
+      <c r="E46" s="62">
         <v>30</v>
       </c>
-      <c r="F46" s="67" t="s">
+      <c r="F46" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="G46" s="68"/>
+      <c r="G46" s="61"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A47" s="66" t="s">
+      <c r="A47" s="59" t="s">
         <v>223</v>
       </c>
-      <c r="B47" s="70" t="s">
+      <c r="B47" s="61" t="s">
         <v>171</v>
       </c>
-      <c r="C47" s="66" t="s">
+      <c r="C47" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="D47" s="68">
+      <c r="D47" s="61">
         <v>18.75</v>
       </c>
-      <c r="E47" s="69">
+      <c r="E47" s="62">
         <v>10</v>
       </c>
-      <c r="F47" s="67" t="s">
+      <c r="F47" s="60" t="s">
         <v>173</v>
       </c>
-      <c r="G47" s="68"/>
+      <c r="G47" s="61"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A48" s="66" t="s">
+      <c r="A48" s="59" t="s">
         <v>224</v>
       </c>
-      <c r="B48" s="70" t="s">
+      <c r="B48" s="61" t="s">
         <v>174</v>
       </c>
-      <c r="C48" s="66" t="s">
+      <c r="C48" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="D48" s="68">
+      <c r="D48" s="61">
         <v>24.5</v>
       </c>
-      <c r="E48" s="69">
+      <c r="E48" s="62">
         <v>15</v>
       </c>
-      <c r="F48" s="67" t="s">
+      <c r="F48" s="60" t="s">
         <v>173</v>
       </c>
-      <c r="G48" s="68"/>
+      <c r="G48" s="61"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A49" s="66" t="s">
+      <c r="A49" s="59" t="s">
         <v>225</v>
       </c>
-      <c r="B49" s="70" t="s">
+      <c r="B49" s="61" t="s">
         <v>175</v>
       </c>
-      <c r="C49" s="66" t="s">
+      <c r="C49" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="D49" s="68">
+      <c r="D49" s="61">
         <v>42</v>
       </c>
-      <c r="E49" s="69">
+      <c r="E49" s="62">
         <v>20</v>
       </c>
-      <c r="F49" s="67" t="s">
+      <c r="F49" s="60" t="s">
         <v>176</v>
       </c>
-      <c r="G49" s="68"/>
+      <c r="G49" s="61"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A50" s="66" t="s">
+      <c r="A50" s="59" t="s">
         <v>226</v>
       </c>
-      <c r="B50" s="70" t="s">
+      <c r="B50" s="61" t="s">
         <v>177</v>
       </c>
-      <c r="C50" s="66" t="s">
+      <c r="C50" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="D50" s="68">
+      <c r="D50" s="61">
         <v>35</v>
       </c>
-      <c r="E50" s="69">
+      <c r="E50" s="62">
         <v>10</v>
       </c>
-      <c r="F50" s="67" t="s">
+      <c r="F50" s="60" t="s">
         <v>178</v>
       </c>
-      <c r="G50" s="68"/>
+      <c r="G50" s="61"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A51" s="66" t="s">
+      <c r="A51" s="59" t="s">
         <v>227</v>
       </c>
-      <c r="B51" s="70" t="s">
+      <c r="B51" s="61" t="s">
         <v>179</v>
       </c>
-      <c r="C51" s="66" t="s">
+      <c r="C51" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="D51" s="68">
+      <c r="D51" s="61">
         <v>28.5</v>
       </c>
-      <c r="E51" s="69">
+      <c r="E51" s="62">
         <v>15</v>
       </c>
-      <c r="F51" s="67" t="s">
+      <c r="F51" s="60" t="s">
         <v>178</v>
       </c>
-      <c r="G51" s="68"/>
+      <c r="G51" s="61"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A52" s="66" t="s">
+      <c r="A52" s="59" t="s">
         <v>228</v>
       </c>
-      <c r="B52" s="70" t="s">
+      <c r="B52" s="61" t="s">
         <v>180</v>
       </c>
-      <c r="C52" s="66" t="s">
+      <c r="C52" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="D52" s="68">
+      <c r="D52" s="61">
         <v>19.75</v>
       </c>
-      <c r="E52" s="69">
+      <c r="E52" s="62">
         <v>10</v>
       </c>
-      <c r="F52" s="67" t="s">
+      <c r="F52" s="60" t="s">
         <v>181</v>
       </c>
-      <c r="G52" s="68"/>
+      <c r="G52" s="61"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A53" s="66" t="s">
+      <c r="A53" s="59" t="s">
         <v>229</v>
       </c>
-      <c r="B53" s="70" t="s">
+      <c r="B53" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="C53" s="66" t="s">
+      <c r="C53" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="D53" s="68">
+      <c r="D53" s="61">
         <v>16.5</v>
       </c>
-      <c r="E53" s="69">
+      <c r="E53" s="62">
         <v>25</v>
       </c>
-      <c r="F53" s="67" t="s">
+      <c r="F53" s="60" t="s">
         <v>181</v>
       </c>
-      <c r="G53" s="68"/>
+      <c r="G53" s="61"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A54" s="66" t="s">
+      <c r="A54" s="59" t="s">
         <v>230</v>
       </c>
-      <c r="B54" s="70" t="s">
+      <c r="B54" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="C54" s="66" t="s">
+      <c r="C54" s="59" t="s">
         <v>184</v>
       </c>
-      <c r="D54" s="68">
+      <c r="D54" s="61">
         <v>45</v>
       </c>
-      <c r="E54" s="69">
+      <c r="E54" s="62">
         <v>20</v>
       </c>
-      <c r="F54" s="67" t="s">
+      <c r="F54" s="60" t="s">
         <v>185</v>
       </c>
-      <c r="G54" s="68"/>
+      <c r="G54" s="61"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A55" s="66" t="s">
+      <c r="A55" s="59" t="s">
         <v>231</v>
       </c>
-      <c r="B55" s="70" t="s">
+      <c r="B55" s="61" t="s">
         <v>186</v>
       </c>
-      <c r="C55" s="66" t="s">
+      <c r="C55" s="59" t="s">
         <v>184</v>
       </c>
-      <c r="D55" s="68">
+      <c r="D55" s="61">
         <v>185</v>
       </c>
-      <c r="E55" s="69">
+      <c r="E55" s="62">
         <v>10</v>
       </c>
-      <c r="F55" s="67" t="s">
+      <c r="F55" s="60" t="s">
         <v>185</v>
       </c>
-      <c r="G55" s="68"/>
+      <c r="G55" s="61"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A56" s="66" t="s">
+      <c r="A56" s="59" t="s">
         <v>232</v>
       </c>
-      <c r="B56" s="70" t="s">
+      <c r="B56" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="C56" s="66" t="s">
+      <c r="C56" s="59" t="s">
         <v>184</v>
       </c>
-      <c r="D56" s="68">
+      <c r="D56" s="61">
         <v>38.5</v>
       </c>
-      <c r="E56" s="69">
+      <c r="E56" s="62">
         <v>5</v>
       </c>
-      <c r="F56" s="67" t="s">
+      <c r="F56" s="60" t="s">
         <v>188</v>
       </c>
-      <c r="G56" s="68"/>
+      <c r="G56" s="61"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A57" s="66" t="s">
+      <c r="A57" s="59" t="s">
         <v>233</v>
       </c>
-      <c r="B57" s="70" t="s">
+      <c r="B57" s="61" t="s">
         <v>189</v>
       </c>
-      <c r="C57" s="66" t="s">
+      <c r="C57" s="59" t="s">
         <v>184</v>
       </c>
-      <c r="D57" s="68">
+      <c r="D57" s="61">
         <v>0.18</v>
       </c>
-      <c r="E57" s="69">
+      <c r="E57" s="62">
         <v>15</v>
       </c>
-      <c r="F57" s="67" t="s">
+      <c r="F57" s="60" t="s">
         <v>190</v>
       </c>
-      <c r="G57" s="68"/>
+      <c r="G57" s="61"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A58" s="66" t="s">
+      <c r="A58" s="59" t="s">
         <v>234</v>
       </c>
-      <c r="B58" s="70" t="s">
+      <c r="B58" s="61" t="s">
         <v>191</v>
       </c>
-      <c r="C58" s="66" t="s">
+      <c r="C58" s="59" t="s">
         <v>192</v>
       </c>
-      <c r="D58" s="68">
+      <c r="D58" s="61">
         <v>0.25</v>
       </c>
-      <c r="E58" s="69">
+      <c r="E58" s="62">
         <v>100</v>
       </c>
-      <c r="F58" s="67" t="s">
+      <c r="F58" s="60" t="s">
         <v>193</v>
       </c>
-      <c r="G58" s="68"/>
+      <c r="G58" s="61"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A59" s="66" t="s">
+      <c r="A59" s="59" t="s">
         <v>235</v>
       </c>
-      <c r="B59" s="70" t="s">
+      <c r="B59" s="61" t="s">
         <v>194</v>
       </c>
-      <c r="C59" s="66" t="s">
+      <c r="C59" s="59" t="s">
         <v>192</v>
       </c>
-      <c r="D59" s="68">
+      <c r="D59" s="61">
         <v>0.15</v>
       </c>
-      <c r="E59" s="69">
+      <c r="E59" s="62">
         <v>100</v>
       </c>
-      <c r="F59" s="67" t="s">
+      <c r="F59" s="60" t="s">
         <v>193</v>
       </c>
-      <c r="G59" s="68"/>
+      <c r="G59" s="61"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A60" s="66" t="s">
+      <c r="A60" s="59" t="s">
         <v>236</v>
       </c>
-      <c r="B60" s="70" t="s">
+      <c r="B60" s="61" t="s">
         <v>195</v>
       </c>
-      <c r="C60" s="66" t="s">
+      <c r="C60" s="59" t="s">
         <v>192</v>
       </c>
-      <c r="D60" s="68">
+      <c r="D60" s="61">
         <v>0.12</v>
       </c>
-      <c r="E60" s="69">
+      <c r="E60" s="62">
         <v>100</v>
       </c>
-      <c r="F60" s="67" t="s">
+      <c r="F60" s="60" t="s">
         <v>196</v>
       </c>
-      <c r="G60" s="68"/>
+      <c r="G60" s="61"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A61" s="66" t="s">
+      <c r="A61" s="59" t="s">
         <v>237</v>
       </c>
-      <c r="B61" s="70" t="s">
+      <c r="B61" s="61" t="s">
         <v>197</v>
       </c>
-      <c r="C61" s="66" t="s">
+      <c r="C61" s="59" t="s">
         <v>192</v>
       </c>
       <c r="D61">
         <v>8.5</v>
       </c>
-      <c r="E61" s="69">
+      <c r="E61" s="62">
         <v>100</v>
       </c>
-      <c r="F61" s="67" t="s">
+      <c r="F61" s="60" t="s">
         <v>196</v>
       </c>
-      <c r="G61" s="68"/>
+      <c r="G61" s="61"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -5731,8 +5803,8 @@
   <cols>
     <col min="2" max="2" width="9.9296875" customWidth="1"/>
     <col min="3" max="3" width="10.9296875" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" style="73" customWidth="1"/>
-    <col min="5" max="5" width="12.46484375" style="73" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="65" customWidth="1"/>
+    <col min="5" max="5" width="12.46484375" style="65" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5746,10 +5818,10 @@
       <c r="C1" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="73" t="s">
+      <c r="D1" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="73" t="s">
+      <c r="E1" s="65" t="s">
         <v>240</v>
       </c>
       <c r="F1" t="s">
@@ -5760,19 +5832,19 @@
       <c r="A2" t="s">
         <v>241</v>
       </c>
-      <c r="B2" s="71">
+      <c r="B2" s="63">
         <v>45900</v>
       </c>
       <c r="C2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="74">
+      <c r="E2" s="66">
         <v>50</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="F2" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -5780,19 +5852,19 @@
       <c r="A3" t="s">
         <v>242</v>
       </c>
-      <c r="B3" s="71">
+      <c r="B3" s="63">
         <v>45900</v>
       </c>
       <c r="C3" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="74">
+      <c r="E3" s="66">
         <v>30</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -5800,19 +5872,19 @@
       <c r="A4" t="s">
         <v>243</v>
       </c>
-      <c r="B4" s="71">
+      <c r="B4" s="63">
         <v>45900</v>
       </c>
       <c r="C4" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="75" t="s">
+      <c r="D4" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="74">
+      <c r="E4" s="66">
         <v>40</v>
       </c>
-      <c r="F4" s="72" t="s">
+      <c r="F4" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -5820,19 +5892,19 @@
       <c r="A5" t="s">
         <v>244</v>
       </c>
-      <c r="B5" s="71">
+      <c r="B5" s="63">
         <v>45900</v>
       </c>
       <c r="C5" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="75" t="s">
+      <c r="D5" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="74">
+      <c r="E5" s="66">
         <v>12</v>
       </c>
-      <c r="F5" s="72" t="s">
+      <c r="F5" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -5840,19 +5912,19 @@
       <c r="A6" t="s">
         <v>245</v>
       </c>
-      <c r="B6" s="71">
+      <c r="B6" s="63">
         <v>45900</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="74">
+      <c r="E6" s="66">
         <v>20</v>
       </c>
-      <c r="F6" s="72" t="s">
+      <c r="F6" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -5860,19 +5932,19 @@
       <c r="A7" t="s">
         <v>246</v>
       </c>
-      <c r="B7" s="71">
+      <c r="B7" s="63">
         <v>45900</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="75" t="s">
+      <c r="D7" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="74">
+      <c r="E7" s="66">
         <v>14</v>
       </c>
-      <c r="F7" s="72" t="s">
+      <c r="F7" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -5880,19 +5952,19 @@
       <c r="A8" t="s">
         <v>247</v>
       </c>
-      <c r="B8" s="71">
+      <c r="B8" s="63">
         <v>45900</v>
       </c>
       <c r="C8" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="74">
+      <c r="E8" s="66">
         <v>25</v>
       </c>
-      <c r="F8" s="72" t="s">
+      <c r="F8" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -5900,19 +5972,19 @@
       <c r="A9" t="s">
         <v>248</v>
       </c>
-      <c r="B9" s="71">
+      <c r="B9" s="63">
         <v>45900</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="75" t="s">
+      <c r="D9" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="74">
+      <c r="E9" s="66">
         <v>30</v>
       </c>
-      <c r="F9" s="72" t="s">
+      <c r="F9" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -5920,19 +5992,19 @@
       <c r="A10" t="s">
         <v>249</v>
       </c>
-      <c r="B10" s="71">
+      <c r="B10" s="63">
         <v>45900</v>
       </c>
       <c r="C10" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="75" t="s">
+      <c r="D10" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="74">
+      <c r="E10" s="66">
         <v>10</v>
       </c>
-      <c r="F10" s="72" t="s">
+      <c r="F10" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -5940,19 +6012,19 @@
       <c r="A11" t="s">
         <v>250</v>
       </c>
-      <c r="B11" s="71">
+      <c r="B11" s="63">
         <v>45900</v>
       </c>
       <c r="C11" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="75" t="s">
+      <c r="D11" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="74">
+      <c r="E11" s="66">
         <v>35</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="F11" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -5960,19 +6032,19 @@
       <c r="A12" t="s">
         <v>251</v>
       </c>
-      <c r="B12" s="71">
+      <c r="B12" s="63">
         <v>45900</v>
       </c>
       <c r="C12" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="75" t="s">
+      <c r="D12" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="74">
+      <c r="E12" s="66">
         <v>25</v>
       </c>
-      <c r="F12" s="72" t="s">
+      <c r="F12" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -5980,19 +6052,19 @@
       <c r="A13" t="s">
         <v>252</v>
       </c>
-      <c r="B13" s="71">
+      <c r="B13" s="63">
         <v>45900</v>
       </c>
       <c r="C13" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="75" t="s">
+      <c r="D13" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="74">
+      <c r="E13" s="66">
         <v>18</v>
       </c>
-      <c r="F13" s="72" t="s">
+      <c r="F13" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6000,19 +6072,19 @@
       <c r="A14" t="s">
         <v>253</v>
       </c>
-      <c r="B14" s="71">
+      <c r="B14" s="63">
         <v>45900</v>
       </c>
       <c r="C14" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="75" t="s">
+      <c r="D14" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="74">
+      <c r="E14" s="66">
         <v>60</v>
       </c>
-      <c r="F14" s="72" t="s">
+      <c r="F14" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6020,19 +6092,19 @@
       <c r="A15" t="s">
         <v>254</v>
       </c>
-      <c r="B15" s="71">
+      <c r="B15" s="63">
         <v>45900</v>
       </c>
       <c r="C15" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="75" t="s">
+      <c r="D15" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="74">
+      <c r="E15" s="66">
         <v>50</v>
       </c>
-      <c r="F15" s="72" t="s">
+      <c r="F15" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6040,19 +6112,19 @@
       <c r="A16" t="s">
         <v>255</v>
       </c>
-      <c r="B16" s="71">
+      <c r="B16" s="63">
         <v>45900</v>
       </c>
       <c r="C16" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="75" t="s">
+      <c r="D16" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="74">
+      <c r="E16" s="66">
         <v>35</v>
       </c>
-      <c r="F16" s="72" t="s">
+      <c r="F16" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6060,19 +6132,19 @@
       <c r="A17" t="s">
         <v>256</v>
       </c>
-      <c r="B17" s="71">
+      <c r="B17" s="63">
         <v>45900</v>
       </c>
       <c r="C17" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="75" t="s">
+      <c r="D17" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="74">
+      <c r="E17" s="66">
         <v>20</v>
       </c>
-      <c r="F17" s="72" t="s">
+      <c r="F17" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6080,19 +6152,19 @@
       <c r="A18" t="s">
         <v>257</v>
       </c>
-      <c r="B18" s="71">
+      <c r="B18" s="63">
         <v>45900</v>
       </c>
       <c r="C18" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="75" t="s">
+      <c r="D18" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="74">
+      <c r="E18" s="66">
         <v>15</v>
       </c>
-      <c r="F18" s="72" t="s">
+      <c r="F18" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6100,19 +6172,19 @@
       <c r="A19" t="s">
         <v>258</v>
       </c>
-      <c r="B19" s="71">
+      <c r="B19" s="63">
         <v>45900</v>
       </c>
       <c r="C19" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="75" t="s">
+      <c r="D19" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="74">
+      <c r="E19" s="66">
         <v>10</v>
       </c>
-      <c r="F19" s="72" t="s">
+      <c r="F19" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6120,19 +6192,19 @@
       <c r="A20" t="s">
         <v>259</v>
       </c>
-      <c r="B20" s="71">
+      <c r="B20" s="63">
         <v>45900</v>
       </c>
       <c r="C20" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="75" t="s">
+      <c r="D20" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="74">
+      <c r="E20" s="66">
         <v>25</v>
       </c>
-      <c r="F20" s="72" t="s">
+      <c r="F20" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6140,19 +6212,19 @@
       <c r="A21" t="s">
         <v>260</v>
       </c>
-      <c r="B21" s="71">
+      <c r="B21" s="63">
         <v>45900</v>
       </c>
       <c r="C21" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="75" t="s">
+      <c r="D21" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="74">
+      <c r="E21" s="66">
         <v>25</v>
       </c>
-      <c r="F21" s="72" t="s">
+      <c r="F21" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6160,19 +6232,19 @@
       <c r="A22" t="s">
         <v>261</v>
       </c>
-      <c r="B22" s="71">
+      <c r="B22" s="63">
         <v>45900</v>
       </c>
       <c r="C22" t="s">
         <v>198</v>
       </c>
-      <c r="D22" s="75" t="s">
+      <c r="D22" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E22" s="74">
+      <c r="E22" s="66">
         <v>3</v>
       </c>
-      <c r="F22" s="72" t="s">
+      <c r="F22" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6180,19 +6252,19 @@
       <c r="A23" t="s">
         <v>262</v>
       </c>
-      <c r="B23" s="71">
+      <c r="B23" s="63">
         <v>45900</v>
       </c>
       <c r="C23" t="s">
         <v>199</v>
       </c>
-      <c r="D23" s="75" t="s">
+      <c r="D23" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E23" s="74">
+      <c r="E23" s="66">
         <v>10</v>
       </c>
-      <c r="F23" s="72" t="s">
+      <c r="F23" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6200,19 +6272,19 @@
       <c r="A24" t="s">
         <v>263</v>
       </c>
-      <c r="B24" s="71">
+      <c r="B24" s="63">
         <v>45900</v>
       </c>
       <c r="C24" t="s">
         <v>200</v>
       </c>
-      <c r="D24" s="75" t="s">
+      <c r="D24" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="74">
+      <c r="E24" s="66">
         <v>1</v>
       </c>
-      <c r="F24" s="72" t="s">
+      <c r="F24" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6220,19 +6292,19 @@
       <c r="A25" t="s">
         <v>264</v>
       </c>
-      <c r="B25" s="71">
+      <c r="B25" s="63">
         <v>45900</v>
       </c>
       <c r="C25" t="s">
         <v>201</v>
       </c>
-      <c r="D25" s="75" t="s">
+      <c r="D25" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="74">
+      <c r="E25" s="66">
         <v>1</v>
       </c>
-      <c r="F25" s="72" t="s">
+      <c r="F25" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6240,19 +6312,19 @@
       <c r="A26" t="s">
         <v>265</v>
       </c>
-      <c r="B26" s="71">
+      <c r="B26" s="63">
         <v>45900</v>
       </c>
       <c r="C26" t="s">
         <v>202</v>
       </c>
-      <c r="D26" s="75" t="s">
+      <c r="D26" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E26" s="74">
+      <c r="E26" s="66">
         <v>1</v>
       </c>
-      <c r="F26" s="72" t="s">
+      <c r="F26" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6260,19 +6332,19 @@
       <c r="A27" t="s">
         <v>266</v>
       </c>
-      <c r="B27" s="71">
+      <c r="B27" s="63">
         <v>45900</v>
       </c>
       <c r="C27" t="s">
         <v>203</v>
       </c>
-      <c r="D27" s="75" t="s">
+      <c r="D27" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="74">
+      <c r="E27" s="66">
         <v>1</v>
       </c>
-      <c r="F27" s="72" t="s">
+      <c r="F27" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6280,19 +6352,19 @@
       <c r="A28" t="s">
         <v>267</v>
       </c>
-      <c r="B28" s="71">
+      <c r="B28" s="63">
         <v>45900</v>
       </c>
       <c r="C28" t="s">
         <v>204</v>
       </c>
-      <c r="D28" s="75" t="s">
+      <c r="D28" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="74">
+      <c r="E28" s="66">
         <v>1</v>
       </c>
-      <c r="F28" s="72" t="s">
+      <c r="F28" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6300,19 +6372,19 @@
       <c r="A29" t="s">
         <v>268</v>
       </c>
-      <c r="B29" s="71">
+      <c r="B29" s="63">
         <v>45900</v>
       </c>
       <c r="C29" t="s">
         <v>205</v>
       </c>
-      <c r="D29" s="75" t="s">
+      <c r="D29" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E29" s="74">
+      <c r="E29" s="66">
         <v>2</v>
       </c>
-      <c r="F29" s="72" t="s">
+      <c r="F29" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6320,19 +6392,19 @@
       <c r="A30" t="s">
         <v>269</v>
       </c>
-      <c r="B30" s="71">
+      <c r="B30" s="63">
         <v>45900</v>
       </c>
       <c r="C30" t="s">
         <v>206</v>
       </c>
-      <c r="D30" s="75" t="s">
+      <c r="D30" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E30" s="74">
+      <c r="E30" s="66">
         <v>1</v>
       </c>
-      <c r="F30" s="72" t="s">
+      <c r="F30" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6340,19 +6412,19 @@
       <c r="A31" t="s">
         <v>270</v>
       </c>
-      <c r="B31" s="71">
+      <c r="B31" s="63">
         <v>45900</v>
       </c>
       <c r="C31" t="s">
         <v>207</v>
       </c>
-      <c r="D31" s="75" t="s">
+      <c r="D31" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E31" s="74">
+      <c r="E31" s="66">
         <v>3</v>
       </c>
-      <c r="F31" s="72" t="s">
+      <c r="F31" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6360,19 +6432,19 @@
       <c r="A32" t="s">
         <v>271</v>
       </c>
-      <c r="B32" s="71">
+      <c r="B32" s="63">
         <v>45900</v>
       </c>
       <c r="C32" t="s">
         <v>208</v>
       </c>
-      <c r="D32" s="75" t="s">
+      <c r="D32" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E32" s="74">
+      <c r="E32" s="66">
         <v>1</v>
       </c>
-      <c r="F32" s="72" t="s">
+      <c r="F32" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6380,19 +6452,19 @@
       <c r="A33" t="s">
         <v>272</v>
       </c>
-      <c r="B33" s="71">
+      <c r="B33" s="63">
         <v>45900</v>
       </c>
       <c r="C33" t="s">
         <v>209</v>
       </c>
-      <c r="D33" s="75" t="s">
+      <c r="D33" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E33" s="74">
+      <c r="E33" s="66">
         <v>1</v>
       </c>
-      <c r="F33" s="72" t="s">
+      <c r="F33" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6400,19 +6472,19 @@
       <c r="A34" t="s">
         <v>273</v>
       </c>
-      <c r="B34" s="71">
+      <c r="B34" s="63">
         <v>45900</v>
       </c>
       <c r="C34" t="s">
         <v>210</v>
       </c>
-      <c r="D34" s="75" t="s">
+      <c r="D34" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E34" s="74">
+      <c r="E34" s="66">
         <v>2</v>
       </c>
-      <c r="F34" s="72" t="s">
+      <c r="F34" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6420,19 +6492,19 @@
       <c r="A35" t="s">
         <v>274</v>
       </c>
-      <c r="B35" s="71">
+      <c r="B35" s="63">
         <v>45900</v>
       </c>
       <c r="C35" t="s">
         <v>211</v>
       </c>
-      <c r="D35" s="75" t="s">
+      <c r="D35" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E35" s="74">
+      <c r="E35" s="66">
         <v>6</v>
       </c>
-      <c r="F35" s="72" t="s">
+      <c r="F35" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6440,19 +6512,19 @@
       <c r="A36" t="s">
         <v>275</v>
       </c>
-      <c r="B36" s="71">
+      <c r="B36" s="63">
         <v>45900</v>
       </c>
       <c r="C36" t="s">
         <v>212</v>
       </c>
-      <c r="D36" s="75" t="s">
+      <c r="D36" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E36" s="74">
+      <c r="E36" s="66">
         <v>2</v>
       </c>
-      <c r="F36" s="72" t="s">
+      <c r="F36" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6460,19 +6532,19 @@
       <c r="A37" t="s">
         <v>276</v>
       </c>
-      <c r="B37" s="71">
+      <c r="B37" s="63">
         <v>45900</v>
       </c>
       <c r="C37" t="s">
         <v>213</v>
       </c>
-      <c r="D37" s="75" t="s">
+      <c r="D37" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="74">
+      <c r="E37" s="66">
         <v>2</v>
       </c>
-      <c r="F37" s="72" t="s">
+      <c r="F37" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6480,19 +6552,19 @@
       <c r="A38" t="s">
         <v>277</v>
       </c>
-      <c r="B38" s="71">
+      <c r="B38" s="63">
         <v>45900</v>
       </c>
       <c r="C38" t="s">
         <v>214</v>
       </c>
-      <c r="D38" s="75" t="s">
+      <c r="D38" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E38" s="74">
+      <c r="E38" s="66">
         <v>2</v>
       </c>
-      <c r="F38" s="72" t="s">
+      <c r="F38" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6500,19 +6572,19 @@
       <c r="A39" t="s">
         <v>278</v>
       </c>
-      <c r="B39" s="71">
+      <c r="B39" s="63">
         <v>45900</v>
       </c>
       <c r="C39" t="s">
         <v>215</v>
       </c>
-      <c r="D39" s="75" t="s">
+      <c r="D39" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E39" s="74">
+      <c r="E39" s="66">
         <v>5</v>
       </c>
-      <c r="F39" s="72" t="s">
+      <c r="F39" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6520,19 +6592,19 @@
       <c r="A40" t="s">
         <v>279</v>
       </c>
-      <c r="B40" s="71">
+      <c r="B40" s="63">
         <v>45900</v>
       </c>
       <c r="C40" t="s">
         <v>216</v>
       </c>
-      <c r="D40" s="75" t="s">
+      <c r="D40" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E40" s="74">
+      <c r="E40" s="66">
         <v>2</v>
       </c>
-      <c r="F40" s="72" t="s">
+      <c r="F40" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6540,19 +6612,19 @@
       <c r="A41" t="s">
         <v>280</v>
       </c>
-      <c r="B41" s="71">
+      <c r="B41" s="63">
         <v>45900</v>
       </c>
       <c r="C41" t="s">
         <v>217</v>
       </c>
-      <c r="D41" s="75" t="s">
+      <c r="D41" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E41" s="74">
+      <c r="E41" s="66">
         <v>3</v>
       </c>
-      <c r="F41" s="72" t="s">
+      <c r="F41" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6560,19 +6632,19 @@
       <c r="A42" t="s">
         <v>281</v>
       </c>
-      <c r="B42" s="71">
+      <c r="B42" s="63">
         <v>45900</v>
       </c>
       <c r="C42" t="s">
         <v>218</v>
       </c>
-      <c r="D42" s="75" t="s">
+      <c r="D42" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E42" s="74">
+      <c r="E42" s="66">
         <v>2</v>
       </c>
-      <c r="F42" s="72" t="s">
+      <c r="F42" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6580,19 +6652,19 @@
       <c r="A43" t="s">
         <v>282</v>
       </c>
-      <c r="B43" s="71">
+      <c r="B43" s="63">
         <v>45900</v>
       </c>
       <c r="C43" t="s">
         <v>219</v>
       </c>
-      <c r="D43" s="75" t="s">
+      <c r="D43" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E43" s="74">
+      <c r="E43" s="66">
         <v>3</v>
       </c>
-      <c r="F43" s="72" t="s">
+      <c r="F43" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6600,19 +6672,19 @@
       <c r="A44" t="s">
         <v>283</v>
       </c>
-      <c r="B44" s="71">
+      <c r="B44" s="63">
         <v>45900</v>
       </c>
       <c r="C44" t="s">
         <v>220</v>
       </c>
-      <c r="D44" s="75" t="s">
+      <c r="D44" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E44" s="74">
+      <c r="E44" s="66">
         <v>3</v>
       </c>
-      <c r="F44" s="72" t="s">
+      <c r="F44" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6620,19 +6692,19 @@
       <c r="A45" t="s">
         <v>284</v>
       </c>
-      <c r="B45" s="71">
+      <c r="B45" s="63">
         <v>45900</v>
       </c>
       <c r="C45" t="s">
         <v>221</v>
       </c>
-      <c r="D45" s="75" t="s">
+      <c r="D45" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E45" s="74">
+      <c r="E45" s="66">
         <v>4</v>
       </c>
-      <c r="F45" s="72" t="s">
+      <c r="F45" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6640,19 +6712,19 @@
       <c r="A46" t="s">
         <v>285</v>
       </c>
-      <c r="B46" s="71">
+      <c r="B46" s="63">
         <v>45900</v>
       </c>
       <c r="C46" t="s">
         <v>222</v>
       </c>
-      <c r="D46" s="75" t="s">
+      <c r="D46" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E46" s="74">
+      <c r="E46" s="66">
         <v>4</v>
       </c>
-      <c r="F46" s="72" t="s">
+      <c r="F46" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6660,19 +6732,19 @@
       <c r="A47" t="s">
         <v>286</v>
       </c>
-      <c r="B47" s="71">
+      <c r="B47" s="63">
         <v>45900</v>
       </c>
       <c r="C47" t="s">
         <v>223</v>
       </c>
-      <c r="D47" s="75" t="s">
+      <c r="D47" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E47" s="74">
+      <c r="E47" s="66">
         <v>4</v>
       </c>
-      <c r="F47" s="72" t="s">
+      <c r="F47" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6680,19 +6752,19 @@
       <c r="A48" t="s">
         <v>287</v>
       </c>
-      <c r="B48" s="71">
+      <c r="B48" s="63">
         <v>45900</v>
       </c>
       <c r="C48" t="s">
         <v>224</v>
       </c>
-      <c r="D48" s="75" t="s">
+      <c r="D48" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E48" s="74">
+      <c r="E48" s="66">
         <v>8</v>
       </c>
-      <c r="F48" s="72" t="s">
+      <c r="F48" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6700,19 +6772,19 @@
       <c r="A49" t="s">
         <v>288</v>
       </c>
-      <c r="B49" s="71">
+      <c r="B49" s="63">
         <v>45900</v>
       </c>
       <c r="C49" t="s">
         <v>225</v>
       </c>
-      <c r="D49" s="75" t="s">
+      <c r="D49" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E49" s="74">
+      <c r="E49" s="66">
         <v>2</v>
       </c>
-      <c r="F49" s="72" t="s">
+      <c r="F49" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6720,19 +6792,19 @@
       <c r="A50" t="s">
         <v>289</v>
       </c>
-      <c r="B50" s="71">
+      <c r="B50" s="63">
         <v>45900</v>
       </c>
       <c r="C50" t="s">
         <v>226</v>
       </c>
-      <c r="D50" s="75" t="s">
+      <c r="D50" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E50" s="74">
+      <c r="E50" s="66">
         <v>2</v>
       </c>
-      <c r="F50" s="72" t="s">
+      <c r="F50" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6740,19 +6812,19 @@
       <c r="A51" t="s">
         <v>290</v>
       </c>
-      <c r="B51" s="71">
+      <c r="B51" s="63">
         <v>45900</v>
       </c>
       <c r="C51" t="s">
         <v>227</v>
       </c>
-      <c r="D51" s="75" t="s">
+      <c r="D51" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E51" s="74">
+      <c r="E51" s="66">
         <v>3</v>
       </c>
-      <c r="F51" s="72" t="s">
+      <c r="F51" s="64" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6760,19 +6832,19 @@
       <c r="A52" t="s">
         <v>291</v>
       </c>
-      <c r="B52" s="71">
+      <c r="B52" s="63">
         <v>45901</v>
       </c>
       <c r="C52" t="s">
         <v>228</v>
       </c>
-      <c r="D52" s="75" t="s">
+      <c r="D52" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E52" s="74">
+      <c r="E52" s="66">
         <v>-2</v>
       </c>
-      <c r="F52" s="72" t="s">
+      <c r="F52" s="64" t="s">
         <v>302</v>
       </c>
     </row>
@@ -6780,19 +6852,19 @@
       <c r="A53" t="s">
         <v>292</v>
       </c>
-      <c r="B53" s="71">
+      <c r="B53" s="63">
         <v>45901</v>
       </c>
       <c r="C53" t="s">
         <v>229</v>
       </c>
-      <c r="D53" s="75" t="s">
+      <c r="D53" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E53" s="74">
+      <c r="E53" s="66">
         <v>-5</v>
       </c>
-      <c r="F53" s="72" t="s">
+      <c r="F53" s="64" t="s">
         <v>302</v>
       </c>
     </row>
@@ -6800,19 +6872,19 @@
       <c r="A54" t="s">
         <v>293</v>
       </c>
-      <c r="B54" s="71">
+      <c r="B54" s="63">
         <v>45901</v>
       </c>
       <c r="C54" t="s">
         <v>230</v>
       </c>
-      <c r="D54" s="75" t="s">
+      <c r="D54" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E54" s="74">
+      <c r="E54" s="66">
         <v>20</v>
       </c>
-      <c r="F54" s="72" t="s">
+      <c r="F54" s="64" t="s">
         <v>303</v>
       </c>
     </row>
@@ -6820,19 +6892,19 @@
       <c r="A55" t="s">
         <v>294</v>
       </c>
-      <c r="B55" s="71">
+      <c r="B55" s="63">
         <v>45902</v>
       </c>
       <c r="C55" t="s">
         <v>231</v>
       </c>
-      <c r="D55" s="75" t="s">
+      <c r="D55" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E55" s="74">
+      <c r="E55" s="66">
         <v>15</v>
       </c>
-      <c r="F55" s="72" t="s">
+      <c r="F55" s="64" t="s">
         <v>303</v>
       </c>
     </row>
@@ -6840,19 +6912,19 @@
       <c r="A56" t="s">
         <v>295</v>
       </c>
-      <c r="B56" s="71">
+      <c r="B56" s="63">
         <v>45902</v>
       </c>
       <c r="C56" t="s">
         <v>232</v>
       </c>
-      <c r="D56" s="75" t="s">
+      <c r="D56" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E56" s="74">
+      <c r="E56" s="66">
         <v>-3</v>
       </c>
-      <c r="F56" s="72" t="s">
+      <c r="F56" s="64" t="s">
         <v>302</v>
       </c>
     </row>
@@ -6860,19 +6932,19 @@
       <c r="A57" t="s">
         <v>296</v>
       </c>
-      <c r="B57" s="71">
+      <c r="B57" s="63">
         <v>45902</v>
       </c>
       <c r="C57" t="s">
         <v>233</v>
       </c>
-      <c r="D57" s="75" t="s">
+      <c r="D57" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E57" s="74">
+      <c r="E57" s="66">
         <v>-2</v>
       </c>
-      <c r="F57" s="72" t="s">
+      <c r="F57" s="64" t="s">
         <v>302</v>
       </c>
     </row>
@@ -6880,19 +6952,19 @@
       <c r="A58" t="s">
         <v>297</v>
       </c>
-      <c r="B58" s="71">
+      <c r="B58" s="63">
         <v>45903</v>
       </c>
       <c r="C58" t="s">
         <v>234</v>
       </c>
-      <c r="D58" s="75" t="s">
+      <c r="D58" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E58" s="74">
+      <c r="E58" s="66">
         <v>-2</v>
       </c>
-      <c r="F58" s="72" t="s">
+      <c r="F58" s="64" t="s">
         <v>302</v>
       </c>
     </row>
@@ -6900,19 +6972,19 @@
       <c r="A59" t="s">
         <v>298</v>
       </c>
-      <c r="B59" s="71">
+      <c r="B59" s="63">
         <v>45903</v>
       </c>
       <c r="C59" t="s">
         <v>235</v>
       </c>
-      <c r="D59" s="75" t="s">
+      <c r="D59" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="E59" s="74">
+      <c r="E59" s="66">
         <v>-1</v>
       </c>
-      <c r="F59" s="72" t="s">
+      <c r="F59" s="64" t="s">
         <v>302</v>
       </c>
     </row>
@@ -6920,19 +6992,19 @@
       <c r="A60" t="s">
         <v>299</v>
       </c>
-      <c r="B60" s="71">
+      <c r="B60" s="63">
         <v>45903</v>
       </c>
       <c r="C60" t="s">
         <v>236</v>
       </c>
-      <c r="D60" s="75" t="s">
+      <c r="D60" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E60" s="74">
+      <c r="E60" s="66">
         <v>-4</v>
       </c>
-      <c r="F60" s="72" t="s">
+      <c r="F60" s="64" t="s">
         <v>302</v>
       </c>
     </row>
@@ -6940,19 +7012,19 @@
       <c r="A61" t="s">
         <v>300</v>
       </c>
-      <c r="B61" s="71">
+      <c r="B61" s="63">
         <v>45904</v>
       </c>
       <c r="C61" t="s">
         <v>237</v>
       </c>
-      <c r="D61" s="75" t="s">
+      <c r="D61" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="E61" s="74">
+      <c r="E61" s="66">
         <v>10</v>
       </c>
-      <c r="F61" s="72" t="s">
+      <c r="F61" s="64" t="s">
         <v>303</v>
       </c>
     </row>
@@ -6988,42 +7060,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="76" t="s">
+      <c r="B1" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="77" t="s">
+      <c r="C1" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="77" t="s">
+      <c r="D1" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="76" t="s">
+      <c r="E1" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="76" t="s">
+      <c r="F1" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="76" t="s">
+      <c r="G1" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="76" t="s">
+      <c r="H1" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="76" t="s">
+      <c r="I1" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="76" t="s">
+      <c r="J1" s="68" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="69" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="str">
@@ -7038,9 +7110,9 @@
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
         <v>12.5</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F2">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>Reorder Level</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -7052,55 +7124,55 @@
       </c>
       <c r="I2" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" s="78" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="78" t="s">
-        <v>63</v>
+      <c r="A3" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="69" t="s">
+        <v>67</v>
       </c>
       <c r="C3" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Industrial Safety Gloves</v>
+        <v>Safety Glasses</v>
       </c>
       <c r="D3" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>NorthStar Industrial Supply</v>
+        <v>Guardian Safety Products</v>
       </c>
       <c r="E3">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>12.5</v>
-      </c>
-      <c r="F3" t="str">
+        <v>4.25</v>
+      </c>
+      <c r="F3">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>Reorder Level</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H3">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="I3" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" s="78" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="78" t="s">
-        <v>63</v>
+      <c r="A4" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="69" t="s">
+        <v>71</v>
       </c>
       <c r="C4" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Industrial Safety Gloves</v>
+        <v>Disposable Dust Mask</v>
       </c>
       <c r="D4" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
@@ -7108,235 +7180,235 @@
       </c>
       <c r="E4">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>12.5</v>
-      </c>
-      <c r="F4" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="F4">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>Reorder Level</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H4">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>156.25</v>
       </c>
       <c r="I4" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="78" t="s">
-        <v>66</v>
+      <c r="B5" s="69" t="s">
+        <v>74</v>
       </c>
       <c r="C5" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Steel-Toe Work Boots</v>
+        <v>Platform Hand Truck</v>
       </c>
       <c r="D5" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>ProSafe Equipment</v>
+        <v>Northern Material Handling</v>
       </c>
       <c r="E5">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="F5">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H5">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>4375</v>
       </c>
       <c r="I5" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="78" t="s">
-        <v>66</v>
+      <c r="B6" s="69" t="s">
+        <v>75</v>
       </c>
       <c r="C6" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Steel-Toe Work Boots</v>
+        <v>Heavy-Duty Pallet Jack</v>
       </c>
       <c r="D6" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>ProSafe Equipment</v>
+        <v>Warehouse Solutions Inc.</v>
       </c>
       <c r="E6">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>85</v>
+        <v>475</v>
       </c>
       <c r="F6">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H6">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>2550</v>
+        <v>11875</v>
       </c>
       <c r="I6" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="78" t="s">
-        <v>66</v>
+      <c r="B7" s="69" t="s">
+        <v>76</v>
       </c>
       <c r="C7" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Steel-Toe Work Boots</v>
+        <v>Steel Storage Bin</v>
       </c>
       <c r="D7" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>ProSafe Equipment</v>
+        <v>Maple Industrial Supply</v>
       </c>
       <c r="E7">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>85</v>
+        <v>18.75</v>
       </c>
       <c r="F7">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="G7">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H7">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>337.5</v>
       </c>
       <c r="I7" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="78" t="s">
-        <v>67</v>
+      <c r="B8" s="69" t="s">
+        <v>77</v>
       </c>
       <c r="C8" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Safety Glasses</v>
+        <v>Plastic Parts Bin</v>
       </c>
       <c r="D8" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Guardian Safety Products</v>
+        <v>StoragePro Canada</v>
       </c>
       <c r="E8">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>4.25</v>
+        <v>6.5</v>
       </c>
       <c r="F8">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G8">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H8">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="I8" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="78" t="s">
-        <v>67</v>
+      <c r="B9" s="69" t="s">
+        <v>78</v>
       </c>
       <c r="C9" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Safety Glasses</v>
+        <v>Wire Shelving Unit</v>
       </c>
       <c r="D9" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Guardian Safety Products</v>
+        <v>Warehouse Solutions Inc.</v>
       </c>
       <c r="E9">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>4.25</v>
+        <v>145</v>
       </c>
       <c r="F9">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G9">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H9">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>7250</v>
       </c>
       <c r="I9" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="78" t="s">
-        <v>67</v>
+      <c r="B10" s="69" t="s">
+        <v>79</v>
       </c>
       <c r="C10" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Safety Glasses</v>
+        <v>Mobile Storage Cart</v>
       </c>
       <c r="D10" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Guardian Safety Products</v>
+        <v>Northern Material Handling</v>
       </c>
       <c r="E10">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>4.25</v>
+        <v>95</v>
       </c>
       <c r="F10">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H10">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>170</v>
+        <v>3325</v>
       </c>
       <c r="I10" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -7344,63 +7416,63 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="78" t="s">
-        <v>68</v>
+      <c r="B11" s="69" t="s">
+        <v>80</v>
       </c>
       <c r="C11" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>High-Visibility Safety Vest</v>
+        <v>Plastic Tote - 27 Gallon</v>
       </c>
       <c r="D11" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>WorkShield Canada</v>
+        <v>StoragePro Canada</v>
       </c>
       <c r="E11">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>9.75</v>
+        <v>22.5</v>
       </c>
       <c r="F11">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G11">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H11">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>117</v>
+        <v>450</v>
       </c>
       <c r="I11" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="78" t="s">
-        <v>68</v>
+      <c r="B12" s="69" t="s">
+        <v>63</v>
       </c>
       <c r="C12" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>High-Visibility Safety Vest</v>
+        <v>Industrial Safety Gloves</v>
       </c>
       <c r="D12" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>WorkShield Canada</v>
+        <v>NorthStar Industrial Supply</v>
       </c>
       <c r="E12">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>9.75</v>
+        <v>12.5</v>
       </c>
       <c r="F12">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G12">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -7416,27 +7488,27 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A13" s="78" t="s">
+      <c r="A13" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="78" t="s">
-        <v>68</v>
+      <c r="B13" s="69" t="s">
+        <v>63</v>
       </c>
       <c r="C13" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>High-Visibility Safety Vest</v>
+        <v>Industrial Safety Gloves</v>
       </c>
       <c r="D13" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>WorkShield Canada</v>
+        <v>NorthStar Industrial Supply</v>
       </c>
       <c r="E13">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>9.75</v>
+        <v>12.5</v>
       </c>
       <c r="F13">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -7452,15 +7524,15 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="78" t="s">
-        <v>69</v>
+      <c r="B14" s="69" t="s">
+        <v>66</v>
       </c>
       <c r="C14" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Hard Hat - Yellow</v>
+        <v>Steel-Toe Work Boots</v>
       </c>
       <c r="D14" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
@@ -7468,11 +7540,11 @@
       </c>
       <c r="E14">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>14.5</v>
+        <v>85</v>
       </c>
       <c r="F14">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G14">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -7488,15 +7560,15 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A15" s="78" t="s">
+      <c r="A15" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="78" t="s">
-        <v>69</v>
+      <c r="B15" s="69" t="s">
+        <v>66</v>
       </c>
       <c r="C15" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Hard Hat - Yellow</v>
+        <v>Steel-Toe Work Boots</v>
       </c>
       <c r="D15" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
@@ -7504,19 +7576,19 @@
       </c>
       <c r="E15">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>14.5</v>
+        <v>85</v>
       </c>
       <c r="F15">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G15">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H15">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>290</v>
+        <v>2550</v>
       </c>
       <c r="I15" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -7524,15 +7596,15 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A16" s="78" t="s">
+      <c r="A16" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="78" t="s">
-        <v>69</v>
+      <c r="B16" s="69" t="s">
+        <v>66</v>
       </c>
       <c r="C16" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Hard Hat - Yellow</v>
+        <v>Steel-Toe Work Boots</v>
       </c>
       <c r="D16" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
@@ -7540,11 +7612,11 @@
       </c>
       <c r="E16">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>14.5</v>
+        <v>85</v>
       </c>
       <c r="F16">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G16">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -7560,15 +7632,15 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A17" s="78" t="s">
+      <c r="A17" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="78" t="s">
-        <v>70</v>
+      <c r="B17" s="69" t="s">
+        <v>67</v>
       </c>
       <c r="C17" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Ear Protection Earmuffs</v>
+        <v>Safety Glasses</v>
       </c>
       <c r="D17" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
@@ -7576,11 +7648,11 @@
       </c>
       <c r="E17">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>18</v>
+        <v>4.25</v>
       </c>
       <c r="F17">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G17">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -7596,15 +7668,15 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A18" s="78" t="s">
+      <c r="A18" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="78" t="s">
-        <v>70</v>
+      <c r="B18" s="69" t="s">
+        <v>67</v>
       </c>
       <c r="C18" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Ear Protection Earmuffs</v>
+        <v>Safety Glasses</v>
       </c>
       <c r="D18" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
@@ -7612,11 +7684,11 @@
       </c>
       <c r="E18">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>18</v>
+        <v>4.25</v>
       </c>
       <c r="F18">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G18">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -7632,35 +7704,35 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A19" s="78" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="78" t="s">
-        <v>70</v>
+      <c r="A19" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="69" t="s">
+        <v>68</v>
       </c>
       <c r="C19" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Ear Protection Earmuffs</v>
+        <v>High-Visibility Safety Vest</v>
       </c>
       <c r="D19" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Guardian Safety Products</v>
+        <v>WorkShield Canada</v>
       </c>
       <c r="E19">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>18</v>
+        <v>9.75</v>
       </c>
       <c r="F19">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G19">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H19">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>252</v>
+        <v>117</v>
       </c>
       <c r="I19" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -7668,63 +7740,63 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A20" s="78" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="78" t="s">
-        <v>71</v>
+      <c r="A20" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="69" t="s">
+        <v>68</v>
       </c>
       <c r="C20" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Disposable Dust Mask</v>
+        <v>High-Visibility Safety Vest</v>
       </c>
       <c r="D20" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>NorthStar Industrial Supply</v>
+        <v>WorkShield Canada</v>
       </c>
       <c r="E20">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>6.25</v>
+        <v>9.75</v>
       </c>
       <c r="F20">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G20">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>156.25</v>
+        <v>0</v>
       </c>
       <c r="I20" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A21" s="78" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" s="78" t="s">
-        <v>71</v>
+      <c r="A21" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="69" t="s">
+        <v>68</v>
       </c>
       <c r="C21" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Disposable Dust Mask</v>
+        <v>High-Visibility Safety Vest</v>
       </c>
       <c r="D21" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>NorthStar Industrial Supply</v>
+        <v>WorkShield Canada</v>
       </c>
       <c r="E21">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>6.25</v>
+        <v>9.75</v>
       </c>
       <c r="F21">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G21">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -7740,27 +7812,27 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A22" s="78" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="78" t="s">
-        <v>71</v>
+      <c r="A22" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="69" t="s">
+        <v>69</v>
       </c>
       <c r="C22" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Disposable Dust Mask</v>
+        <v>Hard Hat - Yellow</v>
       </c>
       <c r="D22" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>NorthStar Industrial Supply</v>
+        <v>ProSafe Equipment</v>
       </c>
       <c r="E22">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>6.25</v>
+        <v>14.5</v>
       </c>
       <c r="F22">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G22">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -7776,35 +7848,35 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A23" s="78" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="78" t="s">
-        <v>72</v>
+      <c r="A23" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="69" t="s">
+        <v>69</v>
       </c>
       <c r="C23" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Cut-Resistant Gloves</v>
+        <v>Hard Hat - Yellow</v>
       </c>
       <c r="D23" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>WorkShield Canada</v>
+        <v>ProSafe Equipment</v>
       </c>
       <c r="E23">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="F23">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G23">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H23">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="I23" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -7812,35 +7884,35 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A24" s="78" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" s="78" t="s">
-        <v>72</v>
+      <c r="A24" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="69" t="s">
+        <v>69</v>
       </c>
       <c r="C24" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Cut-Resistant Gloves</v>
+        <v>Hard Hat - Yellow</v>
       </c>
       <c r="D24" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>WorkShield Canada</v>
+        <v>ProSafe Equipment</v>
       </c>
       <c r="E24">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="F24">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G24">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="I24" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -7848,27 +7920,27 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A25" s="78" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="78" t="s">
-        <v>72</v>
+      <c r="A25" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="69" t="s">
+        <v>70</v>
       </c>
       <c r="C25" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Cut-Resistant Gloves</v>
+        <v>Ear Protection Earmuffs</v>
       </c>
       <c r="D25" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>WorkShield Canada</v>
+        <v>Guardian Safety Products</v>
       </c>
       <c r="E25">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="F25">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G25">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -7884,27 +7956,27 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A26" s="78" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26" s="78" t="s">
-        <v>73</v>
+      <c r="A26" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="69" t="s">
+        <v>70</v>
       </c>
       <c r="C26" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Aluminum Step Ladder</v>
+        <v>Ear Protection Earmuffs</v>
       </c>
       <c r="D26" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Maple Industrial Supply</v>
+        <v>Guardian Safety Products</v>
       </c>
       <c r="E26">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="F26">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G26">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -7920,35 +7992,35 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A27" s="78" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" s="78" t="s">
-        <v>73</v>
+      <c r="A27" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="69" t="s">
+        <v>70</v>
       </c>
       <c r="C27" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Aluminum Step Ladder</v>
+        <v>Ear Protection Earmuffs</v>
       </c>
       <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Maple Industrial Supply</v>
+        <v>Guardian Safety Products</v>
       </c>
       <c r="E27">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="F27">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G27">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H27">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="I27" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -7956,35 +8028,35 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A28" s="78" t="s">
-        <v>65</v>
-      </c>
-      <c r="B28" s="78" t="s">
-        <v>73</v>
+      <c r="A28" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="69" t="s">
+        <v>71</v>
       </c>
       <c r="C28" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Aluminum Step Ladder</v>
+        <v>Disposable Dust Mask</v>
       </c>
       <c r="D28" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Maple Industrial Supply</v>
+        <v>NorthStar Industrial Supply</v>
       </c>
       <c r="E28">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>89</v>
+        <v>6.25</v>
       </c>
       <c r="F28">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G28">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="I28" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -7992,63 +8064,63 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A29" s="78" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="78" t="s">
-        <v>74</v>
+      <c r="A29" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="69" t="s">
+        <v>71</v>
       </c>
       <c r="C29" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Platform Hand Truck</v>
+        <v>Disposable Dust Mask</v>
       </c>
       <c r="D29" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Northern Material Handling</v>
+        <v>NorthStar Industrial Supply</v>
       </c>
       <c r="E29">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>125</v>
+        <v>6.25</v>
       </c>
       <c r="F29">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G29">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>4375</v>
+        <v>0</v>
       </c>
       <c r="I29" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A30" s="78" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="78" t="s">
-        <v>74</v>
+      <c r="A30" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="69" t="s">
+        <v>72</v>
       </c>
       <c r="C30" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Platform Hand Truck</v>
+        <v>Cut-Resistant Gloves</v>
       </c>
       <c r="D30" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Northern Material Handling</v>
+        <v>WorkShield Canada</v>
       </c>
       <c r="E30">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>125</v>
+        <v>11.5</v>
       </c>
       <c r="F30">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="G30">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -8064,35 +8136,35 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A31" s="78" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="78" t="s">
-        <v>74</v>
+      <c r="A31" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="69" t="s">
+        <v>72</v>
       </c>
       <c r="C31" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Platform Hand Truck</v>
+        <v>Cut-Resistant Gloves</v>
       </c>
       <c r="D31" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Northern Material Handling</v>
+        <v>WorkShield Canada</v>
       </c>
       <c r="E31">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>125</v>
+        <v>11.5</v>
       </c>
       <c r="F31">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="G31">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H31">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="I31" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -8100,27 +8172,27 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A32" s="78" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="78" t="s">
-        <v>75</v>
+      <c r="A32" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="69" t="s">
+        <v>72</v>
       </c>
       <c r="C32" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Heavy-Duty Pallet Jack</v>
+        <v>Cut-Resistant Gloves</v>
       </c>
       <c r="D32" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Warehouse Solutions Inc.</v>
+        <v>WorkShield Canada</v>
       </c>
       <c r="E32">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>475</v>
+        <v>11.5</v>
       </c>
       <c r="F32">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G32">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -8136,63 +8208,63 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A33" s="78" t="s">
-        <v>64</v>
-      </c>
-      <c r="B33" s="78" t="s">
-        <v>75</v>
+      <c r="A33" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="69" t="s">
+        <v>73</v>
       </c>
       <c r="C33" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Heavy-Duty Pallet Jack</v>
+        <v>Aluminum Step Ladder</v>
       </c>
       <c r="D33" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Warehouse Solutions Inc.</v>
+        <v>Maple Industrial Supply</v>
       </c>
       <c r="E33">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>475</v>
+        <v>89</v>
       </c>
       <c r="F33">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="G33">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>11875</v>
+        <v>0</v>
       </c>
       <c r="I33" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A34" s="78" t="s">
-        <v>65</v>
-      </c>
-      <c r="B34" s="78" t="s">
-        <v>75</v>
+      <c r="A34" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="69" t="s">
+        <v>73</v>
       </c>
       <c r="C34" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Heavy-Duty Pallet Jack</v>
+        <v>Aluminum Step Ladder</v>
       </c>
       <c r="D34" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Warehouse Solutions Inc.</v>
+        <v>Maple Industrial Supply</v>
       </c>
       <c r="E34">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>475</v>
+        <v>89</v>
       </c>
       <c r="F34">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="G34">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -8208,15 +8280,15 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A35" s="78" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="78" t="s">
-        <v>76</v>
+      <c r="A35" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="69" t="s">
+        <v>73</v>
       </c>
       <c r="C35" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Steel Storage Bin</v>
+        <v>Aluminum Step Ladder</v>
       </c>
       <c r="D35" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
@@ -8224,19 +8296,19 @@
       </c>
       <c r="E35">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>18.75</v>
+        <v>89</v>
       </c>
       <c r="F35">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G35">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H35">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="I35" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -8244,27 +8316,27 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A36" s="78" t="s">
+      <c r="A36" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="B36" s="78" t="s">
-        <v>76</v>
+      <c r="B36" s="69" t="s">
+        <v>74</v>
       </c>
       <c r="C36" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Steel Storage Bin</v>
+        <v>Platform Hand Truck</v>
       </c>
       <c r="D36" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Maple Industrial Supply</v>
+        <v>Northern Material Handling</v>
       </c>
       <c r="E36">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>18.75</v>
+        <v>125</v>
       </c>
       <c r="F36">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G36">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -8280,99 +8352,99 @@
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A37" s="78" t="s">
+      <c r="A37" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="78" t="s">
-        <v>76</v>
+      <c r="B37" s="69" t="s">
+        <v>74</v>
       </c>
       <c r="C37" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Steel Storage Bin</v>
+        <v>Platform Hand Truck</v>
       </c>
       <c r="D37" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Maple Industrial Supply</v>
+        <v>Northern Material Handling</v>
       </c>
       <c r="E37">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>18.75</v>
+        <v>125</v>
       </c>
       <c r="F37">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G37">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H37">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>337.5</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A38" s="78" t="s">
+      <c r="A38" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="B38" s="78" t="s">
-        <v>77</v>
+      <c r="B38" s="69" t="s">
+        <v>75</v>
       </c>
       <c r="C38" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Plastic Parts Bin</v>
+        <v>Heavy-Duty Pallet Jack</v>
       </c>
       <c r="D38" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>StoragePro Canada</v>
+        <v>Warehouse Solutions Inc.</v>
       </c>
       <c r="E38">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>6.5</v>
+        <v>475</v>
       </c>
       <c r="F38">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G38">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H38">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="I38" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A39" s="78" t="s">
-        <v>64</v>
-      </c>
-      <c r="B39" s="78" t="s">
-        <v>77</v>
+      <c r="A39" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="69" t="s">
+        <v>75</v>
       </c>
       <c r="C39" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Plastic Parts Bin</v>
+        <v>Heavy-Duty Pallet Jack</v>
       </c>
       <c r="D39" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>StoragePro Canada</v>
+        <v>Warehouse Solutions Inc.</v>
       </c>
       <c r="E39">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>6.5</v>
+        <v>475</v>
       </c>
       <c r="F39">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G39">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -8388,27 +8460,27 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A40" s="78" t="s">
-        <v>65</v>
-      </c>
-      <c r="B40" s="78" t="s">
-        <v>77</v>
+      <c r="A40" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="69" t="s">
+        <v>76</v>
       </c>
       <c r="C40" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Plastic Parts Bin</v>
+        <v>Steel Storage Bin</v>
       </c>
       <c r="D40" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>StoragePro Canada</v>
+        <v>Maple Industrial Supply</v>
       </c>
       <c r="E40">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>6.5</v>
+        <v>18.75</v>
       </c>
       <c r="F40">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G40">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -8424,27 +8496,27 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A41" s="78" t="s">
-        <v>62</v>
-      </c>
-      <c r="B41" s="78" t="s">
-        <v>78</v>
+      <c r="A41" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="69" t="s">
+        <v>76</v>
       </c>
       <c r="C41" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Wire Shelving Unit</v>
+        <v>Steel Storage Bin</v>
       </c>
       <c r="D41" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Warehouse Solutions Inc.</v>
+        <v>Maple Industrial Supply</v>
       </c>
       <c r="E41">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>145</v>
+        <v>18.75</v>
       </c>
       <c r="F41">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G41">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -8460,63 +8532,63 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A42" s="78" t="s">
+      <c r="A42" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="B42" s="78" t="s">
-        <v>78</v>
+      <c r="B42" s="69" t="s">
+        <v>77</v>
       </c>
       <c r="C42" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Wire Shelving Unit</v>
+        <v>Plastic Parts Bin</v>
       </c>
       <c r="D42" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Warehouse Solutions Inc.</v>
+        <v>StoragePro Canada</v>
       </c>
       <c r="E42">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>145</v>
+        <v>6.5</v>
       </c>
       <c r="F42">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G42">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H42">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>7250</v>
+        <v>0</v>
       </c>
       <c r="I42" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A43" s="78" t="s">
+      <c r="A43" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="B43" s="78" t="s">
-        <v>78</v>
+      <c r="B43" s="69" t="s">
+        <v>77</v>
       </c>
       <c r="C43" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Wire Shelving Unit</v>
+        <v>Plastic Parts Bin</v>
       </c>
       <c r="D43" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Warehouse Solutions Inc.</v>
+        <v>StoragePro Canada</v>
       </c>
       <c r="E43">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>145</v>
+        <v>6.5</v>
       </c>
       <c r="F43">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G43">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -8532,27 +8604,27 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A44" s="78" t="s">
+      <c r="A44" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="B44" s="78" t="s">
-        <v>79</v>
+      <c r="B44" s="69" t="s">
+        <v>78</v>
       </c>
       <c r="C44" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Mobile Storage Cart</v>
+        <v>Wire Shelving Unit</v>
       </c>
       <c r="D44" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Northern Material Handling</v>
+        <v>Warehouse Solutions Inc.</v>
       </c>
       <c r="E44">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="F44">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G44">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -8568,27 +8640,27 @@
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A45" s="78" t="s">
-        <v>64</v>
-      </c>
-      <c r="B45" s="78" t="s">
-        <v>79</v>
+      <c r="A45" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="69" t="s">
+        <v>78</v>
       </c>
       <c r="C45" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Mobile Storage Cart</v>
+        <v>Wire Shelving Unit</v>
       </c>
       <c r="D45" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>Northern Material Handling</v>
+        <v>Warehouse Solutions Inc.</v>
       </c>
       <c r="E45">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="F45">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G45">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
@@ -8604,10 +8676,10 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A46" s="78" t="s">
-        <v>65</v>
-      </c>
-      <c r="B46" s="78" t="s">
+      <c r="A46" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" s="69" t="s">
         <v>79</v>
       </c>
       <c r="C46" t="str">
@@ -8628,58 +8700,58 @@
       </c>
       <c r="G46">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H46">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>3325</v>
+        <v>0</v>
       </c>
       <c r="I46" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A47" s="78" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47" s="78" t="s">
-        <v>80</v>
+      <c r="A47" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" s="69" t="s">
+        <v>79</v>
       </c>
       <c r="C47" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</f>
-        <v>Plastic Tote - 27 Gallon</v>
+        <v>Mobile Storage Cart</v>
       </c>
       <c r="D47" t="str">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</f>
-        <v>StoragePro Canada</v>
+        <v>Northern Material Handling</v>
       </c>
       <c r="E47">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</f>
-        <v>22.5</v>
+        <v>95</v>
       </c>
       <c r="F47">
         <f>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G47">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H47">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="I47" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A48" s="78" t="s">
+      <c r="A48" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="B48" s="78" t="s">
+      <c r="B48" s="69" t="s">
         <v>80</v>
       </c>
       <c r="C48" t="str">
@@ -8712,10 +8784,10 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A49" s="78" t="s">
+      <c r="A49" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="78" t="s">
+      <c r="B49" s="69" t="s">
         <v>80</v>
       </c>
       <c r="C49" t="str">
@@ -8748,10 +8820,10 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A50" s="78" t="s">
+      <c r="A50" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="B50" s="78" t="s">
+      <c r="B50" s="69" t="s">
         <v>81</v>
       </c>
       <c r="C50" t="str">
@@ -8784,10 +8856,10 @@
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A51" s="78" t="s">
+      <c r="A51" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="B51" s="78" t="s">
+      <c r="B51" s="69" t="s">
         <v>81</v>
       </c>
       <c r="C51" t="str">
@@ -8820,10 +8892,10 @@
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A52" s="78" t="s">
+      <c r="A52" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="B52" s="78" t="s">
+      <c r="B52" s="69" t="s">
         <v>81</v>
       </c>
       <c r="C52" t="str">
@@ -8856,10 +8928,10 @@
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A53" s="78" t="s">
+      <c r="A53" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="B53" s="78" t="s">
+      <c r="B53" s="69" t="s">
         <v>82</v>
       </c>
       <c r="C53" t="str">
@@ -8892,10 +8964,10 @@
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A54" s="78" t="s">
+      <c r="A54" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="B54" s="78" t="s">
+      <c r="B54" s="69" t="s">
         <v>82</v>
       </c>
       <c r="C54" t="str">
@@ -8928,10 +9000,10 @@
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A55" s="78" t="s">
+      <c r="A55" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="B55" s="78" t="s">
+      <c r="B55" s="69" t="s">
         <v>82</v>
       </c>
       <c r="C55" t="str">
@@ -8964,10 +9036,10 @@
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A56" s="78" t="s">
+      <c r="A56" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="B56" s="78" t="s">
+      <c r="B56" s="69" t="s">
         <v>83</v>
       </c>
       <c r="C56" t="str">
@@ -9000,10 +9072,10 @@
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A57" s="78" t="s">
+      <c r="A57" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="B57" s="78" t="s">
+      <c r="B57" s="69" t="s">
         <v>83</v>
       </c>
       <c r="C57" t="str">
@@ -9036,10 +9108,10 @@
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A58" s="78" t="s">
+      <c r="A58" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="B58" s="78" t="s">
+      <c r="B58" s="69" t="s">
         <v>83</v>
       </c>
       <c r="C58" t="str">
@@ -9072,10 +9144,10 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A59" s="78" t="s">
+      <c r="A59" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="B59" s="78" t="s">
+      <c r="B59" s="69" t="s">
         <v>84</v>
       </c>
       <c r="C59" t="str">
@@ -9108,10 +9180,10 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A60" s="78" t="s">
+      <c r="A60" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="78" t="s">
+      <c r="B60" s="69" t="s">
         <v>84</v>
       </c>
       <c r="C60" t="str">
@@ -9144,10 +9216,10 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A61" s="78" t="s">
+      <c r="A61" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="78" t="s">
+      <c r="B61" s="69" t="s">
         <v>84</v>
       </c>
       <c r="C61" t="str">
@@ -9180,9 +9252,55 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",I1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",I1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DA699FD3-20CD-4065-9BA7-E2DA1B7037F2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{DA699FD3-20CD-4065-9BA7-E2DA1B7037F2}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>H1:H1048576</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/DataAnalyst.xlsx
+++ b/DataAnalyst.xlsx
@@ -8,23 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malik\OneDrive\Documents\Data\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A97CD8-BE65-4FCB-8C74-C5148A674D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E119B58-BFD9-4900-B6BC-CDF1444E59B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="creatingtable" sheetId="2" r:id="rId2"/>
     <sheet name="Products" sheetId="3" r:id="rId3"/>
     <sheet name="Transactions" sheetId="4" r:id="rId4"/>
-    <sheet name="Inventory Sheet" sheetId="5" r:id="rId5"/>
+    <sheet name="Inventory" sheetId="5" r:id="rId5"/>
+    <sheet name="Order" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="ProductList">Products[ProductID]</definedName>
+    <definedName name="Slicer_Supplier">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="12" r:id="rId7"/>
+  </pivotCaches>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId8"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -41,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="320">
   <si>
     <t>ELECTRONICS COMPANIES REPORT Q1 2023</t>
   </si>
@@ -953,6 +966,54 @@
   </si>
   <si>
     <t>Receipt</t>
+  </si>
+  <si>
+    <t>(All)</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Sum of Reorder Level</t>
+  </si>
+  <si>
+    <t>BoxWorks Canada Total</t>
+  </si>
+  <si>
+    <t>Guardian Safety Products Total</t>
+  </si>
+  <si>
+    <t>Maple Industrial Supply Total</t>
+  </si>
+  <si>
+    <t>Northern Material Handling Total</t>
+  </si>
+  <si>
+    <t>NorthStar Industrial Supply Total</t>
+  </si>
+  <si>
+    <t>PackRight Solutions Total</t>
+  </si>
+  <si>
+    <t>ProSafe Equipment Total</t>
+  </si>
+  <si>
+    <t>StoragePro Canada Total</t>
+  </si>
+  <si>
+    <t>Warehouse Solutions Inc. Total</t>
+  </si>
+  <si>
+    <t>WorkShield Canada Total</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -1250,7 +1311,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1459,6 +1520,18 @@
     </xf>
     <xf numFmtId="7" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -2154,6 +2227,2268 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Supplier">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88C12871-DE9E-661A-B22F-CEBB8729DE99}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Supplier"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5876925" y="552450"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-CA" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="malik" refreshedDate="46275.874918171299" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{E1D8D753-DAC5-4E1D-B12F-2B69C70CB065}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Inventory"/>
+  </cacheSource>
+  <cacheFields count="12">
+    <cacheField name="Site" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Store A"/>
+        <s v="Store C"/>
+        <s v="Store B"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="ProductID" numFmtId="0">
+      <sharedItems count="20">
+        <s v="P001"/>
+        <s v="P003"/>
+        <s v="P007"/>
+        <s v="P010"/>
+        <s v="P011"/>
+        <s v="P012"/>
+        <s v="P013"/>
+        <s v="P014"/>
+        <s v="P015"/>
+        <s v="P016"/>
+        <s v="P002"/>
+        <s v="P004"/>
+        <s v="P005"/>
+        <s v="P006"/>
+        <s v="P008"/>
+        <s v="P009"/>
+        <s v="P017"/>
+        <s v="P018"/>
+        <s v="P019"/>
+        <s v="P020"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Product Description" numFmtId="0">
+      <sharedItems count="20">
+        <s v="Industrial Safety Gloves"/>
+        <s v="Safety Glasses"/>
+        <s v="Disposable Dust Mask"/>
+        <s v="Platform Hand Truck"/>
+        <s v="Heavy-Duty Pallet Jack"/>
+        <s v="Steel Storage Bin"/>
+        <s v="Plastic Parts Bin"/>
+        <s v="Wire Shelving Unit"/>
+        <s v="Mobile Storage Cart"/>
+        <s v="Plastic Tote - 27 Gallon"/>
+        <s v="Steel-Toe Work Boots"/>
+        <s v="High-Visibility Safety Vest"/>
+        <s v="Hard Hat - Yellow"/>
+        <s v="Ear Protection Earmuffs"/>
+        <s v="Cut-Resistant Gloves"/>
+        <s v="Aluminum Step Ladder"/>
+        <s v="Corrugated Shipping Box - Small"/>
+        <s v="Corrugated Shipping Box - Medium"/>
+        <s v="Corrugated Shipping Box - Large"/>
+        <s v="Stretch Wrap Roll"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Supplier" numFmtId="0">
+      <sharedItems count="10">
+        <s v="NorthStar Industrial Supply"/>
+        <s v="Guardian Safety Products"/>
+        <s v="Northern Material Handling"/>
+        <s v="Warehouse Solutions Inc."/>
+        <s v="Maple Industrial Supply"/>
+        <s v="StoragePro Canada"/>
+        <s v="ProSafe Equipment"/>
+        <s v="WorkShield Canada"/>
+        <s v="PackRight Solutions"/>
+        <s v="BoxWorks Canada"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Cost/Unit" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.25" maxValue="475"/>
+    </cacheField>
+    <cacheField name="Reorder Level" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="100"/>
+    </cacheField>
+    <cacheField name="QuantityOnHand" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="60"/>
+    </cacheField>
+    <cacheField name="Stock Value" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="11875"/>
+    </cacheField>
+    <cacheField name="Reorder" numFmtId="0">
+      <sharedItems count="2">
+        <s v="No"/>
+        <s v="Yes"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Order Date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-09-10T00:00:00" maxDate="2026-11-09T00:00:00" count="60">
+        <d v="2026-09-10T00:00:00"/>
+        <d v="2026-09-11T00:00:00"/>
+        <d v="2026-09-12T00:00:00"/>
+        <d v="2026-09-13T00:00:00"/>
+        <d v="2026-09-14T00:00:00"/>
+        <d v="2026-09-15T00:00:00"/>
+        <d v="2026-09-16T00:00:00"/>
+        <d v="2026-09-17T00:00:00"/>
+        <d v="2026-09-18T00:00:00"/>
+        <d v="2026-09-19T00:00:00"/>
+        <d v="2026-09-20T00:00:00"/>
+        <d v="2026-09-21T00:00:00"/>
+        <d v="2026-09-22T00:00:00"/>
+        <d v="2026-09-23T00:00:00"/>
+        <d v="2026-09-24T00:00:00"/>
+        <d v="2026-09-25T00:00:00"/>
+        <d v="2026-09-26T00:00:00"/>
+        <d v="2026-09-27T00:00:00"/>
+        <d v="2026-09-28T00:00:00"/>
+        <d v="2026-09-29T00:00:00"/>
+        <d v="2026-09-30T00:00:00"/>
+        <d v="2026-10-01T00:00:00"/>
+        <d v="2026-10-02T00:00:00"/>
+        <d v="2026-10-03T00:00:00"/>
+        <d v="2026-10-04T00:00:00"/>
+        <d v="2026-10-05T00:00:00"/>
+        <d v="2026-10-06T00:00:00"/>
+        <d v="2026-10-07T00:00:00"/>
+        <d v="2026-10-08T00:00:00"/>
+        <d v="2026-10-09T00:00:00"/>
+        <d v="2026-10-10T00:00:00"/>
+        <d v="2026-10-11T00:00:00"/>
+        <d v="2026-10-12T00:00:00"/>
+        <d v="2026-10-13T00:00:00"/>
+        <d v="2026-10-14T00:00:00"/>
+        <d v="2026-10-15T00:00:00"/>
+        <d v="2026-10-16T00:00:00"/>
+        <d v="2026-10-17T00:00:00"/>
+        <d v="2026-10-18T00:00:00"/>
+        <d v="2026-10-19T00:00:00"/>
+        <d v="2026-10-20T00:00:00"/>
+        <d v="2026-10-21T00:00:00"/>
+        <d v="2026-10-22T00:00:00"/>
+        <d v="2026-10-23T00:00:00"/>
+        <d v="2026-10-24T00:00:00"/>
+        <d v="2026-10-25T00:00:00"/>
+        <d v="2026-10-26T00:00:00"/>
+        <d v="2026-10-27T00:00:00"/>
+        <d v="2026-10-28T00:00:00"/>
+        <d v="2026-10-29T00:00:00"/>
+        <d v="2026-10-30T00:00:00"/>
+        <d v="2026-10-31T00:00:00"/>
+        <d v="2026-11-01T00:00:00"/>
+        <d v="2026-11-02T00:00:00"/>
+        <d v="2026-11-03T00:00:00"/>
+        <d v="2026-11-04T00:00:00"/>
+        <d v="2026-11-05T00:00:00"/>
+        <d v="2026-11-06T00:00:00"/>
+        <d v="2026-11-07T00:00:00"/>
+        <d v="2026-11-08T00:00:00"/>
+      </sharedItems>
+      <fieldGroup par="11"/>
+    </cacheField>
+    <cacheField name="Days (Order Date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="9">
+        <rangePr groupBy="days" startDate="2026-09-10T00:00:00" endDate="2026-11-09T00:00:00"/>
+        <groupItems count="368">
+          <s v="&lt;2026-09-10"/>
+          <s v="01-Jan"/>
+          <s v="02-Jan"/>
+          <s v="03-Jan"/>
+          <s v="04-Jan"/>
+          <s v="05-Jan"/>
+          <s v="06-Jan"/>
+          <s v="07-Jan"/>
+          <s v="08-Jan"/>
+          <s v="09-Jan"/>
+          <s v="10-Jan"/>
+          <s v="11-Jan"/>
+          <s v="12-Jan"/>
+          <s v="13-Jan"/>
+          <s v="14-Jan"/>
+          <s v="15-Jan"/>
+          <s v="16-Jan"/>
+          <s v="17-Jan"/>
+          <s v="18-Jan"/>
+          <s v="19-Jan"/>
+          <s v="20-Jan"/>
+          <s v="21-Jan"/>
+          <s v="22-Jan"/>
+          <s v="23-Jan"/>
+          <s v="24-Jan"/>
+          <s v="25-Jan"/>
+          <s v="26-Jan"/>
+          <s v="27-Jan"/>
+          <s v="28-Jan"/>
+          <s v="29-Jan"/>
+          <s v="30-Jan"/>
+          <s v="31-Jan"/>
+          <s v="01-Feb"/>
+          <s v="02-Feb"/>
+          <s v="03-Feb"/>
+          <s v="04-Feb"/>
+          <s v="05-Feb"/>
+          <s v="06-Feb"/>
+          <s v="07-Feb"/>
+          <s v="08-Feb"/>
+          <s v="09-Feb"/>
+          <s v="10-Feb"/>
+          <s v="11-Feb"/>
+          <s v="12-Feb"/>
+          <s v="13-Feb"/>
+          <s v="14-Feb"/>
+          <s v="15-Feb"/>
+          <s v="16-Feb"/>
+          <s v="17-Feb"/>
+          <s v="18-Feb"/>
+          <s v="19-Feb"/>
+          <s v="20-Feb"/>
+          <s v="21-Feb"/>
+          <s v="22-Feb"/>
+          <s v="23-Feb"/>
+          <s v="24-Feb"/>
+          <s v="25-Feb"/>
+          <s v="26-Feb"/>
+          <s v="27-Feb"/>
+          <s v="28-Feb"/>
+          <s v="29-Feb"/>
+          <s v="01-Mar"/>
+          <s v="02-Mar"/>
+          <s v="03-Mar"/>
+          <s v="04-Mar"/>
+          <s v="05-Mar"/>
+          <s v="06-Mar"/>
+          <s v="07-Mar"/>
+          <s v="08-Mar"/>
+          <s v="09-Mar"/>
+          <s v="10-Mar"/>
+          <s v="11-Mar"/>
+          <s v="12-Mar"/>
+          <s v="13-Mar"/>
+          <s v="14-Mar"/>
+          <s v="15-Mar"/>
+          <s v="16-Mar"/>
+          <s v="17-Mar"/>
+          <s v="18-Mar"/>
+          <s v="19-Mar"/>
+          <s v="20-Mar"/>
+          <s v="21-Mar"/>
+          <s v="22-Mar"/>
+          <s v="23-Mar"/>
+          <s v="24-Mar"/>
+          <s v="25-Mar"/>
+          <s v="26-Mar"/>
+          <s v="27-Mar"/>
+          <s v="28-Mar"/>
+          <s v="29-Mar"/>
+          <s v="30-Mar"/>
+          <s v="31-Mar"/>
+          <s v="01-Apr"/>
+          <s v="02-Apr"/>
+          <s v="03-Apr"/>
+          <s v="04-Apr"/>
+          <s v="05-Apr"/>
+          <s v="06-Apr"/>
+          <s v="07-Apr"/>
+          <s v="08-Apr"/>
+          <s v="09-Apr"/>
+          <s v="10-Apr"/>
+          <s v="11-Apr"/>
+          <s v="12-Apr"/>
+          <s v="13-Apr"/>
+          <s v="14-Apr"/>
+          <s v="15-Apr"/>
+          <s v="16-Apr"/>
+          <s v="17-Apr"/>
+          <s v="18-Apr"/>
+          <s v="19-Apr"/>
+          <s v="20-Apr"/>
+          <s v="21-Apr"/>
+          <s v="22-Apr"/>
+          <s v="23-Apr"/>
+          <s v="24-Apr"/>
+          <s v="25-Apr"/>
+          <s v="26-Apr"/>
+          <s v="27-Apr"/>
+          <s v="28-Apr"/>
+          <s v="29-Apr"/>
+          <s v="30-Apr"/>
+          <s v="01-May"/>
+          <s v="02-May"/>
+          <s v="03-May"/>
+          <s v="04-May"/>
+          <s v="05-May"/>
+          <s v="06-May"/>
+          <s v="07-May"/>
+          <s v="08-May"/>
+          <s v="09-May"/>
+          <s v="10-May"/>
+          <s v="11-May"/>
+          <s v="12-May"/>
+          <s v="13-May"/>
+          <s v="14-May"/>
+          <s v="15-May"/>
+          <s v="16-May"/>
+          <s v="17-May"/>
+          <s v="18-May"/>
+          <s v="19-May"/>
+          <s v="20-May"/>
+          <s v="21-May"/>
+          <s v="22-May"/>
+          <s v="23-May"/>
+          <s v="24-May"/>
+          <s v="25-May"/>
+          <s v="26-May"/>
+          <s v="27-May"/>
+          <s v="28-May"/>
+          <s v="29-May"/>
+          <s v="30-May"/>
+          <s v="31-May"/>
+          <s v="01-Jun"/>
+          <s v="02-Jun"/>
+          <s v="03-Jun"/>
+          <s v="04-Jun"/>
+          <s v="05-Jun"/>
+          <s v="06-Jun"/>
+          <s v="07-Jun"/>
+          <s v="08-Jun"/>
+          <s v="09-Jun"/>
+          <s v="10-Jun"/>
+          <s v="11-Jun"/>
+          <s v="12-Jun"/>
+          <s v="13-Jun"/>
+          <s v="14-Jun"/>
+          <s v="15-Jun"/>
+          <s v="16-Jun"/>
+          <s v="17-Jun"/>
+          <s v="18-Jun"/>
+          <s v="19-Jun"/>
+          <s v="20-Jun"/>
+          <s v="21-Jun"/>
+          <s v="22-Jun"/>
+          <s v="23-Jun"/>
+          <s v="24-Jun"/>
+          <s v="25-Jun"/>
+          <s v="26-Jun"/>
+          <s v="27-Jun"/>
+          <s v="28-Jun"/>
+          <s v="29-Jun"/>
+          <s v="30-Jun"/>
+          <s v="01-Jul"/>
+          <s v="02-Jul"/>
+          <s v="03-Jul"/>
+          <s v="04-Jul"/>
+          <s v="05-Jul"/>
+          <s v="06-Jul"/>
+          <s v="07-Jul"/>
+          <s v="08-Jul"/>
+          <s v="09-Jul"/>
+          <s v="10-Jul"/>
+          <s v="11-Jul"/>
+          <s v="12-Jul"/>
+          <s v="13-Jul"/>
+          <s v="14-Jul"/>
+          <s v="15-Jul"/>
+          <s v="16-Jul"/>
+          <s v="17-Jul"/>
+          <s v="18-Jul"/>
+          <s v="19-Jul"/>
+          <s v="20-Jul"/>
+          <s v="21-Jul"/>
+          <s v="22-Jul"/>
+          <s v="23-Jul"/>
+          <s v="24-Jul"/>
+          <s v="25-Jul"/>
+          <s v="26-Jul"/>
+          <s v="27-Jul"/>
+          <s v="28-Jul"/>
+          <s v="29-Jul"/>
+          <s v="30-Jul"/>
+          <s v="31-Jul"/>
+          <s v="01-Aug"/>
+          <s v="02-Aug"/>
+          <s v="03-Aug"/>
+          <s v="04-Aug"/>
+          <s v="05-Aug"/>
+          <s v="06-Aug"/>
+          <s v="07-Aug"/>
+          <s v="08-Aug"/>
+          <s v="09-Aug"/>
+          <s v="10-Aug"/>
+          <s v="11-Aug"/>
+          <s v="12-Aug"/>
+          <s v="13-Aug"/>
+          <s v="14-Aug"/>
+          <s v="15-Aug"/>
+          <s v="16-Aug"/>
+          <s v="17-Aug"/>
+          <s v="18-Aug"/>
+          <s v="19-Aug"/>
+          <s v="20-Aug"/>
+          <s v="21-Aug"/>
+          <s v="22-Aug"/>
+          <s v="23-Aug"/>
+          <s v="24-Aug"/>
+          <s v="25-Aug"/>
+          <s v="26-Aug"/>
+          <s v="27-Aug"/>
+          <s v="28-Aug"/>
+          <s v="29-Aug"/>
+          <s v="30-Aug"/>
+          <s v="31-Aug"/>
+          <s v="01-Sep"/>
+          <s v="02-Sep"/>
+          <s v="03-Sep"/>
+          <s v="04-Sep"/>
+          <s v="05-Sep"/>
+          <s v="06-Sep"/>
+          <s v="07-Sep"/>
+          <s v="08-Sep"/>
+          <s v="09-Sep"/>
+          <s v="10-Sep"/>
+          <s v="11-Sep"/>
+          <s v="12-Sep"/>
+          <s v="13-Sep"/>
+          <s v="14-Sep"/>
+          <s v="15-Sep"/>
+          <s v="16-Sep"/>
+          <s v="17-Sep"/>
+          <s v="18-Sep"/>
+          <s v="19-Sep"/>
+          <s v="20-Sep"/>
+          <s v="21-Sep"/>
+          <s v="22-Sep"/>
+          <s v="23-Sep"/>
+          <s v="24-Sep"/>
+          <s v="25-Sep"/>
+          <s v="26-Sep"/>
+          <s v="27-Sep"/>
+          <s v="28-Sep"/>
+          <s v="29-Sep"/>
+          <s v="30-Sep"/>
+          <s v="01-Oct"/>
+          <s v="02-Oct"/>
+          <s v="03-Oct"/>
+          <s v="04-Oct"/>
+          <s v="05-Oct"/>
+          <s v="06-Oct"/>
+          <s v="07-Oct"/>
+          <s v="08-Oct"/>
+          <s v="09-Oct"/>
+          <s v="10-Oct"/>
+          <s v="11-Oct"/>
+          <s v="12-Oct"/>
+          <s v="13-Oct"/>
+          <s v="14-Oct"/>
+          <s v="15-Oct"/>
+          <s v="16-Oct"/>
+          <s v="17-Oct"/>
+          <s v="18-Oct"/>
+          <s v="19-Oct"/>
+          <s v="20-Oct"/>
+          <s v="21-Oct"/>
+          <s v="22-Oct"/>
+          <s v="23-Oct"/>
+          <s v="24-Oct"/>
+          <s v="25-Oct"/>
+          <s v="26-Oct"/>
+          <s v="27-Oct"/>
+          <s v="28-Oct"/>
+          <s v="29-Oct"/>
+          <s v="30-Oct"/>
+          <s v="31-Oct"/>
+          <s v="01-Nov"/>
+          <s v="02-Nov"/>
+          <s v="03-Nov"/>
+          <s v="04-Nov"/>
+          <s v="05-Nov"/>
+          <s v="06-Nov"/>
+          <s v="07-Nov"/>
+          <s v="08-Nov"/>
+          <s v="09-Nov"/>
+          <s v="10-Nov"/>
+          <s v="11-Nov"/>
+          <s v="12-Nov"/>
+          <s v="13-Nov"/>
+          <s v="14-Nov"/>
+          <s v="15-Nov"/>
+          <s v="16-Nov"/>
+          <s v="17-Nov"/>
+          <s v="18-Nov"/>
+          <s v="19-Nov"/>
+          <s v="20-Nov"/>
+          <s v="21-Nov"/>
+          <s v="22-Nov"/>
+          <s v="23-Nov"/>
+          <s v="24-Nov"/>
+          <s v="25-Nov"/>
+          <s v="26-Nov"/>
+          <s v="27-Nov"/>
+          <s v="28-Nov"/>
+          <s v="29-Nov"/>
+          <s v="30-Nov"/>
+          <s v="01-Dec"/>
+          <s v="02-Dec"/>
+          <s v="03-Dec"/>
+          <s v="04-Dec"/>
+          <s v="05-Dec"/>
+          <s v="06-Dec"/>
+          <s v="07-Dec"/>
+          <s v="08-Dec"/>
+          <s v="09-Dec"/>
+          <s v="10-Dec"/>
+          <s v="11-Dec"/>
+          <s v="12-Dec"/>
+          <s v="13-Dec"/>
+          <s v="14-Dec"/>
+          <s v="15-Dec"/>
+          <s v="16-Dec"/>
+          <s v="17-Dec"/>
+          <s v="18-Dec"/>
+          <s v="19-Dec"/>
+          <s v="20-Dec"/>
+          <s v="21-Dec"/>
+          <s v="22-Dec"/>
+          <s v="23-Dec"/>
+          <s v="24-Dec"/>
+          <s v="25-Dec"/>
+          <s v="26-Dec"/>
+          <s v="27-Dec"/>
+          <s v="28-Dec"/>
+          <s v="29-Dec"/>
+          <s v="30-Dec"/>
+          <s v="31-Dec"/>
+          <s v="&gt;2026-11-09"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Months (Order Date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="9">
+        <rangePr groupBy="months" startDate="2026-09-10T00:00:00" endDate="2026-11-09T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;2026-09-10"/>
+          <s v="Jan"/>
+          <s v="Feb"/>
+          <s v="Mar"/>
+          <s v="Apr"/>
+          <s v="May"/>
+          <s v="Jun"/>
+          <s v="Jul"/>
+          <s v="Aug"/>
+          <s v="Sep"/>
+          <s v="Oct"/>
+          <s v="Nov"/>
+          <s v="Dec"/>
+          <s v="&gt;2026-11-09"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="1072809326"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="60">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="12.5"/>
+    <n v="9"/>
+    <n v="50"/>
+    <n v="625"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="4.25"/>
+    <n v="15"/>
+    <n v="40"/>
+    <n v="170"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="6.25"/>
+    <n v="15"/>
+    <n v="25"/>
+    <n v="156.25"/>
+    <x v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="125"/>
+    <n v="5"/>
+    <n v="35"/>
+    <n v="4375"/>
+    <x v="0"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="3"/>
+    <n v="475"/>
+    <n v="8"/>
+    <n v="25"/>
+    <n v="11875"/>
+    <x v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="4"/>
+    <n v="18.75"/>
+    <n v="3"/>
+    <n v="18"/>
+    <n v="337.5"/>
+    <x v="0"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <n v="6.5"/>
+    <n v="20"/>
+    <n v="60"/>
+    <n v="390"/>
+    <x v="0"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="7"/>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="145"/>
+    <n v="30"/>
+    <n v="50"/>
+    <n v="7250"/>
+    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="95"/>
+    <n v="5"/>
+    <n v="35"/>
+    <n v="3325"/>
+    <x v="0"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="9"/>
+    <x v="5"/>
+    <n v="22.5"/>
+    <n v="8"/>
+    <n v="20"/>
+    <n v="450"/>
+    <x v="0"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="12.5"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="12.5"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="10"/>
+    <x v="6"/>
+    <n v="85"/>
+    <n v="50"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="10"/>
+    <x v="6"/>
+    <n v="85"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="2550"/>
+    <x v="1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="10"/>
+    <x v="6"/>
+    <n v="85"/>
+    <n v="50"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="4.25"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="4.25"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="11"/>
+    <x v="7"/>
+    <n v="9.75"/>
+    <n v="25"/>
+    <n v="12"/>
+    <n v="117"/>
+    <x v="1"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="11"/>
+    <x v="7"/>
+    <n v="9.75"/>
+    <n v="25"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="11"/>
+    <x v="7"/>
+    <n v="9.75"/>
+    <n v="25"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="12"/>
+    <x v="6"/>
+    <n v="14.5"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="12"/>
+    <x v="12"/>
+    <x v="6"/>
+    <n v="14.5"/>
+    <n v="30"/>
+    <n v="20"/>
+    <n v="290"/>
+    <x v="1"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="12"/>
+    <x v="6"/>
+    <n v="14.5"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="13"/>
+    <x v="1"/>
+    <n v="18"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="13"/>
+    <x v="13"/>
+    <x v="1"/>
+    <n v="18"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="13"/>
+    <x v="1"/>
+    <n v="18"/>
+    <n v="20"/>
+    <n v="14"/>
+    <n v="252"/>
+    <x v="1"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="6.25"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="6.25"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="27"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="14"/>
+    <x v="7"/>
+    <n v="11.5"/>
+    <n v="40"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="14"/>
+    <x v="7"/>
+    <n v="11.5"/>
+    <n v="40"/>
+    <n v="30"/>
+    <n v="345"/>
+    <x v="1"/>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="14"/>
+    <x v="7"/>
+    <n v="11.5"/>
+    <n v="40"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="30"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="15"/>
+    <x v="4"/>
+    <n v="89"/>
+    <n v="25"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="31"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="15"/>
+    <x v="15"/>
+    <x v="4"/>
+    <n v="89"/>
+    <n v="25"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="32"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="15"/>
+    <x v="4"/>
+    <n v="89"/>
+    <n v="25"/>
+    <n v="10"/>
+    <n v="890"/>
+    <x v="1"/>
+    <x v="33"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="125"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="34"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="125"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="35"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="3"/>
+    <n v="475"/>
+    <n v="8"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="36"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="3"/>
+    <n v="475"/>
+    <n v="8"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="37"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="4"/>
+    <n v="18.75"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="38"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="4"/>
+    <n v="18.75"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="39"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <n v="6.5"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="40"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="5"/>
+    <n v="6.5"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="41"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="145"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="42"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="145"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="43"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="95"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="44"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="8"/>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="95"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="45"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="9"/>
+    <x v="5"/>
+    <n v="22.5"/>
+    <n v="8"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="46"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="9"/>
+    <x v="5"/>
+    <n v="22.5"/>
+    <n v="8"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="47"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="16"/>
+    <x v="8"/>
+    <n v="1.25"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="48"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="16"/>
+    <x v="16"/>
+    <x v="8"/>
+    <n v="1.25"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="18.75"/>
+    <x v="1"/>
+    <x v="49"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="16"/>
+    <x v="8"/>
+    <n v="1.25"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="50"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="17"/>
+    <x v="8"/>
+    <n v="2.1"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="51"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="17"/>
+    <x v="17"/>
+    <x v="8"/>
+    <n v="2.1"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="52"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="17"/>
+    <x v="8"/>
+    <n v="2.1"/>
+    <n v="100"/>
+    <n v="10"/>
+    <n v="21"/>
+    <x v="1"/>
+    <x v="53"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="18"/>
+    <x v="9"/>
+    <n v="3.75"/>
+    <n v="100"/>
+    <n v="25"/>
+    <n v="93.75"/>
+    <x v="1"/>
+    <x v="54"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="18"/>
+    <x v="18"/>
+    <x v="9"/>
+    <n v="3.75"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="55"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="18"/>
+    <x v="9"/>
+    <n v="3.75"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="56"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="19"/>
+    <x v="8"/>
+    <n v="18.5"/>
+    <n v="75"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="57"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="19"/>
+    <x v="19"/>
+    <x v="8"/>
+    <n v="18.5"/>
+    <n v="75"/>
+    <n v="25"/>
+    <n v="462.5"/>
+    <x v="1"/>
+    <x v="58"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="19"/>
+    <x v="19"/>
+    <x v="8"/>
+    <n v="18.5"/>
+    <n v="75"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="59"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38DC400E-84BC-4A77-AD46-FA601CF5F496}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A4:E96" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="12">
+    <pivotField axis="axisCol" subtotalTop="0" showAll="0" insertBlankRow="1">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="10"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="2"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0" insertBlankRow="1">
+      <items count="21">
+        <item x="15"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="14"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="19"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0" insertBlankRow="1">
+      <items count="11">
+        <item x="9"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField subtotalTop="0" showAll="0" insertBlankRow="1"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" insertBlankRow="1"/>
+    <pivotField subtotalTop="0" showAll="0" insertBlankRow="1"/>
+    <pivotField subtotalTop="0" showAll="0" insertBlankRow="1"/>
+    <pivotField axis="axisPage" subtotalTop="0" showAll="0" insertBlankRow="1">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" numFmtId="14" subtotalTop="0" showAll="0" insertBlankRow="1">
+      <items count="61">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField subtotalTop="0" showAll="0" insertBlankRow="1">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField subtotalTop="0" showAll="0" insertBlankRow="1">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="3"/>
+    <field x="1"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="91">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="18"/>
+    </i>
+    <i t="default">
+      <x/>
+    </i>
+    <i t="blank">
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x v="15"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="6"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="5"/>
+    </i>
+    <i t="default">
+      <x v="1"/>
+    </i>
+    <i t="blank">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i t="blank" r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="2">
+      <x v="16"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="11"/>
+    </i>
+    <i t="default">
+      <x v="2"/>
+    </i>
+    <i t="blank">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="2">
+      <x v="14"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i r="2">
+      <x v="11"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="14"/>
+    </i>
+    <i t="default">
+      <x v="3"/>
+    </i>
+    <i t="blank">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="10"/>
+    </i>
+    <i t="blank" r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="6"/>
+    </i>
+    <i t="default">
+      <x v="4"/>
+    </i>
+    <i t="blank">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i r="2">
+      <x v="2"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="18"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="19"/>
+    </i>
+    <i t="default">
+      <x v="5"/>
+    </i>
+    <i t="blank">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x v="17"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="7"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="4"/>
+    </i>
+    <i t="default">
+      <x v="6"/>
+    </i>
+    <i t="blank">
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i r="2">
+      <x v="12"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i r="2">
+      <x v="13"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="15"/>
+    </i>
+    <i t="default">
+      <x v="7"/>
+    </i>
+    <i t="blank">
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="13"/>
+    </i>
+    <i t="default">
+      <x v="8"/>
+    </i>
+    <i t="blank">
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="2">
+      <x v="9"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i t="blank" r="1">
+      <x v="7"/>
+    </i>
+    <i t="default">
+      <x v="9"/>
+    </i>
+    <i t="blank">
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="8" item="1" hier="-1"/>
+    <pageField fld="9" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Reorder Level" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleMedium5" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 SubtotalsOnTopDefault="0" InsertBlankRowDefault="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Supplier" xr10:uid="{8194BE1B-4C3E-4889-9801-C5B859E7B9E5}" sourceName="Supplier">
+  <pivotTables>
+    <pivotTable tabId="6" name="PivotTable2"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1072809326">
+      <items count="10">
+        <i x="9" s="1"/>
+        <i x="1" s="1"/>
+        <i x="4" s="1"/>
+        <i x="2" s="1"/>
+        <i x="0" s="1"/>
+        <i x="8" s="1"/>
+        <i x="6" s="1"/>
+        <i x="5" s="1"/>
+        <i x="3" s="1"/>
+        <i x="7" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Supplier" xr10:uid="{A74DBC4E-85A0-4D37-965B-392D189D547F}" cache="Slicer_Supplier" caption="Supplier" rowHeight="241300"/>
+</slicers>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="C4:Q31" totalsRowCount="1">
   <autoFilter ref="C4:Q30" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
@@ -7055,7 +9390,7 @@
     <col min="3" max="6" width="30.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" customWidth="1"/>
     <col min="8" max="8" width="12.3984375" customWidth="1"/>
-    <col min="9" max="9" width="9.46484375" customWidth="1"/>
+    <col min="9" max="9" width="11.796875" customWidth="1"/>
     <col min="10" max="10" width="11.86328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7126,6 +9461,9 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
+      <c r="J2" s="77">
+        <v>46275</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="69" t="s">
@@ -7162,6 +9500,9 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
+      <c r="J3" s="77">
+        <v>46276</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="69" t="s">
@@ -7198,6 +9539,9 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
+      <c r="J4" s="77">
+        <v>46277</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="69" t="s">
@@ -7234,6 +9578,9 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
+      <c r="J5" s="77">
+        <v>46278</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="69" t="s">
@@ -7270,6 +9617,9 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
+      <c r="J6" s="77">
+        <v>46279</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="69" t="s">
@@ -7306,6 +9656,9 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
+      <c r="J7" s="77">
+        <v>46280</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="69" t="s">
@@ -7342,6 +9695,9 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
+      <c r="J8" s="77">
+        <v>46281</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="69" t="s">
@@ -7378,6 +9734,9 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
+      <c r="J9" s="77">
+        <v>46282</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="69" t="s">
@@ -7414,6 +9773,9 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
+      <c r="J10" s="77">
+        <v>46283</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="69" t="s">
@@ -7450,6 +9812,9 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
+      <c r="J11" s="77">
+        <v>46284</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="69" t="s">
@@ -7486,6 +9851,9 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
+      <c r="J12" s="77">
+        <v>46285</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="69" t="s">
@@ -7522,6 +9890,9 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
+      <c r="J13" s="77">
+        <v>46286</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="69" t="s">
@@ -7558,6 +9929,9 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
+      <c r="J14" s="77">
+        <v>46287</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="69" t="s">
@@ -7594,6 +9968,9 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
+      <c r="J15" s="77">
+        <v>46288</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="69" t="s">
@@ -7630,8 +10007,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J16" s="77">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="69" t="s">
         <v>62</v>
       </c>
@@ -7666,8 +10046,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J17" s="77">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="69" t="s">
         <v>64</v>
       </c>
@@ -7702,8 +10085,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J18" s="77">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="69" t="s">
         <v>62</v>
       </c>
@@ -7738,8 +10124,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J19" s="77">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="69" t="s">
         <v>64</v>
       </c>
@@ -7774,8 +10163,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J20" s="77">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="69" t="s">
         <v>65</v>
       </c>
@@ -7810,8 +10202,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J21" s="77">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="69" t="s">
         <v>62</v>
       </c>
@@ -7846,8 +10241,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J22" s="77">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="69" t="s">
         <v>64</v>
       </c>
@@ -7882,8 +10280,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J23" s="77">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="69" t="s">
         <v>65</v>
       </c>
@@ -7918,8 +10319,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J24" s="77">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="69" t="s">
         <v>62</v>
       </c>
@@ -7954,8 +10358,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J25" s="77">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="69" t="s">
         <v>64</v>
       </c>
@@ -7990,8 +10397,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J26" s="77">
+        <v>46299</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="69" t="s">
         <v>65</v>
       </c>
@@ -8026,8 +10436,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J27" s="77">
+        <v>46300</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="69" t="s">
         <v>64</v>
       </c>
@@ -8062,8 +10475,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J28" s="77">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="69" t="s">
         <v>65</v>
       </c>
@@ -8098,8 +10514,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J29" s="77">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="69" t="s">
         <v>62</v>
       </c>
@@ -8134,8 +10553,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J30" s="77">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="69" t="s">
         <v>64</v>
       </c>
@@ -8170,8 +10592,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J31" s="77">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="69" t="s">
         <v>65</v>
       </c>
@@ -8206,8 +10631,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J32" s="77">
+        <v>46305</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="69" t="s">
         <v>62</v>
       </c>
@@ -8242,8 +10670,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J33" s="77">
+        <v>46306</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="69" t="s">
         <v>64</v>
       </c>
@@ -8278,8 +10709,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J34" s="77">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="69" t="s">
         <v>65</v>
       </c>
@@ -8314,8 +10748,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J35" s="77">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" s="69" t="s">
         <v>64</v>
       </c>
@@ -8350,8 +10787,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J36" s="77">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="69" t="s">
         <v>65</v>
       </c>
@@ -8386,8 +10826,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J37" s="77">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="69" t="s">
         <v>62</v>
       </c>
@@ -8422,8 +10865,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J38" s="77">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="69" t="s">
         <v>65</v>
       </c>
@@ -8458,8 +10904,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J39" s="77">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="69" t="s">
         <v>62</v>
       </c>
@@ -8494,8 +10943,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J40" s="77">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="69" t="s">
         <v>64</v>
       </c>
@@ -8530,8 +10982,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J41" s="77">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="69" t="s">
         <v>64</v>
       </c>
@@ -8566,8 +11021,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J42" s="77">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" s="69" t="s">
         <v>65</v>
       </c>
@@ -8602,8 +11060,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J43" s="77">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" s="69" t="s">
         <v>62</v>
       </c>
@@ -8638,8 +11099,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J44" s="77">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" s="69" t="s">
         <v>65</v>
       </c>
@@ -8674,8 +11138,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J45" s="77">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="69" t="s">
         <v>62</v>
       </c>
@@ -8710,8 +11177,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J46" s="77">
+        <v>46319</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" s="69" t="s">
         <v>64</v>
       </c>
@@ -8746,8 +11216,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J47" s="77">
+        <v>46320</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="69" t="s">
         <v>64</v>
       </c>
@@ -8782,8 +11255,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J48" s="77">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" s="69" t="s">
         <v>65</v>
       </c>
@@ -8818,8 +11294,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J49" s="77">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="69" t="s">
         <v>62</v>
       </c>
@@ -8854,8 +11333,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J50" s="77">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="69" t="s">
         <v>64</v>
       </c>
@@ -8890,8 +11372,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J51" s="77">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" s="69" t="s">
         <v>65</v>
       </c>
@@ -8926,8 +11411,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J52" s="77">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="69" t="s">
         <v>62</v>
       </c>
@@ -8962,8 +11450,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J53" s="77">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="69" t="s">
         <v>64</v>
       </c>
@@ -8998,8 +11489,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J54" s="77">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="69" t="s">
         <v>65</v>
       </c>
@@ -9034,8 +11528,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J55" s="77">
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" s="69" t="s">
         <v>62</v>
       </c>
@@ -9070,8 +11567,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J56" s="77">
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="69" t="s">
         <v>64</v>
       </c>
@@ -9106,8 +11606,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J57" s="77">
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="69" t="s">
         <v>65</v>
       </c>
@@ -9142,8 +11645,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J58" s="77">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="69" t="s">
         <v>62</v>
       </c>
@@ -9178,8 +11684,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J59" s="77">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="69" t="s">
         <v>64</v>
       </c>
@@ -9214,8 +11723,11 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J60" s="77">
+        <v>46333</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="69" t="s">
         <v>65</v>
       </c>
@@ -9249,6 +11761,9 @@
       <c r="I61" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
+      </c>
+      <c r="J61" s="77">
+        <v>46334</v>
       </c>
     </row>
   </sheetData>
@@ -9303,4 +11818,1050 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA3C0E5C-5F90-48A5-9B79-2947468EC928}">
+  <dimension ref="A1:E96"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="38.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="78" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="78" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="78" t="s">
+        <v>308</v>
+      </c>
+      <c r="B4" s="78" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="78" t="s">
+        <v>305</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="79" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="81" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="80"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="82" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="80">
+        <v>100</v>
+      </c>
+      <c r="C8" s="80">
+        <v>100</v>
+      </c>
+      <c r="D8" s="80">
+        <v>100</v>
+      </c>
+      <c r="E8" s="80">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="81"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="79" t="s">
+        <v>309</v>
+      </c>
+      <c r="B10" s="80">
+        <v>100</v>
+      </c>
+      <c r="C10" s="80">
+        <v>100</v>
+      </c>
+      <c r="D10" s="80">
+        <v>100</v>
+      </c>
+      <c r="E10" s="80">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="79"/>
+      <c r="B11" s="80"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="80"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="80"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="81" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="80"/>
+      <c r="C13" s="80"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="80"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="82" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="80">
+        <v>15</v>
+      </c>
+      <c r="C14" s="80">
+        <v>15</v>
+      </c>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="81"/>
+      <c r="B15" s="80"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="80"/>
+      <c r="C16" s="80"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="80"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="82" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="80">
+        <v>20</v>
+      </c>
+      <c r="C17" s="80">
+        <v>20</v>
+      </c>
+      <c r="D17" s="80">
+        <v>20</v>
+      </c>
+      <c r="E17" s="80">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="81"/>
+      <c r="B18" s="80"/>
+      <c r="C18" s="80"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="80"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" s="79" t="s">
+        <v>310</v>
+      </c>
+      <c r="B19" s="80">
+        <v>35</v>
+      </c>
+      <c r="C19" s="80">
+        <v>35</v>
+      </c>
+      <c r="D19" s="80">
+        <v>20</v>
+      </c>
+      <c r="E19" s="80">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" s="79"/>
+      <c r="B20" s="80"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" s="79" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="80"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="81" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="80"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="82" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="80">
+        <v>25</v>
+      </c>
+      <c r="C23" s="80">
+        <v>25</v>
+      </c>
+      <c r="D23" s="80">
+        <v>25</v>
+      </c>
+      <c r="E23" s="80">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" s="81"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="80"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A26" s="82" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="80">
+        <v>3</v>
+      </c>
+      <c r="C26" s="80">
+        <v>3</v>
+      </c>
+      <c r="D26" s="80"/>
+      <c r="E26" s="80">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A27" s="81"/>
+      <c r="B27" s="80"/>
+      <c r="C27" s="80"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="80"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A28" s="79" t="s">
+        <v>311</v>
+      </c>
+      <c r="B28" s="80">
+        <v>28</v>
+      </c>
+      <c r="C28" s="80">
+        <v>28</v>
+      </c>
+      <c r="D28" s="80">
+        <v>25</v>
+      </c>
+      <c r="E28" s="80">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A29" s="79"/>
+      <c r="B29" s="80"/>
+      <c r="C29" s="80"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="80"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A30" s="79" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="80"/>
+      <c r="C30" s="80"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="80"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A31" s="81" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="80"/>
+      <c r="C31" s="80"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="80"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A32" s="82" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="80"/>
+      <c r="C32" s="80">
+        <v>5</v>
+      </c>
+      <c r="D32" s="80">
+        <v>5</v>
+      </c>
+      <c r="E32" s="80">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A33" s="81"/>
+      <c r="B33" s="80"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34" s="81" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="80"/>
+      <c r="C34" s="80"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="80"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A35" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="80">
+        <v>5</v>
+      </c>
+      <c r="C35" s="80">
+        <v>5</v>
+      </c>
+      <c r="D35" s="80"/>
+      <c r="E35" s="80">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36" s="81"/>
+      <c r="B36" s="80"/>
+      <c r="C36" s="80"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="80"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A37" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="B37" s="80">
+        <v>5</v>
+      </c>
+      <c r="C37" s="80">
+        <v>10</v>
+      </c>
+      <c r="D37" s="80">
+        <v>5</v>
+      </c>
+      <c r="E37" s="80">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A38" s="79"/>
+      <c r="B38" s="80"/>
+      <c r="C38" s="80"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="80"/>
+      <c r="C39" s="80"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="80"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" s="81" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" s="80"/>
+      <c r="C40" s="80"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="80"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A41" s="82" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" s="80"/>
+      <c r="C41" s="80">
+        <v>9</v>
+      </c>
+      <c r="D41" s="80">
+        <v>9</v>
+      </c>
+      <c r="E41" s="80">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" s="81"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A43" s="81" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" s="80"/>
+      <c r="C43" s="80"/>
+      <c r="D43" s="80"/>
+      <c r="E43" s="80"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A44" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="80"/>
+      <c r="C44" s="80">
+        <v>15</v>
+      </c>
+      <c r="D44" s="80">
+        <v>15</v>
+      </c>
+      <c r="E44" s="80">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A45" s="81"/>
+      <c r="B45" s="80"/>
+      <c r="C45" s="80"/>
+      <c r="D45" s="80"/>
+      <c r="E45" s="80"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" s="79" t="s">
+        <v>313</v>
+      </c>
+      <c r="B46" s="80"/>
+      <c r="C46" s="80">
+        <v>24</v>
+      </c>
+      <c r="D46" s="80">
+        <v>24</v>
+      </c>
+      <c r="E46" s="80">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" s="79"/>
+      <c r="B47" s="80"/>
+      <c r="C47" s="80"/>
+      <c r="D47" s="80"/>
+      <c r="E47" s="80"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A48" s="79" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" s="80"/>
+      <c r="C48" s="80"/>
+      <c r="D48" s="80"/>
+      <c r="E48" s="80"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A49" s="81" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="80"/>
+      <c r="C49" s="80"/>
+      <c r="D49" s="80"/>
+      <c r="E49" s="80"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A50" s="82" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" s="80">
+        <v>15</v>
+      </c>
+      <c r="C50" s="80">
+        <v>15</v>
+      </c>
+      <c r="D50" s="80">
+        <v>15</v>
+      </c>
+      <c r="E50" s="80">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A51" s="81"/>
+      <c r="B51" s="80"/>
+      <c r="C51" s="80"/>
+      <c r="D51" s="80"/>
+      <c r="E51" s="80"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A52" s="81" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" s="80"/>
+      <c r="C52" s="80"/>
+      <c r="D52" s="80"/>
+      <c r="E52" s="80"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A53" s="82" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="80">
+        <v>100</v>
+      </c>
+      <c r="C53" s="80">
+        <v>100</v>
+      </c>
+      <c r="D53" s="80">
+        <v>100</v>
+      </c>
+      <c r="E53" s="80">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A54" s="81"/>
+      <c r="B54" s="80"/>
+      <c r="C54" s="80"/>
+      <c r="D54" s="80"/>
+      <c r="E54" s="80"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A55" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="80"/>
+      <c r="C55" s="80"/>
+      <c r="D55" s="80"/>
+      <c r="E55" s="80"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A56" s="82" t="s">
+        <v>129</v>
+      </c>
+      <c r="B56" s="80">
+        <v>75</v>
+      </c>
+      <c r="C56" s="80">
+        <v>75</v>
+      </c>
+      <c r="D56" s="80">
+        <v>75</v>
+      </c>
+      <c r="E56" s="80">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A57" s="81"/>
+      <c r="B57" s="80"/>
+      <c r="C57" s="80"/>
+      <c r="D57" s="80"/>
+      <c r="E57" s="80"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A58" s="79" t="s">
+        <v>314</v>
+      </c>
+      <c r="B58" s="80">
+        <v>190</v>
+      </c>
+      <c r="C58" s="80">
+        <v>190</v>
+      </c>
+      <c r="D58" s="80">
+        <v>190</v>
+      </c>
+      <c r="E58" s="80">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A59" s="79"/>
+      <c r="B59" s="80"/>
+      <c r="C59" s="80"/>
+      <c r="D59" s="80"/>
+      <c r="E59" s="80"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A60" s="79" t="s">
+        <v>99</v>
+      </c>
+      <c r="B60" s="80"/>
+      <c r="C60" s="80"/>
+      <c r="D60" s="80"/>
+      <c r="E60" s="80"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A61" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" s="80"/>
+      <c r="C61" s="80"/>
+      <c r="D61" s="80"/>
+      <c r="E61" s="80"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A62" s="82" t="s">
+        <v>98</v>
+      </c>
+      <c r="B62" s="80">
+        <v>50</v>
+      </c>
+      <c r="C62" s="80">
+        <v>50</v>
+      </c>
+      <c r="D62" s="80">
+        <v>50</v>
+      </c>
+      <c r="E62" s="80">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A63" s="81"/>
+      <c r="B63" s="80"/>
+      <c r="C63" s="80"/>
+      <c r="D63" s="80"/>
+      <c r="E63" s="80"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A64" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" s="80"/>
+      <c r="C64" s="80"/>
+      <c r="D64" s="80"/>
+      <c r="E64" s="80"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A65" s="82" t="s">
+        <v>104</v>
+      </c>
+      <c r="B65" s="80">
+        <v>30</v>
+      </c>
+      <c r="C65" s="80">
+        <v>30</v>
+      </c>
+      <c r="D65" s="80">
+        <v>30</v>
+      </c>
+      <c r="E65" s="80">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A66" s="81"/>
+      <c r="B66" s="80"/>
+      <c r="C66" s="80"/>
+      <c r="D66" s="80"/>
+      <c r="E66" s="80"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A67" s="79" t="s">
+        <v>315</v>
+      </c>
+      <c r="B67" s="80">
+        <v>80</v>
+      </c>
+      <c r="C67" s="80">
+        <v>80</v>
+      </c>
+      <c r="D67" s="80">
+        <v>80</v>
+      </c>
+      <c r="E67" s="80">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A68" s="79"/>
+      <c r="B68" s="80"/>
+      <c r="C68" s="80"/>
+      <c r="D68" s="80"/>
+      <c r="E68" s="80"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A69" s="79" t="s">
+        <v>119</v>
+      </c>
+      <c r="B69" s="80"/>
+      <c r="C69" s="80"/>
+      <c r="D69" s="80"/>
+      <c r="E69" s="80"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A70" s="81" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="80"/>
+      <c r="C70" s="80"/>
+      <c r="D70" s="80"/>
+      <c r="E70" s="80"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A71" s="82" t="s">
+        <v>118</v>
+      </c>
+      <c r="B71" s="80"/>
+      <c r="C71" s="80">
+        <v>20</v>
+      </c>
+      <c r="D71" s="80">
+        <v>20</v>
+      </c>
+      <c r="E71" s="80">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A72" s="81"/>
+      <c r="B72" s="80"/>
+      <c r="C72" s="80"/>
+      <c r="D72" s="80"/>
+      <c r="E72" s="80"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A73" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="80"/>
+      <c r="C73" s="80"/>
+      <c r="D73" s="80"/>
+      <c r="E73" s="80"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A74" s="82" t="s">
+        <v>122</v>
+      </c>
+      <c r="B74" s="80"/>
+      <c r="C74" s="80">
+        <v>8</v>
+      </c>
+      <c r="D74" s="80">
+        <v>8</v>
+      </c>
+      <c r="E74" s="80">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A75" s="81"/>
+      <c r="B75" s="80"/>
+      <c r="C75" s="80"/>
+      <c r="D75" s="80"/>
+      <c r="E75" s="80"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A76" s="79" t="s">
+        <v>316</v>
+      </c>
+      <c r="B76" s="80"/>
+      <c r="C76" s="80">
+        <v>28</v>
+      </c>
+      <c r="D76" s="80">
+        <v>28</v>
+      </c>
+      <c r="E76" s="80">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A77" s="79"/>
+      <c r="B77" s="80"/>
+      <c r="C77" s="80"/>
+      <c r="D77" s="80"/>
+      <c r="E77" s="80"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A78" s="79" t="s">
+        <v>115</v>
+      </c>
+      <c r="B78" s="80"/>
+      <c r="C78" s="80"/>
+      <c r="D78" s="80"/>
+      <c r="E78" s="80"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A79" s="81" t="s">
+        <v>75</v>
+      </c>
+      <c r="B79" s="80"/>
+      <c r="C79" s="80"/>
+      <c r="D79" s="80"/>
+      <c r="E79" s="80"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A80" s="82" t="s">
+        <v>114</v>
+      </c>
+      <c r="B80" s="80">
+        <v>8</v>
+      </c>
+      <c r="C80" s="80"/>
+      <c r="D80" s="80">
+        <v>8</v>
+      </c>
+      <c r="E80" s="80">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A81" s="81"/>
+      <c r="B81" s="80"/>
+      <c r="C81" s="80"/>
+      <c r="D81" s="80"/>
+      <c r="E81" s="80"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A82" s="81" t="s">
+        <v>78</v>
+      </c>
+      <c r="B82" s="80"/>
+      <c r="C82" s="80"/>
+      <c r="D82" s="80"/>
+      <c r="E82" s="80"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A83" s="82" t="s">
+        <v>120</v>
+      </c>
+      <c r="B83" s="80">
+        <v>30</v>
+      </c>
+      <c r="C83" s="80"/>
+      <c r="D83" s="80">
+        <v>30</v>
+      </c>
+      <c r="E83" s="80">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A84" s="81"/>
+      <c r="B84" s="80"/>
+      <c r="C84" s="80"/>
+      <c r="D84" s="80"/>
+      <c r="E84" s="80"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A85" s="79" t="s">
+        <v>317</v>
+      </c>
+      <c r="B85" s="80">
+        <v>38</v>
+      </c>
+      <c r="C85" s="80"/>
+      <c r="D85" s="80">
+        <v>38</v>
+      </c>
+      <c r="E85" s="80">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A86" s="79"/>
+      <c r="B86" s="80"/>
+      <c r="C86" s="80"/>
+      <c r="D86" s="80"/>
+      <c r="E86" s="80"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A87" s="79" t="s">
+        <v>103</v>
+      </c>
+      <c r="B87" s="80"/>
+      <c r="C87" s="80"/>
+      <c r="D87" s="80"/>
+      <c r="E87" s="80"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A88" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="B88" s="80"/>
+      <c r="C88" s="80"/>
+      <c r="D88" s="80"/>
+      <c r="E88" s="80"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A89" s="82" t="s">
+        <v>102</v>
+      </c>
+      <c r="B89" s="80">
+        <v>25</v>
+      </c>
+      <c r="C89" s="80">
+        <v>25</v>
+      </c>
+      <c r="D89" s="80">
+        <v>25</v>
+      </c>
+      <c r="E89" s="80">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A90" s="81"/>
+      <c r="B90" s="80"/>
+      <c r="C90" s="80"/>
+      <c r="D90" s="80"/>
+      <c r="E90" s="80"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A91" s="81" t="s">
+        <v>72</v>
+      </c>
+      <c r="B91" s="80"/>
+      <c r="C91" s="80"/>
+      <c r="D91" s="80"/>
+      <c r="E91" s="80"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A92" s="82" t="s">
+        <v>107</v>
+      </c>
+      <c r="B92" s="80">
+        <v>40</v>
+      </c>
+      <c r="C92" s="80">
+        <v>40</v>
+      </c>
+      <c r="D92" s="80">
+        <v>40</v>
+      </c>
+      <c r="E92" s="80">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A93" s="81"/>
+      <c r="B93" s="80"/>
+      <c r="C93" s="80"/>
+      <c r="D93" s="80"/>
+      <c r="E93" s="80"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A94" s="79" t="s">
+        <v>318</v>
+      </c>
+      <c r="B94" s="80">
+        <v>65</v>
+      </c>
+      <c r="C94" s="80">
+        <v>65</v>
+      </c>
+      <c r="D94" s="80">
+        <v>65</v>
+      </c>
+      <c r="E94" s="80">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A95" s="79"/>
+      <c r="B95" s="80"/>
+      <c r="C95" s="80"/>
+      <c r="D95" s="80"/>
+      <c r="E95" s="80"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A96" s="79" t="s">
+        <v>306</v>
+      </c>
+      <c r="B96" s="80">
+        <v>541</v>
+      </c>
+      <c r="C96" s="80">
+        <v>560</v>
+      </c>
+      <c r="D96" s="80">
+        <v>575</v>
+      </c>
+      <c r="E96" s="80">
+        <v>1676</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/DataAnalyst.xlsx
+++ b/DataAnalyst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malik\OneDrive\Documents\Data\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E119B58-BFD9-4900-B6BC-CDF1444E59B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08626EE4-0399-430C-BA4D-06A93EACA91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId7"/>
+    <pivotCache cacheId="39" r:id="rId7"/>
   </pivotCaches>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
@@ -1311,7 +1311,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1498,7 +1498,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="8" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="10"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="11"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1533,6 +1532,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="10" applyFont="1"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="3" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{72D35A1C-E0E1-4D48-ACA5-2713C7D76C54}"/>
@@ -1548,7 +1552,37 @@
     <cellStyle name="Normal 8" xfId="9" xr:uid="{0EFC0AAE-EB0E-4FA2-885A-2DA2EB3F3608}"/>
     <cellStyle name="Normal 9" xfId="10" xr:uid="{DFABB175-7506-410D-8AC4-26F83CE150B7}"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="38">
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2311,7 +2345,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="malik" refreshedDate="46275.874918171299" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{E1D8D753-DAC5-4E1D-B12F-2B69C70CB065}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="malik" refreshedDate="46276.631442939812" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{E1D8D753-DAC5-4E1D-B12F-2B69C70CB065}">
   <cacheSource type="worksheet">
     <worksheetSource name="Inventory"/>
   </cacheSource>
@@ -3599,7 +3633,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38DC400E-84BC-4A77-AD46-FA601CF5F496}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38DC400E-84BC-4A77-AD46-FA601CF5F496}" name="PivotTable2" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:E96" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="12">
     <pivotField axis="axisCol" subtotalTop="0" showAll="0" insertBlankRow="1">
@@ -4493,50 +4527,50 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="C4:Q31" totalsRowCount="1">
   <autoFilter ref="C4:Q30" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" totalsRowLabel="Total" totalsRowDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMPANIES" totalsRowDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NUMBER OF EMPLOYEES" totalsRowDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COLOR" totalsRowDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LAUNCH DATE" totalsRowDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="QUANTITY" totalsRowFunction="sum" totalsRowDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PRICE" totalsRowFunction="sum" totalsRowDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AMOUNT" totalsRowFunction="sum" totalsRowDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="QUANTITY " totalsRowDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRICE " totalsRowDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="AMOUNT " totalsRowFunction="sum" totalsRowDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QUANTITY  " totalsRowDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="PRICE  " totalsRowDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="AMOUNT  " totalsRowFunction="sum" totalsRowDxfId="16"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="TOTAL" totalsRowFunction="sum" totalsRowDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" totalsRowLabel="Total" totalsRowDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMPANIES" totalsRowDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NUMBER OF EMPLOYEES" totalsRowDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COLOR" totalsRowDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LAUNCH DATE" totalsRowDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="QUANTITY" totalsRowFunction="sum" totalsRowDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PRICE" totalsRowFunction="sum" totalsRowDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AMOUNT" totalsRowFunction="sum" totalsRowDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="QUANTITY " totalsRowDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRICE " totalsRowDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="AMOUNT " totalsRowFunction="sum" totalsRowDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QUANTITY  " totalsRowDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="PRICE  " totalsRowDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="AMOUNT  " totalsRowFunction="sum" totalsRowDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="TOTAL" totalsRowFunction="sum" totalsRowDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}" name="Products" displayName="Products" ref="A1:F61" totalsRowShown="0" headerRowDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}" name="Products" displayName="Products" ref="A1:F61" totalsRowShown="0" headerRowDxfId="16">
   <autoFilter ref="A1:F61" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{E8F4DFB0-EC56-4CBF-9F8C-23EDCA50F713}" name="ProductID" dataCellStyle="Normal 3"/>
-    <tableColumn id="2" xr3:uid="{01A2DB73-B8C2-4A45-A7CC-94CB4A4A2FEF}" name="Product Name" dataDxfId="13" dataCellStyle="Comma 2"/>
+    <tableColumn id="2" xr3:uid="{01A2DB73-B8C2-4A45-A7CC-94CB4A4A2FEF}" name="Product Name" dataDxfId="15" dataCellStyle="Comma 2"/>
     <tableColumn id="3" xr3:uid="{D7712E33-EC2C-4BBC-9183-D4083230AE51}" name="Category" dataCellStyle="Normal 3"/>
-    <tableColumn id="4" xr3:uid="{10280736-93EE-4A73-97B0-1F59FABAB46F}" name="Cost/Unit" dataDxfId="12" dataCellStyle="Comma 2"/>
-    <tableColumn id="5" xr3:uid="{AC22B57B-F391-4278-9CEA-6381C3C7599A}" name="Reorder Level" dataDxfId="11" dataCellStyle="Normal 3"/>
-    <tableColumn id="6" xr3:uid="{ECE3A126-A7F6-4E8A-B4CA-AC1B78868DAB}" name="Supplier" dataDxfId="10" dataCellStyle="Normal 3"/>
+    <tableColumn id="4" xr3:uid="{10280736-93EE-4A73-97B0-1F59FABAB46F}" name="Cost/Unit" dataDxfId="14" dataCellStyle="Comma 2"/>
+    <tableColumn id="5" xr3:uid="{AC22B57B-F391-4278-9CEA-6381C3C7599A}" name="Reorder Level" dataDxfId="13" dataCellStyle="Normal 3"/>
+    <tableColumn id="6" xr3:uid="{ECE3A126-A7F6-4E8A-B4CA-AC1B78868DAB}" name="Supplier" dataDxfId="12" dataCellStyle="Normal 3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03C4EC66-596A-4191-8AD5-8C56A2B0936F}" name="Transactions" displayName="Transactions" ref="A1:F61" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03C4EC66-596A-4191-8AD5-8C56A2B0936F}" name="Transactions" displayName="Transactions" ref="A1:F61" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:F61" xr:uid="{03C4EC66-596A-4191-8AD5-8C56A2B0936F}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{CF0FBA31-2E94-4135-8B0A-A8ADD4C1D54E}" name="TransID"/>
-    <tableColumn id="2" xr3:uid="{EB83FE89-2487-49C6-80BE-246C3764EFC8}" name="Date" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{EB83FE89-2487-49C6-80BE-246C3764EFC8}" name="Date" dataDxfId="11"/>
     <tableColumn id="3" xr3:uid="{FE85118D-4F73-4CC4-947F-D727DBCF045B}" name="ProductID"/>
-    <tableColumn id="4" xr3:uid="{890FE897-5C0E-4846-94E3-254F9AB59CC8}" name="Site" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{D5DF56AA-CF75-4D46-9133-AE66DE368857}" name="Quantity" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{890FE897-5C0E-4846-94E3-254F9AB59CC8}" name="Site" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{D5DF56AA-CF75-4D46-9133-AE66DE368857}" name="Quantity" dataDxfId="9"/>
     <tableColumn id="6" xr3:uid="{8D0BBA31-EE38-4A83-9E89-796952F75830}" name="Type"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4544,7 +4578,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A5DC87FD-A8D1-440B-BAC9-DE34E48E5936}" name="Inventory" displayName="Inventory" ref="A1:J61" totalsRowShown="0" headerRowCellStyle="Normal 9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A5DC87FD-A8D1-440B-BAC9-DE34E48E5936}" name="Inventory" displayName="Inventory" ref="A1:J61" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="Normal 9">
   <autoFilter ref="A1:J61" xr:uid="{A5DC87FD-A8D1-440B-BAC9-DE34E48E5936}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J61">
     <sortCondition ref="I1:I61"/>
@@ -4552,25 +4586,25 @@
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{E8701318-3AEB-41C8-947D-8F382111F831}" name="Site" dataCellStyle="Normal 10"/>
     <tableColumn id="2" xr3:uid="{A8F9A49C-2A9D-43FA-9513-36E70E2B2700}" name="ProductID" dataCellStyle="Normal 10"/>
-    <tableColumn id="3" xr3:uid="{DD7691E1-3B82-419A-A596-FD7160832936}" name="Product Description" dataDxfId="35">
+    <tableColumn id="3" xr3:uid="{DD7691E1-3B82-419A-A596-FD7160832936}" name="Product Description" dataDxfId="37">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3B6081B7-6D7B-40BA-B050-3F97A1DD80EA}" name="Supplier" dataDxfId="34">
+    <tableColumn id="4" xr3:uid="{3B6081B7-6D7B-40BA-B050-3F97A1DD80EA}" name="Supplier" dataDxfId="36">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8BF557DE-8E2B-4AE9-8A66-D281C045EF9F}" name="Cost/Unit" dataDxfId="33">
+    <tableColumn id="5" xr3:uid="{8BF557DE-8E2B-4AE9-8A66-D281C045EF9F}" name="Cost/Unit" dataDxfId="35">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{82A09554-3010-4D9D-867D-4111E1CD453F}" name="Reorder Level" dataDxfId="32">
+    <tableColumn id="6" xr3:uid="{82A09554-3010-4D9D-867D-4111E1CD453F}" name="Reorder Level" dataDxfId="34">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{B0173CF8-A36E-441A-B27D-4CB13138DA80}" name="QuantityOnHand">
       <calculatedColumnFormula>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F1713281-EF53-48D5-9D64-F33AD9F1106B}" name="Stock Value" dataDxfId="31">
+    <tableColumn id="8" xr3:uid="{F1713281-EF53-48D5-9D64-F33AD9F1106B}" name="Stock Value" dataDxfId="33">
       <calculatedColumnFormula>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1AD33891-BE48-4965-8EAA-F8F9DE5AFD47}" name="Reorder" dataDxfId="30">
+    <tableColumn id="9" xr3:uid="{1AD33891-BE48-4965-8EAA-F8F9DE5AFD47}" name="Reorder" dataDxfId="32">
       <calculatedColumnFormula>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{02298217-ED20-499A-84FA-6F2061FCCDF1}" name="Order Date"/>
@@ -5499,23 +5533,23 @@
   <sheetData>
     <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="3:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="71"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
     </row>
     <row r="3" spans="3:17" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.65">
       <c r="C3" s="8"/>
@@ -5528,16 +5562,16 @@
       </c>
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
-      <c r="K3" s="75" t="s">
+      <c r="K3" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76"/>
-      <c r="N3" s="75" t="s">
+      <c r="L3" s="75"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
       <c r="Q3" s="13" t="s">
         <v>4</v>
       </c>
@@ -8143,23 +8177,23 @@
     <col min="6" max="6" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A1" s="58" t="s">
         <v>238</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="58" t="s">
         <v>239</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="82" t="s">
         <v>240</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="58" t="s">
         <v>47</v>
       </c>
     </row>
@@ -9394,43 +9428,43 @@
     <col min="10" max="10" width="11.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A1" s="68" t="s">
+    <row r="1" spans="1:10" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A1" s="83" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="84" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="68" t="s">
+      <c r="F1" s="83" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="68" t="s">
+      <c r="G1" s="83" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="68" t="s">
+      <c r="H1" s="83" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="68" t="s">
+      <c r="I1" s="83" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="68" t="s">
+      <c r="J1" s="83" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="68" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="str">
@@ -9461,15 +9495,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="J2" s="77">
+      <c r="J2" s="76">
         <v>46275</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="68" t="s">
         <v>67</v>
       </c>
       <c r="C3" t="str">
@@ -9500,15 +9534,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="J3" s="77">
+      <c r="J3" s="76">
         <v>46276</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="68" t="s">
         <v>71</v>
       </c>
       <c r="C4" t="str">
@@ -9539,15 +9573,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="J4" s="77">
+      <c r="J4" s="76">
         <v>46277</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="68" t="s">
         <v>74</v>
       </c>
       <c r="C5" t="str">
@@ -9578,15 +9612,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="J5" s="77">
+      <c r="J5" s="76">
         <v>46278</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="68" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="str">
@@ -9617,15 +9651,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="J6" s="77">
+      <c r="J6" s="76">
         <v>46279</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" s="69" t="s">
+      <c r="A7" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="68" t="s">
         <v>76</v>
       </c>
       <c r="C7" t="str">
@@ -9656,15 +9690,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="J7" s="77">
+      <c r="J7" s="76">
         <v>46280</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="68" t="s">
         <v>77</v>
       </c>
       <c r="C8" t="str">
@@ -9695,15 +9729,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="J8" s="77">
+      <c r="J8" s="76">
         <v>46281</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" s="69" t="s">
+      <c r="A9" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="68" t="s">
         <v>78</v>
       </c>
       <c r="C9" t="str">
@@ -9734,15 +9768,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="J9" s="77">
+      <c r="J9" s="76">
         <v>46282</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" s="69" t="s">
+      <c r="A10" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="68" t="s">
         <v>79</v>
       </c>
       <c r="C10" t="str">
@@ -9773,15 +9807,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="J10" s="77">
+      <c r="J10" s="76">
         <v>46283</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" s="69" t="s">
+      <c r="A11" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="68" t="s">
         <v>80</v>
       </c>
       <c r="C11" t="str">
@@ -9812,15 +9846,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="J11" s="77">
+      <c r="J11" s="76">
         <v>46284</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" s="69" t="s">
+      <c r="A12" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="69" t="s">
+      <c r="B12" s="68" t="s">
         <v>63</v>
       </c>
       <c r="C12" t="str">
@@ -9851,15 +9885,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J12" s="77">
+      <c r="J12" s="76">
         <v>46285</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A13" s="69" t="s">
+      <c r="A13" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="68" t="s">
         <v>63</v>
       </c>
       <c r="C13" t="str">
@@ -9890,15 +9924,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J13" s="77">
+      <c r="J13" s="76">
         <v>46286</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" s="69" t="s">
+      <c r="A14" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="68" t="s">
         <v>66</v>
       </c>
       <c r="C14" t="str">
@@ -9929,15 +9963,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J14" s="77">
+      <c r="J14" s="76">
         <v>46287</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A15" s="69" t="s">
+      <c r="A15" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="68" t="s">
         <v>66</v>
       </c>
       <c r="C15" t="str">
@@ -9968,15 +10002,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J15" s="77">
+      <c r="J15" s="76">
         <v>46288</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A16" s="69" t="s">
+      <c r="A16" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="68" t="s">
         <v>66</v>
       </c>
       <c r="C16" t="str">
@@ -10007,15 +10041,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J16" s="77">
+      <c r="J16" s="76">
         <v>46289</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A17" s="69" t="s">
+      <c r="A17" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="68" t="s">
         <v>67</v>
       </c>
       <c r="C17" t="str">
@@ -10046,15 +10080,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J17" s="77">
+      <c r="J17" s="76">
         <v>46290</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A18" s="69" t="s">
+      <c r="A18" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="68" t="s">
         <v>67</v>
       </c>
       <c r="C18" t="str">
@@ -10085,15 +10119,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J18" s="77">
+      <c r="J18" s="76">
         <v>46291</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A19" s="69" t="s">
+      <c r="A19" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="68" t="s">
         <v>68</v>
       </c>
       <c r="C19" t="str">
@@ -10124,15 +10158,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J19" s="77">
+      <c r="J19" s="76">
         <v>46292</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" s="69" t="s">
+      <c r="A20" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="68" t="s">
         <v>68</v>
       </c>
       <c r="C20" t="str">
@@ -10163,15 +10197,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J20" s="77">
+      <c r="J20" s="76">
         <v>46293</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A21" s="69" t="s">
+      <c r="A21" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="68" t="s">
         <v>68</v>
       </c>
       <c r="C21" t="str">
@@ -10202,15 +10236,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J21" s="77">
+      <c r="J21" s="76">
         <v>46294</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A22" s="69" t="s">
+      <c r="A22" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="68" t="s">
         <v>69</v>
       </c>
       <c r="C22" t="str">
@@ -10241,15 +10275,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J22" s="77">
+      <c r="J22" s="76">
         <v>46295</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A23" s="69" t="s">
+      <c r="A23" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="69" t="s">
+      <c r="B23" s="68" t="s">
         <v>69</v>
       </c>
       <c r="C23" t="str">
@@ -10280,15 +10314,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J23" s="77">
+      <c r="J23" s="76">
         <v>46296</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A24" s="69" t="s">
+      <c r="A24" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B24" s="69" t="s">
+      <c r="B24" s="68" t="s">
         <v>69</v>
       </c>
       <c r="C24" t="str">
@@ -10319,15 +10353,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J24" s="77">
+      <c r="J24" s="76">
         <v>46297</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A25" s="69" t="s">
+      <c r="A25" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="69" t="s">
+      <c r="B25" s="68" t="s">
         <v>70</v>
       </c>
       <c r="C25" t="str">
@@ -10358,15 +10392,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J25" s="77">
+      <c r="J25" s="76">
         <v>46298</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A26" s="69" t="s">
+      <c r="A26" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="69" t="s">
+      <c r="B26" s="68" t="s">
         <v>70</v>
       </c>
       <c r="C26" t="str">
@@ -10397,15 +10431,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J26" s="77">
+      <c r="J26" s="76">
         <v>46299</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A27" s="69" t="s">
+      <c r="A27" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="69" t="s">
+      <c r="B27" s="68" t="s">
         <v>70</v>
       </c>
       <c r="C27" t="str">
@@ -10436,15 +10470,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J27" s="77">
+      <c r="J27" s="76">
         <v>46300</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A28" s="69" t="s">
+      <c r="A28" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="69" t="s">
+      <c r="B28" s="68" t="s">
         <v>71</v>
       </c>
       <c r="C28" t="str">
@@ -10475,15 +10509,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J28" s="77">
+      <c r="J28" s="76">
         <v>46301</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A29" s="69" t="s">
+      <c r="A29" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="69" t="s">
+      <c r="B29" s="68" t="s">
         <v>71</v>
       </c>
       <c r="C29" t="str">
@@ -10514,15 +10548,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J29" s="77">
+      <c r="J29" s="76">
         <v>46302</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A30" s="69" t="s">
+      <c r="A30" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="69" t="s">
+      <c r="B30" s="68" t="s">
         <v>72</v>
       </c>
       <c r="C30" t="str">
@@ -10553,15 +10587,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J30" s="77">
+      <c r="J30" s="76">
         <v>46303</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A31" s="69" t="s">
+      <c r="A31" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B31" s="69" t="s">
+      <c r="B31" s="68" t="s">
         <v>72</v>
       </c>
       <c r="C31" t="str">
@@ -10592,15 +10626,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J31" s="77">
+      <c r="J31" s="76">
         <v>46304</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A32" s="69" t="s">
+      <c r="A32" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="69" t="s">
+      <c r="B32" s="68" t="s">
         <v>72</v>
       </c>
       <c r="C32" t="str">
@@ -10631,15 +10665,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J32" s="77">
+      <c r="J32" s="76">
         <v>46305</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A33" s="69" t="s">
+      <c r="A33" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="69" t="s">
+      <c r="B33" s="68" t="s">
         <v>73</v>
       </c>
       <c r="C33" t="str">
@@ -10670,15 +10704,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J33" s="77">
+      <c r="J33" s="76">
         <v>46306</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A34" s="69" t="s">
+      <c r="A34" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="69" t="s">
+      <c r="B34" s="68" t="s">
         <v>73</v>
       </c>
       <c r="C34" t="str">
@@ -10709,15 +10743,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J34" s="77">
+      <c r="J34" s="76">
         <v>46307</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A35" s="69" t="s">
+      <c r="A35" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="69" t="s">
+      <c r="B35" s="68" t="s">
         <v>73</v>
       </c>
       <c r="C35" t="str">
@@ -10748,15 +10782,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J35" s="77">
+      <c r="J35" s="76">
         <v>46308</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A36" s="69" t="s">
+      <c r="A36" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B36" s="69" t="s">
+      <c r="B36" s="68" t="s">
         <v>74</v>
       </c>
       <c r="C36" t="str">
@@ -10787,15 +10821,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J36" s="77">
+      <c r="J36" s="76">
         <v>46309</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A37" s="69" t="s">
+      <c r="A37" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="69" t="s">
+      <c r="B37" s="68" t="s">
         <v>74</v>
       </c>
       <c r="C37" t="str">
@@ -10826,15 +10860,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J37" s="77">
+      <c r="J37" s="76">
         <v>46310</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A38" s="69" t="s">
+      <c r="A38" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B38" s="69" t="s">
+      <c r="B38" s="68" t="s">
         <v>75</v>
       </c>
       <c r="C38" t="str">
@@ -10865,15 +10899,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J38" s="77">
+      <c r="J38" s="76">
         <v>46311</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A39" s="69" t="s">
+      <c r="A39" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="69" t="s">
+      <c r="B39" s="68" t="s">
         <v>75</v>
       </c>
       <c r="C39" t="str">
@@ -10904,15 +10938,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J39" s="77">
+      <c r="J39" s="76">
         <v>46312</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A40" s="69" t="s">
+      <c r="A40" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="69" t="s">
+      <c r="B40" s="68" t="s">
         <v>76</v>
       </c>
       <c r="C40" t="str">
@@ -10943,15 +10977,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J40" s="77">
+      <c r="J40" s="76">
         <v>46313</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A41" s="69" t="s">
+      <c r="A41" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B41" s="69" t="s">
+      <c r="B41" s="68" t="s">
         <v>76</v>
       </c>
       <c r="C41" t="str">
@@ -10982,15 +11016,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J41" s="77">
+      <c r="J41" s="76">
         <v>46314</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A42" s="69" t="s">
+      <c r="A42" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B42" s="69" t="s">
+      <c r="B42" s="68" t="s">
         <v>77</v>
       </c>
       <c r="C42" t="str">
@@ -11021,15 +11055,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J42" s="77">
+      <c r="J42" s="76">
         <v>46315</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A43" s="69" t="s">
+      <c r="A43" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B43" s="69" t="s">
+      <c r="B43" s="68" t="s">
         <v>77</v>
       </c>
       <c r="C43" t="str">
@@ -11060,15 +11094,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J43" s="77">
+      <c r="J43" s="76">
         <v>46316</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A44" s="69" t="s">
+      <c r="A44" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B44" s="69" t="s">
+      <c r="B44" s="68" t="s">
         <v>78</v>
       </c>
       <c r="C44" t="str">
@@ -11099,15 +11133,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J44" s="77">
+      <c r="J44" s="76">
         <v>46317</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A45" s="69" t="s">
+      <c r="A45" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="69" t="s">
+      <c r="B45" s="68" t="s">
         <v>78</v>
       </c>
       <c r="C45" t="str">
@@ -11138,15 +11172,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J45" s="77">
+      <c r="J45" s="76">
         <v>46318</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A46" s="69" t="s">
+      <c r="A46" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="69" t="s">
+      <c r="B46" s="68" t="s">
         <v>79</v>
       </c>
       <c r="C46" t="str">
@@ -11177,15 +11211,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J46" s="77">
+      <c r="J46" s="76">
         <v>46319</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A47" s="69" t="s">
+      <c r="A47" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B47" s="69" t="s">
+      <c r="B47" s="68" t="s">
         <v>79</v>
       </c>
       <c r="C47" t="str">
@@ -11216,15 +11250,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J47" s="77">
+      <c r="J47" s="76">
         <v>46320</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A48" s="69" t="s">
+      <c r="A48" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B48" s="69" t="s">
+      <c r="B48" s="68" t="s">
         <v>80</v>
       </c>
       <c r="C48" t="str">
@@ -11255,15 +11289,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J48" s="77">
+      <c r="J48" s="76">
         <v>46321</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A49" s="69" t="s">
+      <c r="A49" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="69" t="s">
+      <c r="B49" s="68" t="s">
         <v>80</v>
       </c>
       <c r="C49" t="str">
@@ -11294,15 +11328,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J49" s="77">
+      <c r="J49" s="76">
         <v>46322</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A50" s="69" t="s">
+      <c r="A50" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B50" s="69" t="s">
+      <c r="B50" s="68" t="s">
         <v>81</v>
       </c>
       <c r="C50" t="str">
@@ -11333,15 +11367,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J50" s="77">
+      <c r="J50" s="76">
         <v>46323</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A51" s="69" t="s">
+      <c r="A51" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B51" s="69" t="s">
+      <c r="B51" s="68" t="s">
         <v>81</v>
       </c>
       <c r="C51" t="str">
@@ -11372,15 +11406,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J51" s="77">
+      <c r="J51" s="76">
         <v>46324</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A52" s="69" t="s">
+      <c r="A52" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B52" s="69" t="s">
+      <c r="B52" s="68" t="s">
         <v>81</v>
       </c>
       <c r="C52" t="str">
@@ -11411,15 +11445,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J52" s="77">
+      <c r="J52" s="76">
         <v>46325</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A53" s="69" t="s">
+      <c r="A53" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B53" s="69" t="s">
+      <c r="B53" s="68" t="s">
         <v>82</v>
       </c>
       <c r="C53" t="str">
@@ -11450,15 +11484,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J53" s="77">
+      <c r="J53" s="76">
         <v>46326</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A54" s="69" t="s">
+      <c r="A54" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B54" s="69" t="s">
+      <c r="B54" s="68" t="s">
         <v>82</v>
       </c>
       <c r="C54" t="str">
@@ -11489,15 +11523,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J54" s="77">
+      <c r="J54" s="76">
         <v>46327</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A55" s="69" t="s">
+      <c r="A55" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B55" s="69" t="s">
+      <c r="B55" s="68" t="s">
         <v>82</v>
       </c>
       <c r="C55" t="str">
@@ -11528,15 +11562,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J55" s="77">
+      <c r="J55" s="76">
         <v>46328</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A56" s="69" t="s">
+      <c r="A56" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B56" s="69" t="s">
+      <c r="B56" s="68" t="s">
         <v>83</v>
       </c>
       <c r="C56" t="str">
@@ -11567,15 +11601,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J56" s="77">
+      <c r="J56" s="76">
         <v>46329</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A57" s="69" t="s">
+      <c r="A57" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B57" s="69" t="s">
+      <c r="B57" s="68" t="s">
         <v>83</v>
       </c>
       <c r="C57" t="str">
@@ -11606,15 +11640,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J57" s="77">
+      <c r="J57" s="76">
         <v>46330</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A58" s="69" t="s">
+      <c r="A58" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B58" s="69" t="s">
+      <c r="B58" s="68" t="s">
         <v>83</v>
       </c>
       <c r="C58" t="str">
@@ -11645,15 +11679,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J58" s="77">
+      <c r="J58" s="76">
         <v>46331</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A59" s="69" t="s">
+      <c r="A59" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B59" s="69" t="s">
+      <c r="B59" s="68" t="s">
         <v>84</v>
       </c>
       <c r="C59" t="str">
@@ -11684,15 +11718,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J59" s="77">
+      <c r="J59" s="76">
         <v>46332</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A60" s="69" t="s">
+      <c r="A60" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="69" t="s">
+      <c r="B60" s="68" t="s">
         <v>84</v>
       </c>
       <c r="C60" t="str">
@@ -11723,15 +11757,15 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J60" s="77">
+      <c r="J60" s="76">
         <v>46333</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A61" s="69" t="s">
+      <c r="A61" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="69" t="s">
+      <c r="B61" s="68" t="s">
         <v>84</v>
       </c>
       <c r="C61" t="str">
@@ -11762,16 +11796,16 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="J61" s="77">
+      <c r="J61" s="76">
         <v>46334</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11832,7 +11866,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>90</v>
       </c>
       <c r="B1" t="s">
@@ -11840,7 +11874,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="77" t="s">
         <v>91</v>
       </c>
       <c r="B2" t="s">
@@ -11848,15 +11882,15 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="77" t="s">
         <v>308</v>
       </c>
-      <c r="B4" s="78" t="s">
+      <c r="B4" s="77" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="77" t="s">
         <v>305</v>
       </c>
       <c r="B5" t="s">
@@ -11873,983 +11907,983 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="78" t="s">
         <v>128</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="81" t="s">
+      <c r="A7" s="80" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="80"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="82" t="s">
+      <c r="A8" s="81" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="80">
+      <c r="B8" s="79">
         <v>100</v>
       </c>
-      <c r="C8" s="80">
+      <c r="C8" s="79">
         <v>100</v>
       </c>
-      <c r="D8" s="80">
+      <c r="D8" s="79">
         <v>100</v>
       </c>
-      <c r="E8" s="80">
+      <c r="E8" s="79">
         <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="81"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="80"/>
+      <c r="A9" s="80"/>
+      <c r="B9" s="79"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="79"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="79" t="s">
+      <c r="A10" s="78" t="s">
         <v>309</v>
       </c>
-      <c r="B10" s="80">
+      <c r="B10" s="79">
         <v>100</v>
       </c>
-      <c r="C10" s="80">
+      <c r="C10" s="79">
         <v>100</v>
       </c>
-      <c r="D10" s="80">
+      <c r="D10" s="79">
         <v>100</v>
       </c>
-      <c r="E10" s="80">
+      <c r="E10" s="79">
         <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="79"/>
-      <c r="B11" s="80"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
+      <c r="A11" s="78"/>
+      <c r="B11" s="79"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="79"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="79" t="s">
+      <c r="A12" s="78" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="80"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="80"/>
+      <c r="B12" s="79"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="79"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="B13" s="80"/>
-      <c r="C13" s="80"/>
-      <c r="D13" s="80"/>
-      <c r="E13" s="80"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="79"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" s="82" t="s">
+      <c r="A14" s="81" t="s">
         <v>100</v>
       </c>
-      <c r="B14" s="80">
+      <c r="B14" s="79">
         <v>15</v>
       </c>
-      <c r="C14" s="80">
+      <c r="C14" s="79">
         <v>15</v>
       </c>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80">
+      <c r="D14" s="79"/>
+      <c r="E14" s="79">
         <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" s="81"/>
-      <c r="B15" s="80"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
+      <c r="A15" s="80"/>
+      <c r="B15" s="79"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A16" s="81" t="s">
+      <c r="A16" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="80"/>
-      <c r="C16" s="80"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="79"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A17" s="82" t="s">
+      <c r="A17" s="81" t="s">
         <v>105</v>
       </c>
-      <c r="B17" s="80">
+      <c r="B17" s="79">
         <v>20</v>
       </c>
-      <c r="C17" s="80">
+      <c r="C17" s="79">
         <v>20</v>
       </c>
-      <c r="D17" s="80">
+      <c r="D17" s="79">
         <v>20</v>
       </c>
-      <c r="E17" s="80">
+      <c r="E17" s="79">
         <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A18" s="81"/>
-      <c r="B18" s="80"/>
-      <c r="C18" s="80"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
+      <c r="A18" s="80"/>
+      <c r="B18" s="79"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="79"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A19" s="79" t="s">
+      <c r="A19" s="78" t="s">
         <v>310</v>
       </c>
-      <c r="B19" s="80">
+      <c r="B19" s="79">
         <v>35</v>
       </c>
-      <c r="C19" s="80">
+      <c r="C19" s="79">
         <v>35</v>
       </c>
-      <c r="D19" s="80">
+      <c r="D19" s="79">
         <v>20</v>
       </c>
-      <c r="E19" s="80">
+      <c r="E19" s="79">
         <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A20" s="79"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="80"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
+      <c r="A20" s="78"/>
+      <c r="B20" s="79"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="79"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A21" s="79" t="s">
+      <c r="A21" s="78" t="s">
         <v>110</v>
       </c>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="79"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A22" s="81" t="s">
+      <c r="A22" s="80" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="80"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
+      <c r="E22" s="79"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A23" s="82" t="s">
+      <c r="A23" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="80">
+      <c r="B23" s="79">
         <v>25</v>
       </c>
-      <c r="C23" s="80">
+      <c r="C23" s="79">
         <v>25</v>
       </c>
-      <c r="D23" s="80">
+      <c r="D23" s="79">
         <v>25</v>
       </c>
-      <c r="E23" s="80">
+      <c r="E23" s="79">
         <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A24" s="81"/>
-      <c r="B24" s="80"/>
-      <c r="C24" s="80"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
+      <c r="A24" s="80"/>
+      <c r="B24" s="79"/>
+      <c r="C24" s="79"/>
+      <c r="D24" s="79"/>
+      <c r="E24" s="79"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A25" s="81" t="s">
+      <c r="A25" s="80" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="80"/>
-      <c r="C25" s="80"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
+      <c r="B25" s="79"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="79"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A26" s="82" t="s">
+      <c r="A26" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="80">
+      <c r="B26" s="79">
         <v>3</v>
       </c>
-      <c r="C26" s="80">
+      <c r="C26" s="79">
         <v>3</v>
       </c>
-      <c r="D26" s="80"/>
-      <c r="E26" s="80">
+      <c r="D26" s="79"/>
+      <c r="E26" s="79">
         <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A27" s="81"/>
-      <c r="B27" s="80"/>
-      <c r="C27" s="80"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="80"/>
+      <c r="A27" s="80"/>
+      <c r="B27" s="79"/>
+      <c r="C27" s="79"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="79"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A28" s="79" t="s">
+      <c r="A28" s="78" t="s">
         <v>311</v>
       </c>
-      <c r="B28" s="80">
+      <c r="B28" s="79">
         <v>28</v>
       </c>
-      <c r="C28" s="80">
+      <c r="C28" s="79">
         <v>28</v>
       </c>
-      <c r="D28" s="80">
+      <c r="D28" s="79">
         <v>25</v>
       </c>
-      <c r="E28" s="80">
+      <c r="E28" s="79">
         <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A29" s="79"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="80"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
+      <c r="A29" s="78"/>
+      <c r="B29" s="79"/>
+      <c r="C29" s="79"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="79"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A30" s="79" t="s">
+      <c r="A30" s="78" t="s">
         <v>113</v>
       </c>
-      <c r="B30" s="80"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
+      <c r="B30" s="79"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="79"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A31" s="81" t="s">
+      <c r="A31" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="80"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="79"/>
+      <c r="D31" s="79"/>
+      <c r="E31" s="79"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A32" s="82" t="s">
+      <c r="A32" s="81" t="s">
         <v>111</v>
       </c>
-      <c r="B32" s="80"/>
-      <c r="C32" s="80">
+      <c r="B32" s="79"/>
+      <c r="C32" s="79">
         <v>5</v>
       </c>
-      <c r="D32" s="80">
+      <c r="D32" s="79">
         <v>5</v>
       </c>
-      <c r="E32" s="80">
+      <c r="E32" s="79">
         <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A33" s="81"/>
-      <c r="B33" s="80"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80"/>
+      <c r="A33" s="80"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="79"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A34" s="81" t="s">
+      <c r="A34" s="80" t="s">
         <v>79</v>
       </c>
-      <c r="B34" s="80"/>
-      <c r="C34" s="80"/>
-      <c r="D34" s="80"/>
-      <c r="E34" s="80"/>
+      <c r="B34" s="79"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="79"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A35" s="82" t="s">
+      <c r="A35" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="B35" s="80">
+      <c r="B35" s="79">
         <v>5</v>
       </c>
-      <c r="C35" s="80">
+      <c r="C35" s="79">
         <v>5</v>
       </c>
-      <c r="D35" s="80"/>
-      <c r="E35" s="80">
+      <c r="D35" s="79"/>
+      <c r="E35" s="79">
         <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A36" s="81"/>
-      <c r="B36" s="80"/>
-      <c r="C36" s="80"/>
-      <c r="D36" s="80"/>
-      <c r="E36" s="80"/>
+      <c r="A36" s="80"/>
+      <c r="B36" s="79"/>
+      <c r="C36" s="79"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="79"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A37" s="79" t="s">
+      <c r="A37" s="78" t="s">
         <v>312</v>
       </c>
-      <c r="B37" s="80">
+      <c r="B37" s="79">
         <v>5</v>
       </c>
-      <c r="C37" s="80">
+      <c r="C37" s="79">
         <v>10</v>
       </c>
-      <c r="D37" s="80">
+      <c r="D37" s="79">
         <v>5</v>
       </c>
-      <c r="E37" s="80">
+      <c r="E37" s="79">
         <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A38" s="79"/>
-      <c r="B38" s="80"/>
-      <c r="C38" s="80"/>
-      <c r="D38" s="80"/>
-      <c r="E38" s="80"/>
+      <c r="A38" s="78"/>
+      <c r="B38" s="79"/>
+      <c r="C38" s="79"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="79"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A39" s="79" t="s">
+      <c r="A39" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="B39" s="80"/>
-      <c r="C39" s="80"/>
-      <c r="D39" s="80"/>
-      <c r="E39" s="80"/>
+      <c r="B39" s="79"/>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A40" s="81" t="s">
+      <c r="A40" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="B40" s="80"/>
-      <c r="C40" s="80"/>
-      <c r="D40" s="80"/>
-      <c r="E40" s="80"/>
+      <c r="B40" s="79"/>
+      <c r="C40" s="79"/>
+      <c r="D40" s="79"/>
+      <c r="E40" s="79"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A41" s="82" t="s">
+      <c r="A41" s="81" t="s">
         <v>95</v>
       </c>
-      <c r="B41" s="80"/>
-      <c r="C41" s="80">
+      <c r="B41" s="79"/>
+      <c r="C41" s="79">
         <v>9</v>
       </c>
-      <c r="D41" s="80">
+      <c r="D41" s="79">
         <v>9</v>
       </c>
-      <c r="E41" s="80">
+      <c r="E41" s="79">
         <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A42" s="81"/>
-      <c r="B42" s="80"/>
-      <c r="C42" s="80"/>
-      <c r="D42" s="80"/>
-      <c r="E42" s="80"/>
+      <c r="A42" s="80"/>
+      <c r="B42" s="79"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="79"/>
+      <c r="E42" s="79"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A43" s="81" t="s">
+      <c r="A43" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="80"/>
-      <c r="C43" s="80"/>
-      <c r="D43" s="80"/>
-      <c r="E43" s="80"/>
+      <c r="B43" s="79"/>
+      <c r="C43" s="79"/>
+      <c r="D43" s="79"/>
+      <c r="E43" s="79"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A44" s="82" t="s">
+      <c r="A44" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="B44" s="80"/>
-      <c r="C44" s="80">
+      <c r="B44" s="79"/>
+      <c r="C44" s="79">
         <v>15</v>
       </c>
-      <c r="D44" s="80">
+      <c r="D44" s="79">
         <v>15</v>
       </c>
-      <c r="E44" s="80">
+      <c r="E44" s="79">
         <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A45" s="81"/>
-      <c r="B45" s="80"/>
-      <c r="C45" s="80"/>
-      <c r="D45" s="80"/>
-      <c r="E45" s="80"/>
+      <c r="A45" s="80"/>
+      <c r="B45" s="79"/>
+      <c r="C45" s="79"/>
+      <c r="D45" s="79"/>
+      <c r="E45" s="79"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A46" s="79" t="s">
+      <c r="A46" s="78" t="s">
         <v>313</v>
       </c>
-      <c r="B46" s="80"/>
-      <c r="C46" s="80">
+      <c r="B46" s="79"/>
+      <c r="C46" s="79">
         <v>24</v>
       </c>
-      <c r="D46" s="80">
+      <c r="D46" s="79">
         <v>24</v>
       </c>
-      <c r="E46" s="80">
+      <c r="E46" s="79">
         <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A47" s="79"/>
-      <c r="B47" s="80"/>
-      <c r="C47" s="80"/>
-      <c r="D47" s="80"/>
-      <c r="E47" s="80"/>
+      <c r="A47" s="78"/>
+      <c r="B47" s="79"/>
+      <c r="C47" s="79"/>
+      <c r="D47" s="79"/>
+      <c r="E47" s="79"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A48" s="79" t="s">
+      <c r="A48" s="78" t="s">
         <v>125</v>
       </c>
-      <c r="B48" s="80"/>
-      <c r="C48" s="80"/>
-      <c r="D48" s="80"/>
-      <c r="E48" s="80"/>
+      <c r="B48" s="79"/>
+      <c r="C48" s="79"/>
+      <c r="D48" s="79"/>
+      <c r="E48" s="79"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A49" s="81" t="s">
+      <c r="A49" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="B49" s="80"/>
-      <c r="C49" s="80"/>
-      <c r="D49" s="80"/>
-      <c r="E49" s="80"/>
+      <c r="B49" s="79"/>
+      <c r="C49" s="79"/>
+      <c r="D49" s="79"/>
+      <c r="E49" s="79"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A50" s="82" t="s">
+      <c r="A50" s="81" t="s">
         <v>123</v>
       </c>
-      <c r="B50" s="80">
+      <c r="B50" s="79">
         <v>15</v>
       </c>
-      <c r="C50" s="80">
+      <c r="C50" s="79">
         <v>15</v>
       </c>
-      <c r="D50" s="80">
+      <c r="D50" s="79">
         <v>15</v>
       </c>
-      <c r="E50" s="80">
+      <c r="E50" s="79">
         <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A51" s="81"/>
-      <c r="B51" s="80"/>
-      <c r="C51" s="80"/>
-      <c r="D51" s="80"/>
-      <c r="E51" s="80"/>
+      <c r="A51" s="80"/>
+      <c r="B51" s="79"/>
+      <c r="C51" s="79"/>
+      <c r="D51" s="79"/>
+      <c r="E51" s="79"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A52" s="81" t="s">
+      <c r="A52" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="B52" s="80"/>
-      <c r="C52" s="80"/>
-      <c r="D52" s="80"/>
-      <c r="E52" s="80"/>
+      <c r="B52" s="79"/>
+      <c r="C52" s="79"/>
+      <c r="D52" s="79"/>
+      <c r="E52" s="79"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A53" s="82" t="s">
+      <c r="A53" s="81" t="s">
         <v>126</v>
       </c>
-      <c r="B53" s="80">
+      <c r="B53" s="79">
         <v>100</v>
       </c>
-      <c r="C53" s="80">
+      <c r="C53" s="79">
         <v>100</v>
       </c>
-      <c r="D53" s="80">
+      <c r="D53" s="79">
         <v>100</v>
       </c>
-      <c r="E53" s="80">
+      <c r="E53" s="79">
         <v>300</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A54" s="81"/>
-      <c r="B54" s="80"/>
-      <c r="C54" s="80"/>
-      <c r="D54" s="80"/>
-      <c r="E54" s="80"/>
+      <c r="A54" s="80"/>
+      <c r="B54" s="79"/>
+      <c r="C54" s="79"/>
+      <c r="D54" s="79"/>
+      <c r="E54" s="79"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A55" s="81" t="s">
+      <c r="A55" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="B55" s="80"/>
-      <c r="C55" s="80"/>
-      <c r="D55" s="80"/>
-      <c r="E55" s="80"/>
+      <c r="B55" s="79"/>
+      <c r="C55" s="79"/>
+      <c r="D55" s="79"/>
+      <c r="E55" s="79"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A56" s="82" t="s">
+      <c r="A56" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="B56" s="80">
+      <c r="B56" s="79">
         <v>75</v>
       </c>
-      <c r="C56" s="80">
+      <c r="C56" s="79">
         <v>75</v>
       </c>
-      <c r="D56" s="80">
+      <c r="D56" s="79">
         <v>75</v>
       </c>
-      <c r="E56" s="80">
+      <c r="E56" s="79">
         <v>225</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A57" s="81"/>
-      <c r="B57" s="80"/>
-      <c r="C57" s="80"/>
-      <c r="D57" s="80"/>
-      <c r="E57" s="80"/>
+      <c r="A57" s="80"/>
+      <c r="B57" s="79"/>
+      <c r="C57" s="79"/>
+      <c r="D57" s="79"/>
+      <c r="E57" s="79"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A58" s="79" t="s">
+      <c r="A58" s="78" t="s">
         <v>314</v>
       </c>
-      <c r="B58" s="80">
+      <c r="B58" s="79">
         <v>190</v>
       </c>
-      <c r="C58" s="80">
+      <c r="C58" s="79">
         <v>190</v>
       </c>
-      <c r="D58" s="80">
+      <c r="D58" s="79">
         <v>190</v>
       </c>
-      <c r="E58" s="80">
+      <c r="E58" s="79">
         <v>570</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A59" s="79"/>
-      <c r="B59" s="80"/>
-      <c r="C59" s="80"/>
-      <c r="D59" s="80"/>
-      <c r="E59" s="80"/>
+      <c r="A59" s="78"/>
+      <c r="B59" s="79"/>
+      <c r="C59" s="79"/>
+      <c r="D59" s="79"/>
+      <c r="E59" s="79"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="78" t="s">
         <v>99</v>
       </c>
-      <c r="B60" s="80"/>
-      <c r="C60" s="80"/>
-      <c r="D60" s="80"/>
-      <c r="E60" s="80"/>
+      <c r="B60" s="79"/>
+      <c r="C60" s="79"/>
+      <c r="D60" s="79"/>
+      <c r="E60" s="79"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A61" s="81" t="s">
+      <c r="A61" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="B61" s="80"/>
-      <c r="C61" s="80"/>
-      <c r="D61" s="80"/>
-      <c r="E61" s="80"/>
+      <c r="B61" s="79"/>
+      <c r="C61" s="79"/>
+      <c r="D61" s="79"/>
+      <c r="E61" s="79"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A62" s="82" t="s">
+      <c r="A62" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="B62" s="80">
+      <c r="B62" s="79">
         <v>50</v>
       </c>
-      <c r="C62" s="80">
+      <c r="C62" s="79">
         <v>50</v>
       </c>
-      <c r="D62" s="80">
+      <c r="D62" s="79">
         <v>50</v>
       </c>
-      <c r="E62" s="80">
+      <c r="E62" s="79">
         <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A63" s="81"/>
-      <c r="B63" s="80"/>
-      <c r="C63" s="80"/>
-      <c r="D63" s="80"/>
-      <c r="E63" s="80"/>
+      <c r="A63" s="80"/>
+      <c r="B63" s="79"/>
+      <c r="C63" s="79"/>
+      <c r="D63" s="79"/>
+      <c r="E63" s="79"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A64" s="81" t="s">
+      <c r="A64" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="B64" s="80"/>
-      <c r="C64" s="80"/>
-      <c r="D64" s="80"/>
-      <c r="E64" s="80"/>
+      <c r="B64" s="79"/>
+      <c r="C64" s="79"/>
+      <c r="D64" s="79"/>
+      <c r="E64" s="79"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A65" s="82" t="s">
+      <c r="A65" s="81" t="s">
         <v>104</v>
       </c>
-      <c r="B65" s="80">
+      <c r="B65" s="79">
         <v>30</v>
       </c>
-      <c r="C65" s="80">
+      <c r="C65" s="79">
         <v>30</v>
       </c>
-      <c r="D65" s="80">
+      <c r="D65" s="79">
         <v>30</v>
       </c>
-      <c r="E65" s="80">
+      <c r="E65" s="79">
         <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A66" s="81"/>
-      <c r="B66" s="80"/>
-      <c r="C66" s="80"/>
-      <c r="D66" s="80"/>
-      <c r="E66" s="80"/>
+      <c r="A66" s="80"/>
+      <c r="B66" s="79"/>
+      <c r="C66" s="79"/>
+      <c r="D66" s="79"/>
+      <c r="E66" s="79"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A67" s="79" t="s">
+      <c r="A67" s="78" t="s">
         <v>315</v>
       </c>
-      <c r="B67" s="80">
+      <c r="B67" s="79">
         <v>80</v>
       </c>
-      <c r="C67" s="80">
+      <c r="C67" s="79">
         <v>80</v>
       </c>
-      <c r="D67" s="80">
+      <c r="D67" s="79">
         <v>80</v>
       </c>
-      <c r="E67" s="80">
+      <c r="E67" s="79">
         <v>240</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A68" s="79"/>
-      <c r="B68" s="80"/>
-      <c r="C68" s="80"/>
-      <c r="D68" s="80"/>
-      <c r="E68" s="80"/>
+      <c r="A68" s="78"/>
+      <c r="B68" s="79"/>
+      <c r="C68" s="79"/>
+      <c r="D68" s="79"/>
+      <c r="E68" s="79"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A69" s="79" t="s">
+      <c r="A69" s="78" t="s">
         <v>119</v>
       </c>
-      <c r="B69" s="80"/>
-      <c r="C69" s="80"/>
-      <c r="D69" s="80"/>
-      <c r="E69" s="80"/>
+      <c r="B69" s="79"/>
+      <c r="C69" s="79"/>
+      <c r="D69" s="79"/>
+      <c r="E69" s="79"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A70" s="81" t="s">
+      <c r="A70" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="B70" s="80"/>
-      <c r="C70" s="80"/>
-      <c r="D70" s="80"/>
-      <c r="E70" s="80"/>
+      <c r="B70" s="79"/>
+      <c r="C70" s="79"/>
+      <c r="D70" s="79"/>
+      <c r="E70" s="79"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A71" s="82" t="s">
+      <c r="A71" s="81" t="s">
         <v>118</v>
       </c>
-      <c r="B71" s="80"/>
-      <c r="C71" s="80">
+      <c r="B71" s="79"/>
+      <c r="C71" s="79">
         <v>20</v>
       </c>
-      <c r="D71" s="80">
+      <c r="D71" s="79">
         <v>20</v>
       </c>
-      <c r="E71" s="80">
+      <c r="E71" s="79">
         <v>40</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A72" s="81"/>
-      <c r="B72" s="80"/>
-      <c r="C72" s="80"/>
-      <c r="D72" s="80"/>
-      <c r="E72" s="80"/>
+      <c r="A72" s="80"/>
+      <c r="B72" s="79"/>
+      <c r="C72" s="79"/>
+      <c r="D72" s="79"/>
+      <c r="E72" s="79"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A73" s="81" t="s">
+      <c r="A73" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="B73" s="80"/>
-      <c r="C73" s="80"/>
-      <c r="D73" s="80"/>
-      <c r="E73" s="80"/>
+      <c r="B73" s="79"/>
+      <c r="C73" s="79"/>
+      <c r="D73" s="79"/>
+      <c r="E73" s="79"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A74" s="82" t="s">
+      <c r="A74" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="B74" s="80"/>
-      <c r="C74" s="80">
+      <c r="B74" s="79"/>
+      <c r="C74" s="79">
         <v>8</v>
       </c>
-      <c r="D74" s="80">
+      <c r="D74" s="79">
         <v>8</v>
       </c>
-      <c r="E74" s="80">
+      <c r="E74" s="79">
         <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A75" s="81"/>
-      <c r="B75" s="80"/>
-      <c r="C75" s="80"/>
-      <c r="D75" s="80"/>
-      <c r="E75" s="80"/>
+      <c r="A75" s="80"/>
+      <c r="B75" s="79"/>
+      <c r="C75" s="79"/>
+      <c r="D75" s="79"/>
+      <c r="E75" s="79"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A76" s="79" t="s">
+      <c r="A76" s="78" t="s">
         <v>316</v>
       </c>
-      <c r="B76" s="80"/>
-      <c r="C76" s="80">
+      <c r="B76" s="79"/>
+      <c r="C76" s="79">
         <v>28</v>
       </c>
-      <c r="D76" s="80">
+      <c r="D76" s="79">
         <v>28</v>
       </c>
-      <c r="E76" s="80">
+      <c r="E76" s="79">
         <v>56</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A77" s="79"/>
-      <c r="B77" s="80"/>
-      <c r="C77" s="80"/>
-      <c r="D77" s="80"/>
-      <c r="E77" s="80"/>
+      <c r="A77" s="78"/>
+      <c r="B77" s="79"/>
+      <c r="C77" s="79"/>
+      <c r="D77" s="79"/>
+      <c r="E77" s="79"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A78" s="79" t="s">
+      <c r="A78" s="78" t="s">
         <v>115</v>
       </c>
-      <c r="B78" s="80"/>
-      <c r="C78" s="80"/>
-      <c r="D78" s="80"/>
-      <c r="E78" s="80"/>
+      <c r="B78" s="79"/>
+      <c r="C78" s="79"/>
+      <c r="D78" s="79"/>
+      <c r="E78" s="79"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A79" s="81" t="s">
+      <c r="A79" s="80" t="s">
         <v>75</v>
       </c>
-      <c r="B79" s="80"/>
-      <c r="C79" s="80"/>
-      <c r="D79" s="80"/>
-      <c r="E79" s="80"/>
+      <c r="B79" s="79"/>
+      <c r="C79" s="79"/>
+      <c r="D79" s="79"/>
+      <c r="E79" s="79"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A80" s="82" t="s">
+      <c r="A80" s="81" t="s">
         <v>114</v>
       </c>
-      <c r="B80" s="80">
+      <c r="B80" s="79">
         <v>8</v>
       </c>
-      <c r="C80" s="80"/>
-      <c r="D80" s="80">
+      <c r="C80" s="79"/>
+      <c r="D80" s="79">
         <v>8</v>
       </c>
-      <c r="E80" s="80">
+      <c r="E80" s="79">
         <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A81" s="81"/>
-      <c r="B81" s="80"/>
-      <c r="C81" s="80"/>
-      <c r="D81" s="80"/>
-      <c r="E81" s="80"/>
+      <c r="A81" s="80"/>
+      <c r="B81" s="79"/>
+      <c r="C81" s="79"/>
+      <c r="D81" s="79"/>
+      <c r="E81" s="79"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A82" s="81" t="s">
+      <c r="A82" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="B82" s="80"/>
-      <c r="C82" s="80"/>
-      <c r="D82" s="80"/>
-      <c r="E82" s="80"/>
+      <c r="B82" s="79"/>
+      <c r="C82" s="79"/>
+      <c r="D82" s="79"/>
+      <c r="E82" s="79"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A83" s="82" t="s">
+      <c r="A83" s="81" t="s">
         <v>120</v>
       </c>
-      <c r="B83" s="80">
+      <c r="B83" s="79">
         <v>30</v>
       </c>
-      <c r="C83" s="80"/>
-      <c r="D83" s="80">
+      <c r="C83" s="79"/>
+      <c r="D83" s="79">
         <v>30</v>
       </c>
-      <c r="E83" s="80">
+      <c r="E83" s="79">
         <v>60</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A84" s="81"/>
-      <c r="B84" s="80"/>
-      <c r="C84" s="80"/>
-      <c r="D84" s="80"/>
-      <c r="E84" s="80"/>
+      <c r="A84" s="80"/>
+      <c r="B84" s="79"/>
+      <c r="C84" s="79"/>
+      <c r="D84" s="79"/>
+      <c r="E84" s="79"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A85" s="79" t="s">
+      <c r="A85" s="78" t="s">
         <v>317</v>
       </c>
-      <c r="B85" s="80">
+      <c r="B85" s="79">
         <v>38</v>
       </c>
-      <c r="C85" s="80"/>
-      <c r="D85" s="80">
+      <c r="C85" s="79"/>
+      <c r="D85" s="79">
         <v>38</v>
       </c>
-      <c r="E85" s="80">
+      <c r="E85" s="79">
         <v>76</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A86" s="79"/>
-      <c r="B86" s="80"/>
-      <c r="C86" s="80"/>
-      <c r="D86" s="80"/>
-      <c r="E86" s="80"/>
+      <c r="A86" s="78"/>
+      <c r="B86" s="79"/>
+      <c r="C86" s="79"/>
+      <c r="D86" s="79"/>
+      <c r="E86" s="79"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A87" s="79" t="s">
+      <c r="A87" s="78" t="s">
         <v>103</v>
       </c>
-      <c r="B87" s="80"/>
-      <c r="C87" s="80"/>
-      <c r="D87" s="80"/>
-      <c r="E87" s="80"/>
+      <c r="B87" s="79"/>
+      <c r="C87" s="79"/>
+      <c r="D87" s="79"/>
+      <c r="E87" s="79"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A88" s="81" t="s">
+      <c r="A88" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="B88" s="80"/>
-      <c r="C88" s="80"/>
-      <c r="D88" s="80"/>
-      <c r="E88" s="80"/>
+      <c r="B88" s="79"/>
+      <c r="C88" s="79"/>
+      <c r="D88" s="79"/>
+      <c r="E88" s="79"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A89" s="82" t="s">
+      <c r="A89" s="81" t="s">
         <v>102</v>
       </c>
-      <c r="B89" s="80">
+      <c r="B89" s="79">
         <v>25</v>
       </c>
-      <c r="C89" s="80">
+      <c r="C89" s="79">
         <v>25</v>
       </c>
-      <c r="D89" s="80">
+      <c r="D89" s="79">
         <v>25</v>
       </c>
-      <c r="E89" s="80">
+      <c r="E89" s="79">
         <v>75</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A90" s="81"/>
-      <c r="B90" s="80"/>
-      <c r="C90" s="80"/>
-      <c r="D90" s="80"/>
-      <c r="E90" s="80"/>
+      <c r="A90" s="80"/>
+      <c r="B90" s="79"/>
+      <c r="C90" s="79"/>
+      <c r="D90" s="79"/>
+      <c r="E90" s="79"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A91" s="81" t="s">
+      <c r="A91" s="80" t="s">
         <v>72</v>
       </c>
-      <c r="B91" s="80"/>
-      <c r="C91" s="80"/>
-      <c r="D91" s="80"/>
-      <c r="E91" s="80"/>
+      <c r="B91" s="79"/>
+      <c r="C91" s="79"/>
+      <c r="D91" s="79"/>
+      <c r="E91" s="79"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A92" s="82" t="s">
+      <c r="A92" s="81" t="s">
         <v>107</v>
       </c>
-      <c r="B92" s="80">
+      <c r="B92" s="79">
         <v>40</v>
       </c>
-      <c r="C92" s="80">
+      <c r="C92" s="79">
         <v>40</v>
       </c>
-      <c r="D92" s="80">
+      <c r="D92" s="79">
         <v>40</v>
       </c>
-      <c r="E92" s="80">
+      <c r="E92" s="79">
         <v>120</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A93" s="81"/>
-      <c r="B93" s="80"/>
-      <c r="C93" s="80"/>
-      <c r="D93" s="80"/>
-      <c r="E93" s="80"/>
+      <c r="A93" s="80"/>
+      <c r="B93" s="79"/>
+      <c r="C93" s="79"/>
+      <c r="D93" s="79"/>
+      <c r="E93" s="79"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A94" s="79" t="s">
+      <c r="A94" s="78" t="s">
         <v>318</v>
       </c>
-      <c r="B94" s="80">
+      <c r="B94" s="79">
         <v>65</v>
       </c>
-      <c r="C94" s="80">
+      <c r="C94" s="79">
         <v>65</v>
       </c>
-      <c r="D94" s="80">
+      <c r="D94" s="79">
         <v>65</v>
       </c>
-      <c r="E94" s="80">
+      <c r="E94" s="79">
         <v>195</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A95" s="79"/>
-      <c r="B95" s="80"/>
-      <c r="C95" s="80"/>
-      <c r="D95" s="80"/>
-      <c r="E95" s="80"/>
+      <c r="A95" s="78"/>
+      <c r="B95" s="79"/>
+      <c r="C95" s="79"/>
+      <c r="D95" s="79"/>
+      <c r="E95" s="79"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A96" s="79" t="s">
+      <c r="A96" s="78" t="s">
         <v>306</v>
       </c>
-      <c r="B96" s="80">
+      <c r="B96" s="79">
         <v>541</v>
       </c>
-      <c r="C96" s="80">
+      <c r="C96" s="79">
         <v>560</v>
       </c>
-      <c r="D96" s="80">
+      <c r="D96" s="79">
         <v>575</v>
       </c>
-      <c r="E96" s="80">
+      <c r="E96" s="79">
         <v>1676</v>
       </c>
     </row>

--- a/DataAnalyst.xlsx
+++ b/DataAnalyst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malik\OneDrive\Documents\Data\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08626EE4-0399-430C-BA4D-06A93EACA91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E631C9-F5B0-46BB-93F3-CB96F0D5234D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="332">
   <si>
     <t>ELECTRONICS COMPANIES REPORT Q1 2023</t>
   </si>
@@ -1014,6 +1014,42 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>T061</t>
+  </si>
+  <si>
+    <t>T062</t>
+  </si>
+  <si>
+    <t>T063</t>
+  </si>
+  <si>
+    <t>T064</t>
+  </si>
+  <si>
+    <t>T065</t>
+  </si>
+  <si>
+    <t>T066</t>
+  </si>
+  <si>
+    <t>T067</t>
+  </si>
+  <si>
+    <t>T068</t>
+  </si>
+  <si>
+    <t>T069</t>
+  </si>
+  <si>
+    <t>T070</t>
+  </si>
+  <si>
+    <t>T071</t>
+  </si>
+  <si>
+    <t>T072</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1347,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1537,6 +1573,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="10" applyFont="1"/>
     <xf numFmtId="43" fontId="11" fillId="0" borderId="3" xfId="2" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{72D35A1C-E0E1-4D48-ACA5-2713C7D76C54}"/>
@@ -1553,6 +1592,15 @@
     <cellStyle name="Normal 9" xfId="10" xr:uid="{DFABB175-7506-410D-8AC4-26F83CE150B7}"/>
   </cellStyles>
   <dxfs count="38">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1652,15 +1700,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
@@ -4563,14 +4602,14 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03C4EC66-596A-4191-8AD5-8C56A2B0936F}" name="Transactions" displayName="Transactions" ref="A1:F61" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:F61" xr:uid="{03C4EC66-596A-4191-8AD5-8C56A2B0936F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03C4EC66-596A-4191-8AD5-8C56A2B0936F}" name="Transactions" displayName="Transactions" ref="A1:F73" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A1:F73" xr:uid="{03C4EC66-596A-4191-8AD5-8C56A2B0936F}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{CF0FBA31-2E94-4135-8B0A-A8ADD4C1D54E}" name="TransID"/>
-    <tableColumn id="2" xr3:uid="{EB83FE89-2487-49C6-80BE-246C3764EFC8}" name="Date" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{EB83FE89-2487-49C6-80BE-246C3764EFC8}" name="Date" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{FE85118D-4F73-4CC4-947F-D727DBCF045B}" name="ProductID"/>
-    <tableColumn id="4" xr3:uid="{890FE897-5C0E-4846-94E3-254F9AB59CC8}" name="Site" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{D5DF56AA-CF75-4D46-9133-AE66DE368857}" name="Quantity" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{890FE897-5C0E-4846-94E3-254F9AB59CC8}" name="Site" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{D5DF56AA-CF75-4D46-9133-AE66DE368857}" name="Quantity" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{8D0BBA31-EE38-4A83-9E89-796952F75830}" name="Type"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4578,7 +4617,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A5DC87FD-A8D1-440B-BAC9-DE34E48E5936}" name="Inventory" displayName="Inventory" ref="A1:J61" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="Normal 9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A5DC87FD-A8D1-440B-BAC9-DE34E48E5936}" name="Inventory" displayName="Inventory" ref="A1:J61" totalsRowShown="0" headerRowDxfId="4" headerRowCellStyle="Normal 9">
   <autoFilter ref="A1:J61" xr:uid="{A5DC87FD-A8D1-440B-BAC9-DE34E48E5936}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J61">
     <sortCondition ref="I1:I61"/>
@@ -8167,7 +8206,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.9296875" customWidth="1"/>
@@ -9397,10 +9436,250 @@
         <v>303</v>
       </c>
     </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>320</v>
+      </c>
+      <c r="B62" s="85">
+        <v>45910</v>
+      </c>
+      <c r="C62" t="s">
+        <v>75</v>
+      </c>
+      <c r="D62" s="65" t="s">
+        <v>62</v>
+      </c>
+      <c r="E62" s="65">
+        <v>10</v>
+      </c>
+      <c r="F62" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>321</v>
+      </c>
+      <c r="B63" s="85">
+        <v>45910</v>
+      </c>
+      <c r="C63" t="s">
+        <v>77</v>
+      </c>
+      <c r="D63" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="E63" s="65">
+        <v>20</v>
+      </c>
+      <c r="F63" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>322</v>
+      </c>
+      <c r="B64" s="85">
+        <v>45910</v>
+      </c>
+      <c r="C64" t="s">
+        <v>84</v>
+      </c>
+      <c r="D64" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="E64" s="65">
+        <v>10</v>
+      </c>
+      <c r="F64" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>323</v>
+      </c>
+      <c r="B65" s="85">
+        <v>45910</v>
+      </c>
+      <c r="C65" t="s">
+        <v>74</v>
+      </c>
+      <c r="D65" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="E65" s="65">
+        <v>10</v>
+      </c>
+      <c r="F65" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>324</v>
+      </c>
+      <c r="B66" s="85">
+        <v>45910</v>
+      </c>
+      <c r="C66" t="s">
+        <v>77</v>
+      </c>
+      <c r="D66" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="E66" s="65">
+        <v>20</v>
+      </c>
+      <c r="F66" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>325</v>
+      </c>
+      <c r="B67" s="85">
+        <v>45911</v>
+      </c>
+      <c r="C67" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="E67" s="65">
+        <v>12</v>
+      </c>
+      <c r="F67" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>326</v>
+      </c>
+      <c r="B68" s="85">
+        <v>45911</v>
+      </c>
+      <c r="C68" t="s">
+        <v>74</v>
+      </c>
+      <c r="D68" s="65" t="s">
+        <v>62</v>
+      </c>
+      <c r="E68" s="65">
+        <v>10</v>
+      </c>
+      <c r="F68" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>327</v>
+      </c>
+      <c r="B69" s="85">
+        <v>45911</v>
+      </c>
+      <c r="C69" t="s">
+        <v>77</v>
+      </c>
+      <c r="D69" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="E69" s="65">
+        <v>20</v>
+      </c>
+      <c r="F69" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>328</v>
+      </c>
+      <c r="B70" s="85">
+        <v>45912</v>
+      </c>
+      <c r="C70" t="s">
+        <v>69</v>
+      </c>
+      <c r="D70" s="65" t="s">
+        <v>62</v>
+      </c>
+      <c r="E70" s="65">
+        <v>-25</v>
+      </c>
+      <c r="F70" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>329</v>
+      </c>
+      <c r="B71" s="85">
+        <v>45912</v>
+      </c>
+      <c r="C71" t="s">
+        <v>78</v>
+      </c>
+      <c r="D71" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="E71" s="65">
+        <v>-1</v>
+      </c>
+      <c r="F71" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>330</v>
+      </c>
+      <c r="B72" s="85">
+        <v>45912</v>
+      </c>
+      <c r="C72" t="s">
+        <v>83</v>
+      </c>
+      <c r="D72" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="E72" s="65">
+        <v>-2</v>
+      </c>
+      <c r="F72" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>331</v>
+      </c>
+      <c r="B73" s="85">
+        <v>45913</v>
+      </c>
+      <c r="C73" t="s">
+        <v>66</v>
+      </c>
+      <c r="D73" s="65" t="s">
+        <v>62</v>
+      </c>
+      <c r="E73" s="65">
+        <v>-8</v>
+      </c>
+      <c r="F73" t="s">
+        <v>302</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C61" xr:uid="{8442A689-EFD5-4F1D-8E71-3A321F89ED08}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C73" xr:uid="{8442A689-EFD5-4F1D-8E71-3A321F89ED08}">
       <formula1>ProductList</formula1>
     </dataValidation>
   </dataValidations>
@@ -9602,11 +9881,11 @@
       </c>
       <c r="G5">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H5">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>4375</v>
+        <v>5625</v>
       </c>
       <c r="I5" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -9758,11 +10037,11 @@
       </c>
       <c r="G9">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H9">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>7250</v>
+        <v>7105</v>
       </c>
       <c r="I9" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -9953,11 +10232,11 @@
       </c>
       <c r="G14">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="H14">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>-680</v>
       </c>
       <c r="I14" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -10265,11 +10544,11 @@
       </c>
       <c r="G22">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="H22">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>-362.5</v>
       </c>
       <c r="I22" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -10460,15 +10739,15 @@
       </c>
       <c r="G27">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H27">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>252</v>
+        <v>468</v>
       </c>
       <c r="I27" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="J27" s="76">
         <v>46300</v>
@@ -10811,15 +11090,15 @@
       </c>
       <c r="G36">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H36">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="I36" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="J36" s="76">
         <v>46309</v>
@@ -10889,15 +11168,15 @@
       </c>
       <c r="G38">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H38">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>4750</v>
       </c>
       <c r="I38" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="J38" s="76">
         <v>46311</v>
@@ -11045,15 +11324,15 @@
       </c>
       <c r="G42">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H42">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="I42" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="J42" s="76">
         <v>46315</v>
@@ -11084,11 +11363,11 @@
       </c>
       <c r="G43">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H43">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="I43" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -11669,11 +11948,11 @@
       </c>
       <c r="G58">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H58">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>-7.5</v>
       </c>
       <c r="I58" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -11786,11 +12065,11 @@
       </c>
       <c r="G61">
         <f>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H61">
         <f>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</f>
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="I61" t="str">
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
@@ -11802,10 +12081,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",I1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/DataAnalyst.xlsx
+++ b/DataAnalyst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malik\OneDrive\Documents\Data\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E631C9-F5B0-46BB-93F3-CB96F0D5234D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EFF52E9-6564-4FA5-B2F1-60F277C96E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -10749,9 +10749,7 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="J27" s="76">
-        <v>46300</v>
-      </c>
+      <c r="J27" s="76"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="68" t="s">
@@ -11100,9 +11098,7 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="J36" s="76">
-        <v>46309</v>
-      </c>
+      <c r="J36" s="76"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="68" t="s">
@@ -11178,9 +11174,7 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="J38" s="76">
-        <v>46311</v>
-      </c>
+      <c r="J38" s="76"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="68" t="s">
@@ -11334,9 +11328,7 @@
         <f>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="J42" s="76">
-        <v>46315</v>
-      </c>
+      <c r="J42" s="76"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" s="68" t="s">

--- a/DataAnalyst.xlsx
+++ b/DataAnalyst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malik\OneDrive\Documents\Data\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EFF52E9-6564-4FA5-B2F1-60F277C96E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8956CD8-05AA-439E-AC43-1A505CDB4606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Transactions" sheetId="4" r:id="rId4"/>
     <sheet name="Inventory" sheetId="5" r:id="rId5"/>
     <sheet name="Order" sheetId="6" r:id="rId6"/>
+    <sheet name="Reports" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="ProductList">Products[ProductID]</definedName>
@@ -26,13 +27,13 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="39" r:id="rId7"/>
+    <pivotCache cacheId="40" r:id="rId8"/>
   </pivotCaches>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId8"/>
+        <x14:slicerCache r:id="rId9"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="334">
   <si>
     <t>ELECTRONICS COMPANIES REPORT Q1 2023</t>
   </si>
@@ -977,6 +978,9 @@
     <t>Grand Total</t>
   </si>
   <si>
+    <t>Sum of Stock Value</t>
+  </si>
+  <si>
     <t>Column Labels</t>
   </si>
   <si>
@@ -1050,6 +1054,9 @@
   </si>
   <si>
     <t>T072</t>
+  </si>
+  <si>
+    <t>Sum of QuantityOnHand</t>
   </si>
 </sst>
 </file>
@@ -1591,7 +1598,7 @@
     <cellStyle name="Normal 8" xfId="9" xr:uid="{0EFC0AAE-EB0E-4FA2-885A-2DA2EB3F3608}"/>
     <cellStyle name="Normal 9" xfId="10" xr:uid="{DFABB175-7506-410D-8AC4-26F83CE150B7}"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="33">
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1638,56 +1645,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3672,7 +3629,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38DC400E-84BC-4A77-AD46-FA601CF5F496}" name="PivotTable2" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38DC400E-84BC-4A77-AD46-FA601CF5F496}" name="PivotTable2" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:E96" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="12">
     <pivotField axis="axisCol" subtotalTop="0" showAll="0" insertBlankRow="1">
@@ -4532,6 +4489,634 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8760556F-EE87-45AC-8AA1-691971073720}" name="PivotTable4" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="G2:K44" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="21">
+        <item x="0"/>
+        <item x="10"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="2"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="21">
+        <item x="15"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="14"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="19"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="61">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="2"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="41">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Stock Value" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleMedium5" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{056141E7-6BFB-4C95-B00A-B531F48F40E9}" name="PivotTable3" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A2:E44" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="21">
+        <item x="0"/>
+        <item x="10"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="2"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="21">
+        <item x="15"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="14"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="19"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="61">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="2"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="41">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of QuantityOnHand" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleMedium5" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Supplier" xr10:uid="{8194BE1B-4C3E-4889-9801-C5B859E7B9E5}" sourceName="Supplier">
   <pivotTables>
@@ -4566,36 +5151,36 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="C4:Q31" totalsRowCount="1">
   <autoFilter ref="C4:Q30" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" totalsRowLabel="Total" totalsRowDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMPANIES" totalsRowDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NUMBER OF EMPLOYEES" totalsRowDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COLOR" totalsRowDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LAUNCH DATE" totalsRowDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="QUANTITY" totalsRowFunction="sum" totalsRowDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PRICE" totalsRowFunction="sum" totalsRowDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AMOUNT" totalsRowFunction="sum" totalsRowDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="QUANTITY " totalsRowDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRICE " totalsRowDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="AMOUNT " totalsRowFunction="sum" totalsRowDxfId="21"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QUANTITY  " totalsRowDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="PRICE  " totalsRowDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="AMOUNT  " totalsRowFunction="sum" totalsRowDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="TOTAL" totalsRowFunction="sum" totalsRowDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" totalsRowLabel="Total" totalsRowDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMPANIES" totalsRowDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NUMBER OF EMPLOYEES" totalsRowDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COLOR" totalsRowDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LAUNCH DATE" totalsRowDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="QUANTITY" totalsRowFunction="sum" totalsRowDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PRICE" totalsRowFunction="sum" totalsRowDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AMOUNT" totalsRowFunction="sum" totalsRowDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="QUANTITY " totalsRowDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRICE " totalsRowDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="AMOUNT " totalsRowFunction="sum" totalsRowDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QUANTITY  " totalsRowDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="PRICE  " totalsRowDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="AMOUNT  " totalsRowFunction="sum" totalsRowDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="TOTAL" totalsRowFunction="sum" totalsRowDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}" name="Products" displayName="Products" ref="A1:F61" totalsRowShown="0" headerRowDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}" name="Products" displayName="Products" ref="A1:F61" totalsRowShown="0" headerRowDxfId="11">
   <autoFilter ref="A1:F61" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{E8F4DFB0-EC56-4CBF-9F8C-23EDCA50F713}" name="ProductID" dataCellStyle="Normal 3"/>
-    <tableColumn id="2" xr3:uid="{01A2DB73-B8C2-4A45-A7CC-94CB4A4A2FEF}" name="Product Name" dataDxfId="15" dataCellStyle="Comma 2"/>
+    <tableColumn id="2" xr3:uid="{01A2DB73-B8C2-4A45-A7CC-94CB4A4A2FEF}" name="Product Name" dataDxfId="10" dataCellStyle="Comma 2"/>
     <tableColumn id="3" xr3:uid="{D7712E33-EC2C-4BBC-9183-D4083230AE51}" name="Category" dataCellStyle="Normal 3"/>
-    <tableColumn id="4" xr3:uid="{10280736-93EE-4A73-97B0-1F59FABAB46F}" name="Cost/Unit" dataDxfId="14" dataCellStyle="Comma 2"/>
-    <tableColumn id="5" xr3:uid="{AC22B57B-F391-4278-9CEA-6381C3C7599A}" name="Reorder Level" dataDxfId="13" dataCellStyle="Normal 3"/>
-    <tableColumn id="6" xr3:uid="{ECE3A126-A7F6-4E8A-B4CA-AC1B78868DAB}" name="Supplier" dataDxfId="12" dataCellStyle="Normal 3"/>
+    <tableColumn id="4" xr3:uid="{10280736-93EE-4A73-97B0-1F59FABAB46F}" name="Cost/Unit" dataDxfId="9" dataCellStyle="Comma 2"/>
+    <tableColumn id="5" xr3:uid="{AC22B57B-F391-4278-9CEA-6381C3C7599A}" name="Reorder Level" dataDxfId="8" dataCellStyle="Normal 3"/>
+    <tableColumn id="6" xr3:uid="{ECE3A126-A7F6-4E8A-B4CA-AC1B78868DAB}" name="Supplier" dataDxfId="7" dataCellStyle="Normal 3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4625,25 +5210,25 @@
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{E8701318-3AEB-41C8-947D-8F382111F831}" name="Site" dataCellStyle="Normal 10"/>
     <tableColumn id="2" xr3:uid="{A8F9A49C-2A9D-43FA-9513-36E70E2B2700}" name="ProductID" dataCellStyle="Normal 10"/>
-    <tableColumn id="3" xr3:uid="{DD7691E1-3B82-419A-A596-FD7160832936}" name="Product Description" dataDxfId="37">
+    <tableColumn id="3" xr3:uid="{DD7691E1-3B82-419A-A596-FD7160832936}" name="Product Description" dataDxfId="32">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3B6081B7-6D7B-40BA-B050-3F97A1DD80EA}" name="Supplier" dataDxfId="36">
+    <tableColumn id="4" xr3:uid="{3B6081B7-6D7B-40BA-B050-3F97A1DD80EA}" name="Supplier" dataDxfId="31">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8BF557DE-8E2B-4AE9-8A66-D281C045EF9F}" name="Cost/Unit" dataDxfId="35">
+    <tableColumn id="5" xr3:uid="{8BF557DE-8E2B-4AE9-8A66-D281C045EF9F}" name="Cost/Unit" dataDxfId="30">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{82A09554-3010-4D9D-867D-4111E1CD453F}" name="Reorder Level" dataDxfId="34">
+    <tableColumn id="6" xr3:uid="{82A09554-3010-4D9D-867D-4111E1CD453F}" name="Reorder Level" dataDxfId="29">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{B0173CF8-A36E-441A-B27D-4CB13138DA80}" name="QuantityOnHand">
       <calculatedColumnFormula>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F1713281-EF53-48D5-9D64-F33AD9F1106B}" name="Stock Value" dataDxfId="33">
+    <tableColumn id="8" xr3:uid="{F1713281-EF53-48D5-9D64-F33AD9F1106B}" name="Stock Value" dataDxfId="28">
       <calculatedColumnFormula>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1AD33891-BE48-4965-8EAA-F8F9DE5AFD47}" name="Reorder" dataDxfId="32">
+    <tableColumn id="9" xr3:uid="{1AD33891-BE48-4965-8EAA-F8F9DE5AFD47}" name="Reorder" dataDxfId="27">
       <calculatedColumnFormula>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{02298217-ED20-499A-84FA-6F2061FCCDF1}" name="Order Date"/>
@@ -9438,7 +10023,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B62" s="85">
         <v>45910</v>
@@ -9458,7 +10043,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B63" s="85">
         <v>45910</v>
@@ -9478,7 +10063,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B64" s="85">
         <v>45910</v>
@@ -9498,7 +10083,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B65" s="85">
         <v>45910</v>
@@ -9518,7 +10103,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B66" s="85">
         <v>45910</v>
@@ -9538,7 +10123,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B67" s="85">
         <v>45911</v>
@@ -9558,7 +10143,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B68" s="85">
         <v>45911</v>
@@ -9578,7 +10163,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B69" s="85">
         <v>45911</v>
@@ -9598,7 +10183,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B70" s="85">
         <v>45912</v>
@@ -9618,7 +10203,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B71" s="85">
         <v>45912</v>
@@ -9638,7 +10223,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B72" s="85">
         <v>45912</v>
@@ -9658,7 +10243,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B73" s="85">
         <v>45913</v>
@@ -12073,10 +12658,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12127,6 +12712,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA3C0E5C-5F90-48A5-9B79-2947468EC928}">
+  <sheetPr>
+    <tabColor theme="7" tint="0.39997558519241921"/>
+  </sheetPr>
   <dimension ref="A1:E96"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -12141,7 +12729,7 @@
         <v>90</v>
       </c>
       <c r="B1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
@@ -12154,10 +12742,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="77" t="s">
+        <v>309</v>
+      </c>
+      <c r="B4" s="77" t="s">
         <v>308</v>
-      </c>
-      <c r="B4" s="77" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
@@ -12221,7 +12809,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="78" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B10" s="79">
         <v>100</v>
@@ -12318,7 +12906,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="78" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B19" s="79">
         <v>35</v>
@@ -12415,7 +13003,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="78" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B28" s="79">
         <v>28</v>
@@ -12510,7 +13098,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="78" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B37" s="79">
         <v>5</v>
@@ -12605,7 +13193,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="78" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B46" s="79"/>
       <c r="C46" s="79">
@@ -12735,7 +13323,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="78" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B58" s="79">
         <v>190</v>
@@ -12834,7 +13422,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" s="78" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B67" s="79">
         <v>80</v>
@@ -12929,7 +13517,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="78" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B76" s="79"/>
       <c r="C76" s="79">
@@ -13022,7 +13610,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="78" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B85" s="79">
         <v>38</v>
@@ -13119,7 +13707,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94" s="78" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B94" s="79">
         <v>65</v>
@@ -13169,4 +13757,1392 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7314C2BE-BA7C-4B43-81FB-A1961855FF30}">
+  <dimension ref="A2:K44"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="31.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" s="77" t="s">
+        <v>333</v>
+      </c>
+      <c r="B2" s="77" t="s">
+        <v>308</v>
+      </c>
+      <c r="G2" s="77" t="s">
+        <v>307</v>
+      </c>
+      <c r="H2" s="77" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A3" s="77" t="s">
+        <v>305</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G3" s="77" t="s">
+        <v>305</v>
+      </c>
+      <c r="H3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A4" s="78" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="79">
+        <v>0</v>
+      </c>
+      <c r="C4" s="79">
+        <v>0</v>
+      </c>
+      <c r="D4" s="79">
+        <v>10</v>
+      </c>
+      <c r="E4" s="79">
+        <v>10</v>
+      </c>
+      <c r="G4" s="78" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" s="79">
+        <v>0</v>
+      </c>
+      <c r="I4" s="79">
+        <v>0</v>
+      </c>
+      <c r="J4" s="79">
+        <v>890</v>
+      </c>
+      <c r="K4" s="79">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" s="80" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="79">
+        <v>0</v>
+      </c>
+      <c r="C5" s="79">
+        <v>0</v>
+      </c>
+      <c r="D5" s="79">
+        <v>10</v>
+      </c>
+      <c r="E5" s="79">
+        <v>10</v>
+      </c>
+      <c r="G5" s="80" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" s="79">
+        <v>0</v>
+      </c>
+      <c r="I5" s="79">
+        <v>0</v>
+      </c>
+      <c r="J5" s="79">
+        <v>890</v>
+      </c>
+      <c r="K5" s="79">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A6" s="78" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="79">
+        <v>25</v>
+      </c>
+      <c r="C6" s="79">
+        <v>0</v>
+      </c>
+      <c r="D6" s="79">
+        <v>0</v>
+      </c>
+      <c r="E6" s="79">
+        <v>25</v>
+      </c>
+      <c r="G6" s="78" t="s">
+        <v>127</v>
+      </c>
+      <c r="H6" s="79">
+        <v>93.75</v>
+      </c>
+      <c r="I6" s="79">
+        <v>0</v>
+      </c>
+      <c r="J6" s="79">
+        <v>0</v>
+      </c>
+      <c r="K6" s="79">
+        <v>93.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A7" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="79">
+        <v>25</v>
+      </c>
+      <c r="C7" s="79">
+        <v>0</v>
+      </c>
+      <c r="D7" s="79">
+        <v>0</v>
+      </c>
+      <c r="E7" s="79">
+        <v>25</v>
+      </c>
+      <c r="G7" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="79">
+        <v>93.75</v>
+      </c>
+      <c r="I7" s="79">
+        <v>0</v>
+      </c>
+      <c r="J7" s="79">
+        <v>0</v>
+      </c>
+      <c r="K7" s="79">
+        <v>93.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A8" s="78" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="79">
+        <v>0</v>
+      </c>
+      <c r="C8" s="79">
+        <v>0</v>
+      </c>
+      <c r="D8" s="79">
+        <v>10</v>
+      </c>
+      <c r="E8" s="79">
+        <v>10</v>
+      </c>
+      <c r="G8" s="78" t="s">
+        <v>126</v>
+      </c>
+      <c r="H8" s="79">
+        <v>0</v>
+      </c>
+      <c r="I8" s="79">
+        <v>0</v>
+      </c>
+      <c r="J8" s="79">
+        <v>21</v>
+      </c>
+      <c r="K8" s="79">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A9" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="79">
+        <v>0</v>
+      </c>
+      <c r="C9" s="79">
+        <v>0</v>
+      </c>
+      <c r="D9" s="79">
+        <v>10</v>
+      </c>
+      <c r="E9" s="79">
+        <v>10</v>
+      </c>
+      <c r="G9" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="79">
+        <v>0</v>
+      </c>
+      <c r="I9" s="79">
+        <v>0</v>
+      </c>
+      <c r="J9" s="79">
+        <v>21</v>
+      </c>
+      <c r="K9" s="79">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A10" s="78" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="79">
+        <v>0</v>
+      </c>
+      <c r="C10" s="79">
+        <v>15</v>
+      </c>
+      <c r="D10" s="79">
+        <v>0</v>
+      </c>
+      <c r="E10" s="79">
+        <v>15</v>
+      </c>
+      <c r="G10" s="78" t="s">
+        <v>123</v>
+      </c>
+      <c r="H10" s="79">
+        <v>0</v>
+      </c>
+      <c r="I10" s="79">
+        <v>18.75</v>
+      </c>
+      <c r="J10" s="79">
+        <v>0</v>
+      </c>
+      <c r="K10" s="79">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A11" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="79">
+        <v>0</v>
+      </c>
+      <c r="C11" s="79">
+        <v>15</v>
+      </c>
+      <c r="D11" s="79">
+        <v>0</v>
+      </c>
+      <c r="E11" s="79">
+        <v>15</v>
+      </c>
+      <c r="G11" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="79">
+        <v>0</v>
+      </c>
+      <c r="I11" s="79">
+        <v>18.75</v>
+      </c>
+      <c r="J11" s="79">
+        <v>0</v>
+      </c>
+      <c r="K11" s="79">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A12" s="78" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="79">
+        <v>0</v>
+      </c>
+      <c r="C12" s="79">
+        <v>30</v>
+      </c>
+      <c r="D12" s="79">
+        <v>0</v>
+      </c>
+      <c r="E12" s="79">
+        <v>30</v>
+      </c>
+      <c r="G12" s="78" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="79">
+        <v>0</v>
+      </c>
+      <c r="I12" s="79">
+        <v>345</v>
+      </c>
+      <c r="J12" s="79">
+        <v>0</v>
+      </c>
+      <c r="K12" s="79">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A13" s="80" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="79">
+        <v>0</v>
+      </c>
+      <c r="C13" s="79">
+        <v>30</v>
+      </c>
+      <c r="D13" s="79">
+        <v>0</v>
+      </c>
+      <c r="E13" s="79">
+        <v>30</v>
+      </c>
+      <c r="G13" s="80" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="79">
+        <v>0</v>
+      </c>
+      <c r="I13" s="79">
+        <v>345</v>
+      </c>
+      <c r="J13" s="79">
+        <v>0</v>
+      </c>
+      <c r="K13" s="79">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A14" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="79">
+        <v>25</v>
+      </c>
+      <c r="C14" s="79">
+        <v>0</v>
+      </c>
+      <c r="D14" s="79">
+        <v>0</v>
+      </c>
+      <c r="E14" s="79">
+        <v>25</v>
+      </c>
+      <c r="G14" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="79">
+        <v>156.25</v>
+      </c>
+      <c r="I14" s="79">
+        <v>0</v>
+      </c>
+      <c r="J14" s="79">
+        <v>0</v>
+      </c>
+      <c r="K14" s="79">
+        <v>156.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A15" s="80" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="79">
+        <v>25</v>
+      </c>
+      <c r="C15" s="79">
+        <v>0</v>
+      </c>
+      <c r="D15" s="79">
+        <v>0</v>
+      </c>
+      <c r="E15" s="79">
+        <v>25</v>
+      </c>
+      <c r="G15" s="80" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="79">
+        <v>156.25</v>
+      </c>
+      <c r="I15" s="79">
+        <v>0</v>
+      </c>
+      <c r="J15" s="79">
+        <v>0</v>
+      </c>
+      <c r="K15" s="79">
+        <v>156.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A16" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="79">
+        <v>0</v>
+      </c>
+      <c r="C16" s="79">
+        <v>0</v>
+      </c>
+      <c r="D16" s="79">
+        <v>14</v>
+      </c>
+      <c r="E16" s="79">
+        <v>14</v>
+      </c>
+      <c r="G16" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="H16" s="79">
+        <v>0</v>
+      </c>
+      <c r="I16" s="79">
+        <v>0</v>
+      </c>
+      <c r="J16" s="79">
+        <v>252</v>
+      </c>
+      <c r="K16" s="79">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A17" s="80" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="79">
+        <v>0</v>
+      </c>
+      <c r="C17" s="79">
+        <v>0</v>
+      </c>
+      <c r="D17" s="79">
+        <v>14</v>
+      </c>
+      <c r="E17" s="79">
+        <v>14</v>
+      </c>
+      <c r="G17" s="80" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="79">
+        <v>0</v>
+      </c>
+      <c r="I17" s="79">
+        <v>0</v>
+      </c>
+      <c r="J17" s="79">
+        <v>252</v>
+      </c>
+      <c r="K17" s="79">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A18" s="78" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="79">
+        <v>0</v>
+      </c>
+      <c r="C18" s="79">
+        <v>20</v>
+      </c>
+      <c r="D18" s="79">
+        <v>0</v>
+      </c>
+      <c r="E18" s="79">
+        <v>20</v>
+      </c>
+      <c r="G18" s="78" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="79">
+        <v>0</v>
+      </c>
+      <c r="I18" s="79">
+        <v>290</v>
+      </c>
+      <c r="J18" s="79">
+        <v>0</v>
+      </c>
+      <c r="K18" s="79">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A19" s="80" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="79">
+        <v>0</v>
+      </c>
+      <c r="C19" s="79">
+        <v>20</v>
+      </c>
+      <c r="D19" s="79">
+        <v>0</v>
+      </c>
+      <c r="E19" s="79">
+        <v>20</v>
+      </c>
+      <c r="G19" s="80" t="s">
+        <v>69</v>
+      </c>
+      <c r="H19" s="79">
+        <v>0</v>
+      </c>
+      <c r="I19" s="79">
+        <v>290</v>
+      </c>
+      <c r="J19" s="79">
+        <v>0</v>
+      </c>
+      <c r="K19" s="79">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A20" s="78" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" s="79">
+        <v>0</v>
+      </c>
+      <c r="C20" s="79">
+        <v>25</v>
+      </c>
+      <c r="D20" s="79">
+        <v>0</v>
+      </c>
+      <c r="E20" s="79">
+        <v>25</v>
+      </c>
+      <c r="G20" s="78" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" s="79">
+        <v>0</v>
+      </c>
+      <c r="I20" s="79">
+        <v>11875</v>
+      </c>
+      <c r="J20" s="79">
+        <v>0</v>
+      </c>
+      <c r="K20" s="79">
+        <v>11875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A21" s="80" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="79">
+        <v>0</v>
+      </c>
+      <c r="C21" s="79">
+        <v>25</v>
+      </c>
+      <c r="D21" s="79">
+        <v>0</v>
+      </c>
+      <c r="E21" s="79">
+        <v>25</v>
+      </c>
+      <c r="G21" s="80" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="79">
+        <v>0</v>
+      </c>
+      <c r="I21" s="79">
+        <v>11875</v>
+      </c>
+      <c r="J21" s="79">
+        <v>0</v>
+      </c>
+      <c r="K21" s="79">
+        <v>11875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A22" s="78" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="79">
+        <v>12</v>
+      </c>
+      <c r="C22" s="79">
+        <v>0</v>
+      </c>
+      <c r="D22" s="79">
+        <v>0</v>
+      </c>
+      <c r="E22" s="79">
+        <v>12</v>
+      </c>
+      <c r="G22" s="78" t="s">
+        <v>102</v>
+      </c>
+      <c r="H22" s="79">
+        <v>117</v>
+      </c>
+      <c r="I22" s="79">
+        <v>0</v>
+      </c>
+      <c r="J22" s="79">
+        <v>0</v>
+      </c>
+      <c r="K22" s="79">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A23" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="79">
+        <v>12</v>
+      </c>
+      <c r="C23" s="79">
+        <v>0</v>
+      </c>
+      <c r="D23" s="79">
+        <v>0</v>
+      </c>
+      <c r="E23" s="79">
+        <v>12</v>
+      </c>
+      <c r="G23" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H23" s="79">
+        <v>117</v>
+      </c>
+      <c r="I23" s="79">
+        <v>0</v>
+      </c>
+      <c r="J23" s="79">
+        <v>0</v>
+      </c>
+      <c r="K23" s="79">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A24" s="78" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="79">
+        <v>50</v>
+      </c>
+      <c r="C24" s="79">
+        <v>0</v>
+      </c>
+      <c r="D24" s="79">
+        <v>0</v>
+      </c>
+      <c r="E24" s="79">
+        <v>50</v>
+      </c>
+      <c r="G24" s="78" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="79">
+        <v>625</v>
+      </c>
+      <c r="I24" s="79">
+        <v>0</v>
+      </c>
+      <c r="J24" s="79">
+        <v>0</v>
+      </c>
+      <c r="K24" s="79">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A25" s="80" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="79">
+        <v>50</v>
+      </c>
+      <c r="C25" s="79">
+        <v>0</v>
+      </c>
+      <c r="D25" s="79">
+        <v>0</v>
+      </c>
+      <c r="E25" s="79">
+        <v>50</v>
+      </c>
+      <c r="G25" s="80" t="s">
+        <v>63</v>
+      </c>
+      <c r="H25" s="79">
+        <v>625</v>
+      </c>
+      <c r="I25" s="79">
+        <v>0</v>
+      </c>
+      <c r="J25" s="79">
+        <v>0</v>
+      </c>
+      <c r="K25" s="79">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A26" s="78" t="s">
+        <v>121</v>
+      </c>
+      <c r="B26" s="79">
+        <v>0</v>
+      </c>
+      <c r="C26" s="79">
+        <v>0</v>
+      </c>
+      <c r="D26" s="79">
+        <v>35</v>
+      </c>
+      <c r="E26" s="79">
+        <v>35</v>
+      </c>
+      <c r="G26" s="78" t="s">
+        <v>121</v>
+      </c>
+      <c r="H26" s="79">
+        <v>0</v>
+      </c>
+      <c r="I26" s="79">
+        <v>0</v>
+      </c>
+      <c r="J26" s="79">
+        <v>3325</v>
+      </c>
+      <c r="K26" s="79">
+        <v>3325</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A27" s="80" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="79">
+        <v>0</v>
+      </c>
+      <c r="C27" s="79">
+        <v>0</v>
+      </c>
+      <c r="D27" s="79">
+        <v>35</v>
+      </c>
+      <c r="E27" s="79">
+        <v>35</v>
+      </c>
+      <c r="G27" s="80" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" s="79">
+        <v>0</v>
+      </c>
+      <c r="I27" s="79">
+        <v>0</v>
+      </c>
+      <c r="J27" s="79">
+        <v>3325</v>
+      </c>
+      <c r="K27" s="79">
+        <v>3325</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A28" s="78" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" s="79">
+        <v>60</v>
+      </c>
+      <c r="C28" s="79">
+        <v>0</v>
+      </c>
+      <c r="D28" s="79">
+        <v>0</v>
+      </c>
+      <c r="E28" s="79">
+        <v>60</v>
+      </c>
+      <c r="G28" s="78" t="s">
+        <v>118</v>
+      </c>
+      <c r="H28" s="79">
+        <v>390</v>
+      </c>
+      <c r="I28" s="79">
+        <v>0</v>
+      </c>
+      <c r="J28" s="79">
+        <v>0</v>
+      </c>
+      <c r="K28" s="79">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A29" s="80" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="79">
+        <v>60</v>
+      </c>
+      <c r="C29" s="79">
+        <v>0</v>
+      </c>
+      <c r="D29" s="79">
+        <v>0</v>
+      </c>
+      <c r="E29" s="79">
+        <v>60</v>
+      </c>
+      <c r="G29" s="80" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29" s="79">
+        <v>390</v>
+      </c>
+      <c r="I29" s="79">
+        <v>0</v>
+      </c>
+      <c r="J29" s="79">
+        <v>0</v>
+      </c>
+      <c r="K29" s="79">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A30" s="78" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="79">
+        <v>20</v>
+      </c>
+      <c r="C30" s="79">
+        <v>0</v>
+      </c>
+      <c r="D30" s="79">
+        <v>0</v>
+      </c>
+      <c r="E30" s="79">
+        <v>20</v>
+      </c>
+      <c r="G30" s="78" t="s">
+        <v>122</v>
+      </c>
+      <c r="H30" s="79">
+        <v>450</v>
+      </c>
+      <c r="I30" s="79">
+        <v>0</v>
+      </c>
+      <c r="J30" s="79">
+        <v>0</v>
+      </c>
+      <c r="K30" s="79">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A31" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="79">
+        <v>20</v>
+      </c>
+      <c r="C31" s="79">
+        <v>0</v>
+      </c>
+      <c r="D31" s="79">
+        <v>0</v>
+      </c>
+      <c r="E31" s="79">
+        <v>20</v>
+      </c>
+      <c r="G31" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="H31" s="79">
+        <v>450</v>
+      </c>
+      <c r="I31" s="79">
+        <v>0</v>
+      </c>
+      <c r="J31" s="79">
+        <v>0</v>
+      </c>
+      <c r="K31" s="79">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A32" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="79">
+        <v>35</v>
+      </c>
+      <c r="C32" s="79">
+        <v>0</v>
+      </c>
+      <c r="D32" s="79">
+        <v>0</v>
+      </c>
+      <c r="E32" s="79">
+        <v>35</v>
+      </c>
+      <c r="G32" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="H32" s="79">
+        <v>4375</v>
+      </c>
+      <c r="I32" s="79">
+        <v>0</v>
+      </c>
+      <c r="J32" s="79">
+        <v>0</v>
+      </c>
+      <c r="K32" s="79">
+        <v>4375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A33" s="80" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="79">
+        <v>35</v>
+      </c>
+      <c r="C33" s="79">
+        <v>0</v>
+      </c>
+      <c r="D33" s="79">
+        <v>0</v>
+      </c>
+      <c r="E33" s="79">
+        <v>35</v>
+      </c>
+      <c r="G33" s="80" t="s">
+        <v>74</v>
+      </c>
+      <c r="H33" s="79">
+        <v>4375</v>
+      </c>
+      <c r="I33" s="79">
+        <v>0</v>
+      </c>
+      <c r="J33" s="79">
+        <v>0</v>
+      </c>
+      <c r="K33" s="79">
+        <v>4375</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A34" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" s="79">
+        <v>0</v>
+      </c>
+      <c r="C34" s="79">
+        <v>0</v>
+      </c>
+      <c r="D34" s="79">
+        <v>40</v>
+      </c>
+      <c r="E34" s="79">
+        <v>40</v>
+      </c>
+      <c r="G34" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="H34" s="79">
+        <v>0</v>
+      </c>
+      <c r="I34" s="79">
+        <v>0</v>
+      </c>
+      <c r="J34" s="79">
+        <v>170</v>
+      </c>
+      <c r="K34" s="79">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A35" s="80" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="79">
+        <v>0</v>
+      </c>
+      <c r="C35" s="79">
+        <v>0</v>
+      </c>
+      <c r="D35" s="79">
+        <v>40</v>
+      </c>
+      <c r="E35" s="79">
+        <v>40</v>
+      </c>
+      <c r="G35" s="80" t="s">
+        <v>67</v>
+      </c>
+      <c r="H35" s="79">
+        <v>0</v>
+      </c>
+      <c r="I35" s="79">
+        <v>0</v>
+      </c>
+      <c r="J35" s="79">
+        <v>170</v>
+      </c>
+      <c r="K35" s="79">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A36" s="78" t="s">
+        <v>116</v>
+      </c>
+      <c r="B36" s="79">
+        <v>0</v>
+      </c>
+      <c r="C36" s="79">
+        <v>0</v>
+      </c>
+      <c r="D36" s="79">
+        <v>18</v>
+      </c>
+      <c r="E36" s="79">
+        <v>18</v>
+      </c>
+      <c r="G36" s="78" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" s="79">
+        <v>0</v>
+      </c>
+      <c r="I36" s="79">
+        <v>0</v>
+      </c>
+      <c r="J36" s="79">
+        <v>337.5</v>
+      </c>
+      <c r="K36" s="79">
+        <v>337.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A37" s="80" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="79">
+        <v>0</v>
+      </c>
+      <c r="C37" s="79">
+        <v>0</v>
+      </c>
+      <c r="D37" s="79">
+        <v>18</v>
+      </c>
+      <c r="E37" s="79">
+        <v>18</v>
+      </c>
+      <c r="G37" s="80" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" s="79">
+        <v>0</v>
+      </c>
+      <c r="I37" s="79">
+        <v>0</v>
+      </c>
+      <c r="J37" s="79">
+        <v>337.5</v>
+      </c>
+      <c r="K37" s="79">
+        <v>337.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A38" s="78" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="79">
+        <v>0</v>
+      </c>
+      <c r="C38" s="79">
+        <v>30</v>
+      </c>
+      <c r="D38" s="79">
+        <v>0</v>
+      </c>
+      <c r="E38" s="79">
+        <v>30</v>
+      </c>
+      <c r="G38" s="78" t="s">
+        <v>98</v>
+      </c>
+      <c r="H38" s="79">
+        <v>0</v>
+      </c>
+      <c r="I38" s="79">
+        <v>2550</v>
+      </c>
+      <c r="J38" s="79">
+        <v>0</v>
+      </c>
+      <c r="K38" s="79">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A39" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" s="79">
+        <v>0</v>
+      </c>
+      <c r="C39" s="79">
+        <v>30</v>
+      </c>
+      <c r="D39" s="79">
+        <v>0</v>
+      </c>
+      <c r="E39" s="79">
+        <v>30</v>
+      </c>
+      <c r="G39" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H39" s="79">
+        <v>0</v>
+      </c>
+      <c r="I39" s="79">
+        <v>2550</v>
+      </c>
+      <c r="J39" s="79">
+        <v>0</v>
+      </c>
+      <c r="K39" s="79">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A40" s="78" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" s="79">
+        <v>0</v>
+      </c>
+      <c r="C40" s="79">
+        <v>25</v>
+      </c>
+      <c r="D40" s="79">
+        <v>0</v>
+      </c>
+      <c r="E40" s="79">
+        <v>25</v>
+      </c>
+      <c r="G40" s="78" t="s">
+        <v>129</v>
+      </c>
+      <c r="H40" s="79">
+        <v>0</v>
+      </c>
+      <c r="I40" s="79">
+        <v>462.5</v>
+      </c>
+      <c r="J40" s="79">
+        <v>0</v>
+      </c>
+      <c r="K40" s="79">
+        <v>462.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A41" s="80" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="79">
+        <v>0</v>
+      </c>
+      <c r="C41" s="79">
+        <v>25</v>
+      </c>
+      <c r="D41" s="79">
+        <v>0</v>
+      </c>
+      <c r="E41" s="79">
+        <v>25</v>
+      </c>
+      <c r="G41" s="80" t="s">
+        <v>84</v>
+      </c>
+      <c r="H41" s="79">
+        <v>0</v>
+      </c>
+      <c r="I41" s="79">
+        <v>462.5</v>
+      </c>
+      <c r="J41" s="79">
+        <v>0</v>
+      </c>
+      <c r="K41" s="79">
+        <v>462.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A42" s="78" t="s">
+        <v>120</v>
+      </c>
+      <c r="B42" s="79">
+        <v>0</v>
+      </c>
+      <c r="C42" s="79">
+        <v>50</v>
+      </c>
+      <c r="D42" s="79">
+        <v>0</v>
+      </c>
+      <c r="E42" s="79">
+        <v>50</v>
+      </c>
+      <c r="G42" s="78" t="s">
+        <v>120</v>
+      </c>
+      <c r="H42" s="79">
+        <v>0</v>
+      </c>
+      <c r="I42" s="79">
+        <v>7250</v>
+      </c>
+      <c r="J42" s="79">
+        <v>0</v>
+      </c>
+      <c r="K42" s="79">
+        <v>7250</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A43" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="B43" s="79">
+        <v>0</v>
+      </c>
+      <c r="C43" s="79">
+        <v>50</v>
+      </c>
+      <c r="D43" s="79">
+        <v>0</v>
+      </c>
+      <c r="E43" s="79">
+        <v>50</v>
+      </c>
+      <c r="G43" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" s="79">
+        <v>0</v>
+      </c>
+      <c r="I43" s="79">
+        <v>7250</v>
+      </c>
+      <c r="J43" s="79">
+        <v>0</v>
+      </c>
+      <c r="K43" s="79">
+        <v>7250</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A44" s="78" t="s">
+        <v>306</v>
+      </c>
+      <c r="B44" s="79">
+        <v>227</v>
+      </c>
+      <c r="C44" s="79">
+        <v>195</v>
+      </c>
+      <c r="D44" s="79">
+        <v>127</v>
+      </c>
+      <c r="E44" s="79">
+        <v>549</v>
+      </c>
+      <c r="G44" s="78" t="s">
+        <v>306</v>
+      </c>
+      <c r="H44" s="79">
+        <v>6207</v>
+      </c>
+      <c r="I44" s="79">
+        <v>22791.25</v>
+      </c>
+      <c r="J44" s="79">
+        <v>4995.5</v>
+      </c>
+      <c r="K44" s="79">
+        <v>33993.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B1:D1048576">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/DataAnalyst.xlsx
+++ b/DataAnalyst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malik\OneDrive\Documents\Data\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8956CD8-05AA-439E-AC43-1A505CDB4606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFF76EF-BAFB-4647-A18E-8A9CCFCB2AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,9 @@
     <sheet name="Products" sheetId="3" r:id="rId3"/>
     <sheet name="Transactions" sheetId="4" r:id="rId4"/>
     <sheet name="Inventory" sheetId="5" r:id="rId5"/>
-    <sheet name="Order" sheetId="6" r:id="rId6"/>
-    <sheet name="Reports" sheetId="7" r:id="rId7"/>
+    <sheet name="Total Stock Value" sheetId="8" r:id="rId6"/>
+    <sheet name="Order" sheetId="6" r:id="rId7"/>
+    <sheet name="Reports" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="ProductList">Products[ProductID]</definedName>
@@ -27,13 +28,13 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="40" r:id="rId8"/>
+    <pivotCache cacheId="40" r:id="rId9"/>
   </pivotCaches>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId9"/>
+        <x14:slicerCache r:id="rId10"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="335">
   <si>
     <t>ELECTRONICS COMPANIES REPORT Q1 2023</t>
   </si>
@@ -1057,19 +1058,23 @@
   </si>
   <si>
     <t>Sum of QuantityOnHand</t>
+  </si>
+  <si>
+    <t>STOCK VALUE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00;\-&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="mmm/dd"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1149,8 +1154,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1187,8 +1208,14 @@
         <fgColor rgb="FFC0E6F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1339,6 +1366,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1354,7 +1390,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1583,6 +1619,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="11" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{72D35A1C-E0E1-4D48-ACA5-2713C7D76C54}"/>
@@ -1598,7 +1641,93 @@
     <cellStyle name="Normal 8" xfId="9" xr:uid="{0EFC0AAE-EB0E-4FA2-885A-2DA2EB3F3608}"/>
     <cellStyle name="Normal 9" xfId="10" xr:uid="{DFABB175-7506-410D-8AC4-26F83CE150B7}"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="35">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1637,26 +1766,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
@@ -5151,50 +5260,50 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="C4:Q31" totalsRowCount="1">
   <autoFilter ref="C4:Q30" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" totalsRowLabel="Total" totalsRowDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMPANIES" totalsRowDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NUMBER OF EMPLOYEES" totalsRowDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COLOR" totalsRowDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LAUNCH DATE" totalsRowDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="QUANTITY" totalsRowFunction="sum" totalsRowDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PRICE" totalsRowFunction="sum" totalsRowDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AMOUNT" totalsRowFunction="sum" totalsRowDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="QUANTITY " totalsRowDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRICE " totalsRowDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="AMOUNT " totalsRowFunction="sum" totalsRowDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QUANTITY  " totalsRowDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="PRICE  " totalsRowDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="AMOUNT  " totalsRowFunction="sum" totalsRowDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="TOTAL" totalsRowFunction="sum" totalsRowDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" totalsRowLabel="Total" totalsRowDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMPANIES" totalsRowDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NUMBER OF EMPLOYEES" totalsRowDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COLOR" totalsRowDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LAUNCH DATE" totalsRowDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="QUANTITY" totalsRowFunction="sum" totalsRowDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PRICE" totalsRowFunction="sum" totalsRowDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AMOUNT" totalsRowFunction="sum" totalsRowDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="QUANTITY " totalsRowDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRICE " totalsRowDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="AMOUNT " totalsRowFunction="sum" totalsRowDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="QUANTITY  " totalsRowDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="PRICE  " totalsRowDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="AMOUNT  " totalsRowFunction="sum" totalsRowDxfId="15"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="TOTAL" totalsRowFunction="sum" totalsRowDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}" name="Products" displayName="Products" ref="A1:F61" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}" name="Products" displayName="Products" ref="A1:F61" totalsRowShown="0" headerRowDxfId="13">
   <autoFilter ref="A1:F61" xr:uid="{40BC2372-BD88-49F5-808E-66ED1AE47FE9}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{E8F4DFB0-EC56-4CBF-9F8C-23EDCA50F713}" name="ProductID" dataCellStyle="Normal 3"/>
-    <tableColumn id="2" xr3:uid="{01A2DB73-B8C2-4A45-A7CC-94CB4A4A2FEF}" name="Product Name" dataDxfId="10" dataCellStyle="Comma 2"/>
+    <tableColumn id="2" xr3:uid="{01A2DB73-B8C2-4A45-A7CC-94CB4A4A2FEF}" name="Product Name" dataDxfId="12" dataCellStyle="Comma 2"/>
     <tableColumn id="3" xr3:uid="{D7712E33-EC2C-4BBC-9183-D4083230AE51}" name="Category" dataCellStyle="Normal 3"/>
-    <tableColumn id="4" xr3:uid="{10280736-93EE-4A73-97B0-1F59FABAB46F}" name="Cost/Unit" dataDxfId="9" dataCellStyle="Comma 2"/>
-    <tableColumn id="5" xr3:uid="{AC22B57B-F391-4278-9CEA-6381C3C7599A}" name="Reorder Level" dataDxfId="8" dataCellStyle="Normal 3"/>
-    <tableColumn id="6" xr3:uid="{ECE3A126-A7F6-4E8A-B4CA-AC1B78868DAB}" name="Supplier" dataDxfId="7" dataCellStyle="Normal 3"/>
+    <tableColumn id="4" xr3:uid="{10280736-93EE-4A73-97B0-1F59FABAB46F}" name="Cost/Unit" dataDxfId="11" dataCellStyle="Comma 2"/>
+    <tableColumn id="5" xr3:uid="{AC22B57B-F391-4278-9CEA-6381C3C7599A}" name="Reorder Level" dataDxfId="10" dataCellStyle="Normal 3"/>
+    <tableColumn id="6" xr3:uid="{ECE3A126-A7F6-4E8A-B4CA-AC1B78868DAB}" name="Supplier" dataDxfId="9" dataCellStyle="Normal 3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03C4EC66-596A-4191-8AD5-8C56A2B0936F}" name="Transactions" displayName="Transactions" ref="A1:F73" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03C4EC66-596A-4191-8AD5-8C56A2B0936F}" name="Transactions" displayName="Transactions" ref="A1:F73" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="A1:F73" xr:uid="{03C4EC66-596A-4191-8AD5-8C56A2B0936F}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{CF0FBA31-2E94-4135-8B0A-A8ADD4C1D54E}" name="TransID"/>
-    <tableColumn id="2" xr3:uid="{EB83FE89-2487-49C6-80BE-246C3764EFC8}" name="Date" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{EB83FE89-2487-49C6-80BE-246C3764EFC8}" name="Date" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{FE85118D-4F73-4CC4-947F-D727DBCF045B}" name="ProductID"/>
-    <tableColumn id="4" xr3:uid="{890FE897-5C0E-4846-94E3-254F9AB59CC8}" name="Site" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{D5DF56AA-CF75-4D46-9133-AE66DE368857}" name="Quantity" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{890FE897-5C0E-4846-94E3-254F9AB59CC8}" name="Site" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{D5DF56AA-CF75-4D46-9133-AE66DE368857}" name="Quantity" dataDxfId="4"/>
     <tableColumn id="6" xr3:uid="{8D0BBA31-EE38-4A83-9E89-796952F75830}" name="Type"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -5202,36 +5311,36 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A5DC87FD-A8D1-440B-BAC9-DE34E48E5936}" name="Inventory" displayName="Inventory" ref="A1:J61" totalsRowShown="0" headerRowDxfId="4" headerRowCellStyle="Normal 9">
-  <autoFilter ref="A1:J61" xr:uid="{A5DC87FD-A8D1-440B-BAC9-DE34E48E5936}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A5DC87FD-A8D1-440B-BAC9-DE34E48E5936}" name="Inventory" displayName="Inventory" ref="A1:J62" headerRowDxfId="8" headerRowCellStyle="Normal 9">
+  <autoFilter ref="A1:J62" xr:uid="{A5DC87FD-A8D1-440B-BAC9-DE34E48E5936}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J61">
     <sortCondition ref="I1:I61"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{E8701318-3AEB-41C8-947D-8F382111F831}" name="Site" dataCellStyle="Normal 10"/>
-    <tableColumn id="2" xr3:uid="{A8F9A49C-2A9D-43FA-9513-36E70E2B2700}" name="ProductID" dataCellStyle="Normal 10"/>
-    <tableColumn id="3" xr3:uid="{DD7691E1-3B82-419A-A596-FD7160832936}" name="Product Description" dataDxfId="32">
+    <tableColumn id="1" xr3:uid="{E8701318-3AEB-41C8-947D-8F382111F831}" name="Site" totalsRowLabel="Total" totalsRowDxfId="2" dataCellStyle="Normal 10"/>
+    <tableColumn id="2" xr3:uid="{A8F9A49C-2A9D-43FA-9513-36E70E2B2700}" name="ProductID" totalsRowDxfId="3" dataCellStyle="Normal 10"/>
+    <tableColumn id="3" xr3:uid="{DD7691E1-3B82-419A-A596-FD7160832936}" name="Product Description" dataDxfId="34">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Product Name],"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3B6081B7-6D7B-40BA-B050-3F97A1DD80EA}" name="Supplier" dataDxfId="31">
+    <tableColumn id="4" xr3:uid="{3B6081B7-6D7B-40BA-B050-3F97A1DD80EA}" name="Supplier" dataDxfId="33">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Supplier],"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8BF557DE-8E2B-4AE9-8A66-D281C045EF9F}" name="Cost/Unit" dataDxfId="30">
+    <tableColumn id="5" xr3:uid="{8BF557DE-8E2B-4AE9-8A66-D281C045EF9F}" name="Cost/Unit" dataDxfId="32">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Cost/Unit],"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{82A09554-3010-4D9D-867D-4111E1CD453F}" name="Reorder Level" dataDxfId="29">
+    <tableColumn id="6" xr3:uid="{82A09554-3010-4D9D-867D-4111E1CD453F}" name="Reorder Level" dataDxfId="31">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Inventory[[#This Row],[ProductID]],Products[ProductID],Products[Reorder Level],"Not Found")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{B0173CF8-A36E-441A-B27D-4CB13138DA80}" name="QuantityOnHand">
       <calculatedColumnFormula>SUMIFS(Transactions[Quantity],Transactions[ProductID],Inventory[[#This Row],[ProductID]],Transactions[Site],Inventory[[#This Row],[Site]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F1713281-EF53-48D5-9D64-F33AD9F1106B}" name="Stock Value" dataDxfId="28">
+    <tableColumn id="8" xr3:uid="{F1713281-EF53-48D5-9D64-F33AD9F1106B}" name="Stock Value" totalsRowFunction="sum" dataDxfId="30">
       <calculatedColumnFormula>Inventory[[#This Row],[Cost/Unit]]*Inventory[[#This Row],[QuantityOnHand]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1AD33891-BE48-4965-8EAA-F8F9DE5AFD47}" name="Reorder" dataDxfId="27">
+    <tableColumn id="9" xr3:uid="{1AD33891-BE48-4965-8EAA-F8F9DE5AFD47}" name="Reorder" dataDxfId="29">
       <calculatedColumnFormula>IF(Inventory[[#This Row],[QuantityOnHand]]&lt;=Inventory[[#This Row],[Reorder Level]],"Yes","No")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{02298217-ED20-499A-84FA-6F2061FCCDF1}" name="Order Date"/>
+    <tableColumn id="10" xr3:uid="{02298217-ED20-499A-84FA-6F2061FCCDF1}" name="Order Date" totalsRowFunction="count"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10280,16 +10389,16 @@
   <sheetPr>
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.59765625" customWidth="1"/>
     <col min="2" max="2" width="10.9296875" customWidth="1"/>
     <col min="3" max="6" width="30.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="12.3984375" customWidth="1"/>
+    <col min="8" max="8" width="13.796875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.796875" customWidth="1"/>
-    <col min="10" max="10" width="11.86328125" customWidth="1"/>
+    <col min="10" max="10" width="19.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
@@ -12656,16 +12765,33 @@
         <v>46334</v>
       </c>
     </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A62" s="86"/>
+      <c r="B62" s="86"/>
+      <c r="C62" s="79"/>
+      <c r="D62" s="79"/>
+      <c r="E62" s="79"/>
+      <c r="F62" s="79"/>
+      <c r="H62" s="79"/>
+      <c r="I62" s="79"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",I1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",I1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -12677,13 +12803,6 @@
           <x14:id>{DA699FD3-20CD-4065-9BA7-E2DA1B7037F2}</x14:id>
         </ext>
       </extLst>
-    </cfRule>
-    <cfRule type="iconSet" priority="1">
-      <iconSet iconSet="3Arrows">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="33"/>
-        <cfvo type="percent" val="67"/>
-      </iconSet>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12711,6 +12830,43 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5869EC6-E2ED-4AE1-A2D2-D67FC34A817A}">
+  <sheetPr>
+    <tabColor theme="7" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="12.46484375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="87" t="s">
+        <v>334</v>
+      </c>
+      <c r="B1" s="88">
+        <f>SUM(Inventory!H:H)</f>
+        <v>40839.75</v>
+      </c>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+    </row>
+    <row r="2" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA3C0E5C-5F90-48A5-9B79-2947468EC928}">
   <sheetPr>
     <tabColor theme="7" tint="0.39997558519241921"/>
@@ -13759,7 +13915,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7314C2BE-BA7C-4B43-81FB-A1961855FF30}">
   <dimension ref="A2:K44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>

--- a/DataAnalyst.xlsx
+++ b/DataAnalyst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malik\OneDrive\Documents\Data\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFF76EF-BAFB-4647-A18E-8A9CCFCB2AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50710F22-A42C-4453-A8E6-8A8858D0ABBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-9210" windowWidth="21840" windowHeight="13740" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="334">
   <si>
     <t>ELECTRONICS COMPANIES REPORT Q1 2023</t>
   </si>
@@ -973,18 +973,12 @@
     <t>(All)</t>
   </si>
   <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
     <t>Grand Total</t>
   </si>
   <si>
     <t>Sum of Stock Value</t>
   </si>
   <si>
-    <t>Column Labels</t>
-  </si>
-  <si>
     <t>Sum of Reorder Level</t>
   </si>
   <si>
@@ -1061,6 +1055,9 @@
   </si>
   <si>
     <t>STOCK VALUE</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -2370,16 +2367,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -2415,7 +2412,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5876925" y="552450"/>
+              <a:off x="5572125" y="523875"/>
               <a:ext cx="1828800" cy="2524125"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3738,7 +3735,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38DC400E-84BC-4A77-AD46-FA601CF5F496}" name="PivotTable2" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38DC400E-84BC-4A77-AD46-FA601CF5F496}" name="PivotTable2" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="" colHeaderCaption="">
   <location ref="A4:E96" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="12">
     <pivotField axis="axisCol" subtotalTop="0" showAll="0" insertBlankRow="1">
@@ -4599,7 +4596,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8760556F-EE87-45AC-8AA1-691971073720}" name="PivotTable4" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8760556F-EE87-45AC-8AA1-691971073720}" name="PivotTable4" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="" colHeaderCaption="">
   <location ref="G2:K44" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField axis="axisCol" showAll="0">
@@ -4913,7 +4910,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{056141E7-6BFB-4C95-B00A-B531F48F40E9}" name="PivotTable3" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{056141E7-6BFB-4C95-B00A-B531F48F40E9}" name="PivotTable3" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="" colHeaderCaption="">
   <location ref="A2:E44" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField axis="axisCol" showAll="0">
@@ -10132,7 +10129,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B62" s="85">
         <v>45910</v>
@@ -10152,7 +10149,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B63" s="85">
         <v>45910</v>
@@ -10172,7 +10169,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B64" s="85">
         <v>45910</v>
@@ -10192,7 +10189,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B65" s="85">
         <v>45910</v>
@@ -10212,7 +10209,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B66" s="85">
         <v>45910</v>
@@ -10232,7 +10229,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B67" s="85">
         <v>45911</v>
@@ -10252,7 +10249,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B68" s="85">
         <v>45911</v>
@@ -10272,7 +10269,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B69" s="85">
         <v>45911</v>
@@ -10292,7 +10289,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B70" s="85">
         <v>45912</v>
@@ -10312,7 +10309,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B71" s="85">
         <v>45912</v>
@@ -10332,7 +10329,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B72" s="85">
         <v>45912</v>
@@ -10352,7 +10349,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B73" s="85">
         <v>45913</v>
@@ -12842,7 +12839,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="87" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B1" s="88">
         <f>SUM(Inventory!H:H)</f>
@@ -12885,7 +12882,7 @@
         <v>90</v>
       </c>
       <c r="B1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
@@ -12898,15 +12895,15 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="77" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B4" s="77" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="77" t="s">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -12918,7 +12915,7 @@
         <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -12965,7 +12962,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="78" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B10" s="79">
         <v>100</v>
@@ -13062,7 +13059,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="78" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B19" s="79">
         <v>35</v>
@@ -13159,7 +13156,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="78" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B28" s="79">
         <v>28</v>
@@ -13254,7 +13251,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="78" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B37" s="79">
         <v>5</v>
@@ -13349,7 +13346,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="78" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B46" s="79"/>
       <c r="C46" s="79">
@@ -13479,7 +13476,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="78" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B58" s="79">
         <v>190</v>
@@ -13578,7 +13575,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" s="78" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B67" s="79">
         <v>80</v>
@@ -13673,7 +13670,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="78" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B76" s="79"/>
       <c r="C76" s="79">
@@ -13766,7 +13763,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="78" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B85" s="79">
         <v>38</v>
@@ -13863,7 +13860,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94" s="78" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B94" s="79">
         <v>65</v>
@@ -13887,7 +13884,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A96" s="78" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B96" s="79">
         <v>541</v>
@@ -13933,21 +13930,21 @@
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="77" t="s">
+        <v>331</v>
+      </c>
+      <c r="B2" s="77" t="s">
         <v>333</v>
       </c>
-      <c r="B2" s="77" t="s">
-        <v>308</v>
-      </c>
       <c r="G2" s="77" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H2" s="77" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="77" t="s">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -13959,10 +13956,10 @@
         <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G3" s="77" t="s">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="H3" t="s">
         <v>62</v>
@@ -13974,7 +13971,7 @@
         <v>65</v>
       </c>
       <c r="K3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
@@ -15259,7 +15256,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" s="78" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B44" s="79">
         <v>227</v>
@@ -15274,7 +15271,7 @@
         <v>549</v>
       </c>
       <c r="G44" s="78" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H44" s="79">
         <v>6207</v>
